--- a/data/BallparkPal_Teams.xlsx
+++ b/data/BallparkPal_Teams.xlsx
@@ -164,18 +164,54 @@
     <t>RunsInningExtra</t>
   </si>
   <si>
-    <t>2026-04-28</t>
+    <t>2026-04-29</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>CHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
     <t xml:space="preserve">SF </t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>NYM</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
     <t>ARI</t>
   </si>
   <si>
@@ -200,64 +236,28 @@
     <t>CIN</t>
   </si>
   <si>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
     <t>HOU</t>
   </si>
   <si>
     <t>BAL</t>
   </si>
   <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
     <t xml:space="preserve">KC </t>
   </si>
   <si>
     <t>ATH</t>
-  </si>
-  <si>
-    <t>BOS</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>NYY</t>
-  </si>
-  <si>
-    <t>TEX</t>
-  </si>
-  <si>
-    <t>CHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD </t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>WAS</t>
-  </si>
-  <si>
-    <t>NYM</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>MIN</t>
-  </si>
-  <si>
-    <t>LAA</t>
-  </si>
-  <si>
-    <t>CHW</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>ATL</t>
   </si>
   <si>
     <t>H</t>
@@ -754,7 +754,7 @@
     </row>
     <row r="2" spans="1:49">
       <c r="A2">
-        <v>823473</v>
+        <v>822821</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -769,141 +769,141 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>4.116</v>
+        <v>4.526</v>
       </c>
       <c r="G2">
-        <v>0.362</v>
+        <v>0.438</v>
       </c>
       <c r="H2">
-        <v>0.082</v>
+        <v>0.09</v>
       </c>
       <c r="I2">
-        <v>0.175</v>
+        <v>0.232</v>
       </c>
       <c r="J2">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="K2">
-        <v>0.343</v>
+        <v>0.299</v>
       </c>
       <c r="L2">
-        <v>0.967</v>
+        <v>1.244</v>
       </c>
       <c r="M2">
-        <v>0.11</v>
+        <v>0.133</v>
       </c>
       <c r="N2">
-        <v>1.41</v>
+        <v>1.821</v>
       </c>
       <c r="O2">
-        <v>6.102</v>
+        <v>5.246</v>
       </c>
       <c r="P2">
-        <v>2.825</v>
+        <v>2.955</v>
       </c>
       <c r="Q2">
-        <v>9.933</v>
+        <v>8.128</v>
       </c>
       <c r="R2">
-        <v>0.404</v>
+        <v>0.294</v>
       </c>
       <c r="S2">
-        <v>0.343</v>
+        <v>0.347</v>
       </c>
       <c r="T2">
-        <v>0.171</v>
+        <v>0.23</v>
       </c>
       <c r="U2">
+        <v>0.089</v>
+      </c>
+      <c r="V2">
+        <v>0.03</v>
+      </c>
+      <c r="W2">
+        <v>0.009</v>
+      </c>
+      <c r="X2">
         <v>0.054</v>
       </c>
-      <c r="V2">
-        <v>0.024</v>
-      </c>
-      <c r="W2">
-        <v>0.005</v>
-      </c>
-      <c r="X2">
-        <v>0.08</v>
-      </c>
       <c r="Y2">
-        <v>0.119</v>
+        <v>0.095</v>
       </c>
       <c r="Z2">
-        <v>0.141</v>
+        <v>0.124</v>
       </c>
       <c r="AA2">
         <v>0.139</v>
       </c>
       <c r="AB2">
-        <v>0.127</v>
+        <v>0.132</v>
       </c>
       <c r="AC2">
-        <v>0.115</v>
+        <v>0.124</v>
       </c>
       <c r="AD2">
-        <v>0.086</v>
+        <v>0.106</v>
       </c>
       <c r="AE2">
-        <v>0.062</v>
+        <v>0.075</v>
       </c>
       <c r="AF2">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="AG2">
-        <v>0.028</v>
+        <v>0.035</v>
       </c>
       <c r="AH2">
-        <v>0.017</v>
+        <v>0.026</v>
       </c>
       <c r="AI2">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="AJ2">
         <v>0.009</v>
       </c>
       <c r="AK2">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AL2">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN2">
-        <v>0.44</v>
+        <v>0.576</v>
       </c>
       <c r="AO2">
-        <v>0.402</v>
+        <v>0.53</v>
       </c>
       <c r="AP2">
-        <v>0.416</v>
+        <v>0.515</v>
       </c>
       <c r="AQ2">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="AR2">
-        <v>0.433</v>
+        <v>0.475</v>
       </c>
       <c r="AS2">
-        <v>0.426</v>
+        <v>0.449</v>
       </c>
       <c r="AT2">
-        <v>0.45</v>
+        <v>0.423</v>
       </c>
       <c r="AU2">
-        <v>0.459</v>
+        <v>0.424</v>
       </c>
       <c r="AV2">
-        <v>0.444</v>
+        <v>0.413</v>
       </c>
       <c r="AW2">
-        <v>0.141</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3" spans="1:49">
       <c r="A3">
-        <v>823798</v>
+        <v>822907</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -918,141 +918,141 @@
         <v>54</v>
       </c>
       <c r="F3">
-        <v>4.519</v>
+        <v>4.65</v>
       </c>
       <c r="G3">
-        <v>0.403</v>
+        <v>0.428</v>
       </c>
       <c r="H3">
-        <v>0.076</v>
+        <v>0.085</v>
       </c>
       <c r="I3">
-        <v>0.223</v>
+        <v>0.238</v>
       </c>
       <c r="J3">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K3">
-        <v>0.306</v>
+        <v>0.309</v>
       </c>
       <c r="L3">
-        <v>1.189</v>
+        <v>1.371</v>
       </c>
       <c r="M3">
-        <v>0.172</v>
+        <v>0.127</v>
       </c>
       <c r="N3">
-        <v>1.511</v>
+        <v>1.571</v>
       </c>
       <c r="O3">
-        <v>5.377</v>
+        <v>5.033</v>
       </c>
       <c r="P3">
-        <v>3.202</v>
+        <v>3.387</v>
       </c>
       <c r="Q3">
-        <v>7.628</v>
+        <v>8.899</v>
       </c>
       <c r="R3">
-        <v>0.307</v>
+        <v>0.27</v>
       </c>
       <c r="S3">
-        <v>0.359</v>
+        <v>0.328</v>
       </c>
       <c r="T3">
-        <v>0.214</v>
+        <v>0.241</v>
       </c>
       <c r="U3">
-        <v>0.084</v>
+        <v>0.106</v>
       </c>
       <c r="V3">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="W3">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="X3">
-        <v>0.062</v>
+        <v>0.056</v>
       </c>
       <c r="Y3">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="Z3">
+        <v>0.132</v>
+      </c>
+      <c r="AA3">
         <v>0.138</v>
       </c>
-      <c r="AA3">
-        <v>0.133</v>
-      </c>
       <c r="AB3">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="AC3">
-        <v>0.125</v>
+        <v>0.116</v>
       </c>
       <c r="AD3">
-        <v>0.084</v>
+        <v>0.091</v>
       </c>
       <c r="AE3">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="AF3">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
       <c r="AG3">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="AH3">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AI3">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="AJ3">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="AK3">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AM3">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AN3">
-        <v>0.529</v>
+        <v>0.536</v>
       </c>
       <c r="AO3">
-        <v>0.426</v>
+        <v>0.405</v>
       </c>
       <c r="AP3">
-        <v>0.455</v>
+        <v>0.53</v>
       </c>
       <c r="AQ3">
-        <v>0.487</v>
+        <v>0.445</v>
       </c>
       <c r="AR3">
+        <v>0.457</v>
+      </c>
+      <c r="AS3">
+        <v>0.5</v>
+      </c>
+      <c r="AT3">
+        <v>0.479</v>
+      </c>
+      <c r="AU3">
+        <v>0.554</v>
+      </c>
+      <c r="AV3">
         <v>0.507</v>
       </c>
-      <c r="AS3">
-        <v>0.481</v>
-      </c>
-      <c r="AT3">
-        <v>0.499</v>
-      </c>
-      <c r="AU3">
-        <v>0.448</v>
-      </c>
-      <c r="AV3">
-        <v>0.463</v>
-      </c>
       <c r="AW3">
-        <v>0.13</v>
+        <v>0.146</v>
       </c>
     </row>
     <row r="4" spans="1:49">
       <c r="A4">
-        <v>823956</v>
+        <v>823312</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -1067,141 +1067,141 @@
         <v>56</v>
       </c>
       <c r="F4">
-        <v>3.106</v>
+        <v>5.324</v>
       </c>
       <c r="G4">
-        <v>0.283</v>
+        <v>0.526</v>
       </c>
       <c r="H4">
-        <v>0.07</v>
+        <v>0.095</v>
       </c>
       <c r="I4">
-        <v>0.115</v>
+        <v>0.316</v>
       </c>
       <c r="J4">
-        <v>0.139</v>
+        <v>0.098</v>
       </c>
       <c r="K4">
-        <v>0.389</v>
+        <v>0.217</v>
       </c>
       <c r="L4">
-        <v>0.743</v>
+        <v>1.178</v>
       </c>
       <c r="M4">
-        <v>0.098</v>
+        <v>0.128</v>
       </c>
       <c r="N4">
-        <v>1.253</v>
+        <v>1.539</v>
       </c>
       <c r="O4">
-        <v>4.757</v>
+        <v>5.83</v>
       </c>
       <c r="P4">
-        <v>2.777</v>
+        <v>4.928</v>
       </c>
       <c r="Q4">
-        <v>10.882</v>
+        <v>8.137</v>
       </c>
       <c r="R4">
-        <v>0.487</v>
+        <v>0.317</v>
       </c>
       <c r="S4">
-        <v>0.335</v>
+        <v>0.357</v>
       </c>
       <c r="T4">
-        <v>0.136</v>
+        <v>0.203</v>
       </c>
       <c r="U4">
-        <v>0.032</v>
+        <v>0.089</v>
       </c>
       <c r="V4">
+        <v>0.023</v>
+      </c>
+      <c r="W4">
+        <v>0.011</v>
+      </c>
+      <c r="X4">
+        <v>0.033</v>
+      </c>
+      <c r="Y4">
+        <v>0.065</v>
+      </c>
+      <c r="Z4">
+        <v>0.113</v>
+      </c>
+      <c r="AA4">
+        <v>0.104</v>
+      </c>
+      <c r="AB4">
+        <v>0.12</v>
+      </c>
+      <c r="AC4">
+        <v>0.13</v>
+      </c>
+      <c r="AD4">
+        <v>0.11</v>
+      </c>
+      <c r="AE4">
+        <v>0.092</v>
+      </c>
+      <c r="AF4">
+        <v>0.077</v>
+      </c>
+      <c r="AG4">
+        <v>0.049</v>
+      </c>
+      <c r="AH4">
+        <v>0.045</v>
+      </c>
+      <c r="AI4">
+        <v>0.02</v>
+      </c>
+      <c r="AJ4">
+        <v>0.016</v>
+      </c>
+      <c r="AK4">
+        <v>0.011</v>
+      </c>
+      <c r="AL4">
+        <v>0.006</v>
+      </c>
+      <c r="AM4">
         <v>0.009</v>
       </c>
-      <c r="W4">
-        <v>0.001</v>
-      </c>
-      <c r="X4">
-        <v>0.134</v>
-      </c>
-      <c r="Y4">
-        <v>0.171</v>
-      </c>
-      <c r="Z4">
-        <v>0.183</v>
-      </c>
-      <c r="AA4">
-        <v>0.14</v>
-      </c>
-      <c r="AB4">
-        <v>0.113</v>
-      </c>
-      <c r="AC4">
-        <v>0.092</v>
-      </c>
-      <c r="AD4">
-        <v>0.066</v>
-      </c>
-      <c r="AE4">
-        <v>0.038</v>
-      </c>
-      <c r="AF4">
-        <v>0.029</v>
-      </c>
-      <c r="AG4">
-        <v>0.014</v>
-      </c>
-      <c r="AH4">
-        <v>0.009</v>
-      </c>
-      <c r="AI4">
-        <v>0.005</v>
-      </c>
-      <c r="AJ4">
-        <v>0.002</v>
-      </c>
-      <c r="AK4">
-        <v>0.002</v>
-      </c>
-      <c r="AL4">
-        <v>0.001</v>
-      </c>
-      <c r="AM4">
-        <v>0.0</v>
-      </c>
       <c r="AN4">
-        <v>0.323</v>
+        <v>0.665</v>
       </c>
       <c r="AO4">
-        <v>0.278</v>
+        <v>0.638</v>
       </c>
       <c r="AP4">
-        <v>0.294</v>
+        <v>0.653</v>
       </c>
       <c r="AQ4">
-        <v>0.295</v>
+        <v>0.634</v>
       </c>
       <c r="AR4">
-        <v>0.293</v>
+        <v>0.584</v>
       </c>
       <c r="AS4">
-        <v>0.317</v>
+        <v>0.503</v>
       </c>
       <c r="AT4">
-        <v>0.356</v>
+        <v>0.478</v>
       </c>
       <c r="AU4">
-        <v>0.398</v>
+        <v>0.47</v>
       </c>
       <c r="AV4">
-        <v>0.366</v>
+        <v>0.436</v>
       </c>
       <c r="AW4">
-        <v>0.109</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="5" spans="1:49">
       <c r="A5">
-        <v>824447</v>
+        <v>823392</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -1216,52 +1216,52 @@
         <v>58</v>
       </c>
       <c r="F5">
-        <v>4.477</v>
+        <v>3.952</v>
       </c>
       <c r="G5">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="H5">
-        <v>0.099</v>
+        <v>0.072</v>
       </c>
       <c r="I5">
-        <v>0.268</v>
+        <v>0.196</v>
       </c>
       <c r="J5">
-        <v>0.104</v>
+        <v>0.115</v>
       </c>
       <c r="K5">
-        <v>0.226</v>
+        <v>0.333</v>
       </c>
       <c r="L5">
-        <v>0.976</v>
+        <v>0.926</v>
       </c>
       <c r="M5">
-        <v>0.098</v>
+        <v>0.046</v>
       </c>
       <c r="N5">
-        <v>1.613</v>
+        <v>1.623</v>
       </c>
       <c r="O5">
-        <v>5.843</v>
+        <v>4.761</v>
       </c>
       <c r="P5">
-        <v>3.312</v>
+        <v>3.879</v>
       </c>
       <c r="Q5">
-        <v>7.41</v>
+        <v>8.716</v>
       </c>
       <c r="R5">
-        <v>0.379</v>
+        <v>0.394</v>
       </c>
       <c r="S5">
-        <v>0.361</v>
+        <v>0.369</v>
       </c>
       <c r="T5">
-        <v>0.184</v>
+        <v>0.17</v>
       </c>
       <c r="U5">
-        <v>0.063</v>
+        <v>0.053</v>
       </c>
       <c r="V5">
         <v>0.011</v>
@@ -1270,87 +1270,87 @@
         <v>0.003</v>
       </c>
       <c r="X5">
-        <v>0.054</v>
+        <v>0.087</v>
       </c>
       <c r="Y5">
-        <v>0.11</v>
+        <v>0.127</v>
       </c>
       <c r="Z5">
-        <v>0.122</v>
+        <v>0.153</v>
       </c>
       <c r="AA5">
         <v>0.139</v>
       </c>
       <c r="AB5">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="AC5">
-        <v>0.123</v>
+        <v>0.101</v>
       </c>
       <c r="AD5">
-        <v>0.098</v>
+        <v>0.084</v>
       </c>
       <c r="AE5">
-        <v>0.076</v>
+        <v>0.054</v>
       </c>
       <c r="AF5">
-        <v>0.054</v>
+        <v>0.046</v>
       </c>
       <c r="AG5">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="AH5">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="AI5">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AJ5">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="AK5">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AL5">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="AM5">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="AN5">
-        <v>0.502</v>
+        <v>0.424</v>
       </c>
       <c r="AO5">
-        <v>0.419</v>
+        <v>0.388</v>
       </c>
       <c r="AP5">
-        <v>0.502</v>
+        <v>0.396</v>
       </c>
       <c r="AQ5">
-        <v>0.517</v>
+        <v>0.377</v>
       </c>
       <c r="AR5">
+        <v>0.384</v>
+      </c>
+      <c r="AS5">
+        <v>0.443</v>
+      </c>
+      <c r="AT5">
+        <v>0.443</v>
+      </c>
+      <c r="AU5">
         <v>0.471</v>
       </c>
-      <c r="AS5">
-        <v>0.489</v>
-      </c>
-      <c r="AT5">
-        <v>0.462</v>
-      </c>
-      <c r="AU5">
-        <v>0.457</v>
-      </c>
       <c r="AV5">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
       <c r="AW5">
-        <v>0.135</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="6" spans="1:49">
       <c r="A6">
-        <v>824526</v>
+        <v>823471</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -1365,141 +1365,141 @@
         <v>60</v>
       </c>
       <c r="F6">
-        <v>4.134</v>
+        <v>3.918</v>
       </c>
       <c r="G6">
-        <v>0.401</v>
+        <v>0.387</v>
       </c>
       <c r="H6">
-        <v>0.09</v>
+        <v>0.081</v>
       </c>
       <c r="I6">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="J6">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="K6">
-        <v>0.299</v>
+        <v>0.308</v>
       </c>
       <c r="L6">
-        <v>1.243</v>
+        <v>0.903</v>
       </c>
       <c r="M6">
-        <v>0.138</v>
+        <v>0.108</v>
       </c>
       <c r="N6">
-        <v>1.451</v>
+        <v>1.304</v>
       </c>
       <c r="O6">
-        <v>4.619</v>
+        <v>6.139</v>
       </c>
       <c r="P6">
-        <v>3.426</v>
+        <v>2.664</v>
       </c>
       <c r="Q6">
-        <v>10.553</v>
+        <v>9.457</v>
       </c>
       <c r="R6">
-        <v>0.302</v>
+        <v>0.413</v>
       </c>
       <c r="S6">
-        <v>0.353</v>
+        <v>0.356</v>
       </c>
       <c r="T6">
-        <v>0.21</v>
+        <v>0.166</v>
       </c>
       <c r="U6">
-        <v>0.089</v>
+        <v>0.049</v>
       </c>
       <c r="V6">
-        <v>0.033</v>
+        <v>0.011</v>
       </c>
       <c r="W6">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="X6">
-        <v>0.071</v>
+        <v>0.086</v>
       </c>
       <c r="Y6">
-        <v>0.126</v>
+        <v>0.132</v>
       </c>
       <c r="Z6">
         <v>0.142</v>
       </c>
       <c r="AA6">
-        <v>0.147</v>
+        <v>0.146</v>
       </c>
       <c r="AB6">
-        <v>0.128</v>
+        <v>0.133</v>
       </c>
       <c r="AC6">
-        <v>0.104</v>
+        <v>0.107</v>
       </c>
       <c r="AD6">
-        <v>0.091</v>
+        <v>0.082</v>
       </c>
       <c r="AE6">
-        <v>0.064</v>
+        <v>0.057</v>
       </c>
       <c r="AF6">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="AG6">
         <v>0.032</v>
       </c>
       <c r="AH6">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="AI6">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="AJ6">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AK6">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AL6">
+        <v>0.001</v>
+      </c>
+      <c r="AM6">
         <v>0.004</v>
       </c>
-      <c r="AM6">
-        <v>0.006</v>
-      </c>
       <c r="AN6">
-        <v>0.384</v>
+        <v>0.373</v>
       </c>
       <c r="AO6">
-        <v>0.364</v>
+        <v>0.388</v>
       </c>
       <c r="AP6">
-        <v>0.399</v>
+        <v>0.381</v>
       </c>
       <c r="AQ6">
-        <v>0.378</v>
+        <v>0.397</v>
       </c>
       <c r="AR6">
-        <v>0.391</v>
+        <v>0.377</v>
       </c>
       <c r="AS6">
-        <v>0.465</v>
+        <v>0.43</v>
       </c>
       <c r="AT6">
-        <v>0.485</v>
+        <v>0.44</v>
       </c>
       <c r="AU6">
-        <v>0.528</v>
+        <v>0.466</v>
       </c>
       <c r="AV6">
-        <v>0.505</v>
+        <v>0.44</v>
       </c>
       <c r="AW6">
-        <v>0.142</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="7" spans="1:49">
       <c r="A7">
-        <v>824849</v>
+        <v>823633</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -1514,97 +1514,97 @@
         <v>62</v>
       </c>
       <c r="F7">
-        <v>4.816</v>
+        <v>4.414</v>
       </c>
       <c r="G7">
-        <v>0.476</v>
+        <v>0.456</v>
       </c>
       <c r="H7">
-        <v>0.094</v>
+        <v>0.09</v>
       </c>
       <c r="I7">
-        <v>0.266</v>
+        <v>0.252</v>
       </c>
       <c r="J7">
-        <v>0.104</v>
+        <v>0.114</v>
       </c>
       <c r="K7">
-        <v>0.258</v>
+        <v>0.251</v>
       </c>
       <c r="L7">
-        <v>0.987</v>
+        <v>0.863</v>
       </c>
       <c r="M7">
-        <v>0.08</v>
+        <v>0.119</v>
       </c>
       <c r="N7">
-        <v>1.831</v>
+        <v>1.572</v>
       </c>
       <c r="O7">
-        <v>6.109</v>
+        <v>5.898</v>
       </c>
       <c r="P7">
-        <v>3.606</v>
+        <v>3.911</v>
       </c>
       <c r="Q7">
-        <v>8.681</v>
+        <v>9.132</v>
       </c>
       <c r="R7">
-        <v>0.386</v>
+        <v>0.431</v>
       </c>
       <c r="S7">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="T7">
-        <v>0.179</v>
+        <v>0.154</v>
       </c>
       <c r="U7">
-        <v>0.064</v>
+        <v>0.049</v>
       </c>
       <c r="V7">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="W7">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="X7">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="Y7">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="Z7">
+        <v>0.139</v>
+      </c>
+      <c r="AA7">
+        <v>0.15</v>
+      </c>
+      <c r="AB7">
+        <v>0.136</v>
+      </c>
+      <c r="AC7">
         <v>0.105</v>
       </c>
-      <c r="AA7">
-        <v>0.133</v>
-      </c>
-      <c r="AB7">
-        <v>0.14</v>
-      </c>
-      <c r="AC7">
-        <v>0.118</v>
-      </c>
       <c r="AD7">
-        <v>0.103</v>
+        <v>0.087</v>
       </c>
       <c r="AE7">
-        <v>0.088</v>
+        <v>0.087</v>
       </c>
       <c r="AF7">
-        <v>0.069</v>
+        <v>0.052</v>
       </c>
       <c r="AG7">
-        <v>0.043</v>
+        <v>0.032</v>
       </c>
       <c r="AH7">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="AI7">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="AJ7">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="AK7">
         <v>0.005</v>
@@ -1613,42 +1613,42 @@
         <v>0.004</v>
       </c>
       <c r="AM7">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AN7">
-        <v>0.619</v>
+        <v>0.565</v>
       </c>
       <c r="AO7">
-        <v>0.472</v>
+        <v>0.547</v>
       </c>
       <c r="AP7">
-        <v>0.571</v>
+        <v>0.568</v>
       </c>
       <c r="AQ7">
-        <v>0.499</v>
+        <v>0.504</v>
       </c>
       <c r="AR7">
-        <v>0.505</v>
+        <v>0.468</v>
       </c>
       <c r="AS7">
-        <v>0.463</v>
+        <v>0.42</v>
       </c>
       <c r="AT7">
-        <v>0.453</v>
+        <v>0.376</v>
       </c>
       <c r="AU7">
-        <v>0.482</v>
+        <v>0.353</v>
       </c>
       <c r="AV7">
-        <v>0.456</v>
+        <v>0.362</v>
       </c>
       <c r="AW7">
-        <v>0.144</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="8" spans="1:49">
       <c r="A8">
-        <v>825017</v>
+        <v>823717</v>
       </c>
       <c r="B8" t="s">
         <v>49</v>
@@ -1663,141 +1663,141 @@
         <v>64</v>
       </c>
       <c r="F8">
-        <v>4.904</v>
+        <v>4.594</v>
       </c>
       <c r="G8">
-        <v>0.502</v>
+        <v>0.518</v>
       </c>
       <c r="H8">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="I8">
-        <v>0.282</v>
+        <v>0.28</v>
       </c>
       <c r="J8">
-        <v>0.103</v>
+        <v>0.093</v>
       </c>
       <c r="K8">
-        <v>0.227</v>
+        <v>0.225</v>
       </c>
       <c r="L8">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="M8">
-        <v>0.186</v>
+        <v>0.084</v>
       </c>
       <c r="N8">
-        <v>1.886</v>
+        <v>1.783</v>
       </c>
       <c r="O8">
-        <v>5.268</v>
+        <v>4.877</v>
       </c>
       <c r="P8">
-        <v>2.868</v>
+        <v>4.283</v>
       </c>
       <c r="Q8">
-        <v>6.884</v>
+        <v>9.74</v>
       </c>
       <c r="R8">
-        <v>0.242</v>
+        <v>0.33</v>
       </c>
       <c r="S8">
-        <v>0.346</v>
+        <v>0.37</v>
       </c>
       <c r="T8">
-        <v>0.248</v>
+        <v>0.197</v>
       </c>
       <c r="U8">
-        <v>0.106</v>
+        <v>0.073</v>
       </c>
       <c r="V8">
-        <v>0.041</v>
+        <v>0.021</v>
       </c>
       <c r="W8">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="X8">
-        <v>0.04</v>
+        <v>0.053</v>
       </c>
       <c r="Y8">
-        <v>0.088</v>
+        <v>0.101</v>
       </c>
       <c r="Z8">
-        <v>0.109</v>
+        <v>0.124</v>
       </c>
       <c r="AA8">
-        <v>0.13</v>
+        <v>0.139</v>
       </c>
       <c r="AB8">
-        <v>0.147</v>
+        <v>0.129</v>
       </c>
       <c r="AC8">
-        <v>0.114</v>
+        <v>0.115</v>
       </c>
       <c r="AD8">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="AE8">
-        <v>0.078</v>
+        <v>0.07</v>
       </c>
       <c r="AF8">
-        <v>0.063</v>
+        <v>0.054</v>
       </c>
       <c r="AG8">
         <v>0.042</v>
       </c>
       <c r="AH8">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="AI8">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="AJ8">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="AK8">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="AL8">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="AM8">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AN8">
-        <v>0.552</v>
+        <v>0.555</v>
       </c>
       <c r="AO8">
-        <v>0.454</v>
+        <v>0.42</v>
       </c>
       <c r="AP8">
-        <v>0.524</v>
+        <v>0.511</v>
       </c>
       <c r="AQ8">
-        <v>0.5</v>
+        <v>0.463</v>
       </c>
       <c r="AR8">
-        <v>0.474</v>
+        <v>0.469</v>
       </c>
       <c r="AS8">
-        <v>0.531</v>
+        <v>0.508</v>
       </c>
       <c r="AT8">
-        <v>0.523</v>
+        <v>0.456</v>
       </c>
       <c r="AU8">
-        <v>0.543</v>
+        <v>0.471</v>
       </c>
       <c r="AV8">
-        <v>0.581</v>
+        <v>0.478</v>
       </c>
       <c r="AW8">
-        <v>0.125</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="9" spans="1:49">
       <c r="A9">
-        <v>822823</v>
+        <v>823796</v>
       </c>
       <c r="B9" t="s">
         <v>49</v>
@@ -1812,141 +1812,141 @@
         <v>66</v>
       </c>
       <c r="F9">
-        <v>3.636</v>
+        <v>4.638</v>
       </c>
       <c r="G9">
-        <v>0.421</v>
+        <v>0.438</v>
       </c>
       <c r="H9">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="I9">
-        <v>0.199</v>
+        <v>0.235</v>
       </c>
       <c r="J9">
-        <v>0.117</v>
+        <v>0.107</v>
       </c>
       <c r="K9">
-        <v>0.284</v>
+        <v>0.275</v>
       </c>
       <c r="L9">
-        <v>1.049</v>
+        <v>1.019</v>
       </c>
       <c r="M9">
-        <v>0.115</v>
+        <v>0.172</v>
       </c>
       <c r="N9">
-        <v>1.351</v>
+        <v>1.459</v>
       </c>
       <c r="O9">
-        <v>4.659</v>
+        <v>5.831</v>
       </c>
       <c r="P9">
-        <v>2.962</v>
+        <v>4.005</v>
       </c>
       <c r="Q9">
-        <v>11.359</v>
+        <v>8.105</v>
       </c>
       <c r="R9">
-        <v>0.359</v>
+        <v>0.374</v>
       </c>
       <c r="S9">
-        <v>0.353</v>
+        <v>0.347</v>
       </c>
       <c r="T9">
-        <v>0.197</v>
+        <v>0.193</v>
       </c>
       <c r="U9">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="V9">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="W9">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="X9">
-        <v>0.097</v>
+        <v>0.052</v>
       </c>
       <c r="Y9">
-        <v>0.139</v>
+        <v>0.096</v>
       </c>
       <c r="Z9">
-        <v>0.167</v>
+        <v>0.13</v>
       </c>
       <c r="AA9">
-        <v>0.144</v>
+        <v>0.14</v>
       </c>
       <c r="AB9">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
       <c r="AC9">
-        <v>0.102</v>
+        <v>0.12</v>
       </c>
       <c r="AD9">
-        <v>0.076</v>
+        <v>0.088</v>
       </c>
       <c r="AE9">
-        <v>0.055</v>
+        <v>0.08</v>
       </c>
       <c r="AF9">
+        <v>0.059</v>
+      </c>
+      <c r="AG9">
         <v>0.04</v>
       </c>
-      <c r="AG9">
-        <v>0.019</v>
-      </c>
       <c r="AH9">
-        <v>0.014</v>
+        <v>0.023</v>
       </c>
       <c r="AI9">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="AJ9">
+        <v>0.011</v>
+      </c>
+      <c r="AK9">
+        <v>0.009</v>
+      </c>
+      <c r="AL9">
         <v>0.005</v>
       </c>
-      <c r="AK9">
-        <v>0.003</v>
-      </c>
-      <c r="AL9">
-        <v>0.001</v>
-      </c>
       <c r="AM9">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="AN9">
-        <v>0.378</v>
+        <v>0.567</v>
       </c>
       <c r="AO9">
-        <v>0.336</v>
+        <v>0.505</v>
       </c>
       <c r="AP9">
-        <v>0.356</v>
+        <v>0.518</v>
       </c>
       <c r="AQ9">
-        <v>0.352</v>
+        <v>0.53</v>
       </c>
       <c r="AR9">
-        <v>0.351</v>
+        <v>0.53</v>
       </c>
       <c r="AS9">
-        <v>0.4</v>
+        <v>0.492</v>
       </c>
       <c r="AT9">
-        <v>0.432</v>
+        <v>0.403</v>
       </c>
       <c r="AU9">
-        <v>0.415</v>
+        <v>0.454</v>
       </c>
       <c r="AV9">
-        <v>0.419</v>
+        <v>0.406</v>
       </c>
       <c r="AW9">
-        <v>0.127</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="10" spans="1:49">
       <c r="A10">
-        <v>822908</v>
+        <v>823958</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -1961,141 +1961,141 @@
         <v>68</v>
       </c>
       <c r="F10">
-        <v>4.186</v>
+        <v>3.455</v>
       </c>
       <c r="G10">
-        <v>0.534</v>
+        <v>0.351</v>
       </c>
       <c r="H10">
-        <v>0.108</v>
+        <v>0.071</v>
       </c>
       <c r="I10">
-        <v>0.295</v>
+        <v>0.167</v>
       </c>
       <c r="J10">
+        <v>0.123</v>
+      </c>
+      <c r="K10">
+        <v>0.346</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
         <v>0.098</v>
       </c>
-      <c r="K10">
-        <v>0.185</v>
-      </c>
-      <c r="L10">
-        <v>1.333</v>
-      </c>
-      <c r="M10">
-        <v>0.092</v>
-      </c>
       <c r="N10">
-        <v>1.291</v>
+        <v>1.311</v>
       </c>
       <c r="O10">
-        <v>4.304</v>
+        <v>4.383</v>
       </c>
       <c r="P10">
-        <v>3.528</v>
+        <v>2.797</v>
       </c>
       <c r="Q10">
-        <v>10.594</v>
+        <v>10.897</v>
       </c>
       <c r="R10">
-        <v>0.281</v>
+        <v>0.38</v>
       </c>
       <c r="S10">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="T10">
-        <v>0.224</v>
+        <v>0.189</v>
       </c>
       <c r="U10">
-        <v>0.105</v>
+        <v>0.061</v>
       </c>
       <c r="V10">
-        <v>0.036</v>
+        <v>0.023</v>
       </c>
       <c r="W10">
+        <v>0.002</v>
+      </c>
+      <c r="X10">
+        <v>0.104</v>
+      </c>
+      <c r="Y10">
+        <v>0.154</v>
+      </c>
+      <c r="Z10">
+        <v>0.172</v>
+      </c>
+      <c r="AA10">
+        <v>0.15</v>
+      </c>
+      <c r="AB10">
+        <v>0.12</v>
+      </c>
+      <c r="AC10">
+        <v>0.099</v>
+      </c>
+      <c r="AD10">
+        <v>0.073</v>
+      </c>
+      <c r="AE10">
+        <v>0.048</v>
+      </c>
+      <c r="AF10">
+        <v>0.033</v>
+      </c>
+      <c r="AG10">
         <v>0.017</v>
       </c>
-      <c r="X10">
-        <v>0.067</v>
-      </c>
-      <c r="Y10">
-        <v>0.118</v>
-      </c>
-      <c r="Z10">
-        <v>0.149</v>
-      </c>
-      <c r="AA10">
-        <v>0.141</v>
-      </c>
-      <c r="AB10">
-        <v>0.126</v>
-      </c>
-      <c r="AC10">
-        <v>0.107</v>
-      </c>
-      <c r="AD10">
-        <v>0.088</v>
-      </c>
-      <c r="AE10">
-        <v>0.065</v>
-      </c>
-      <c r="AF10">
-        <v>0.05</v>
-      </c>
-      <c r="AG10">
-        <v>0.038</v>
-      </c>
       <c r="AH10">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="AI10">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="AJ10">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AK10">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AL10">
         <v>0.002</v>
       </c>
       <c r="AM10">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AN10">
-        <v>0.419</v>
+        <v>0.358</v>
       </c>
       <c r="AO10">
-        <v>0.334</v>
+        <v>0.282</v>
       </c>
       <c r="AP10">
-        <v>0.39</v>
+        <v>0.347</v>
       </c>
       <c r="AQ10">
-        <v>0.396</v>
+        <v>0.345</v>
       </c>
       <c r="AR10">
-        <v>0.409</v>
+        <v>0.329</v>
       </c>
       <c r="AS10">
-        <v>0.475</v>
+        <v>0.353</v>
       </c>
       <c r="AT10">
-        <v>0.468</v>
+        <v>0.393</v>
       </c>
       <c r="AU10">
-        <v>0.499</v>
+        <v>0.38</v>
       </c>
       <c r="AV10">
-        <v>0.543</v>
+        <v>0.446</v>
       </c>
       <c r="AW10">
-        <v>0.171</v>
+        <v>0.148</v>
       </c>
     </row>
     <row r="11" spans="1:49">
       <c r="A11">
-        <v>823310</v>
+        <v>824445</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -2110,141 +2110,141 @@
         <v>70</v>
       </c>
       <c r="F11">
-        <v>4.549</v>
+        <v>3.46</v>
       </c>
       <c r="G11">
-        <v>0.466</v>
+        <v>0.489</v>
       </c>
       <c r="H11">
-        <v>0.094</v>
+        <v>0.105</v>
       </c>
       <c r="I11">
-        <v>0.25</v>
+        <v>0.243</v>
       </c>
       <c r="J11">
-        <v>0.097</v>
+        <v>0.101</v>
       </c>
       <c r="K11">
-        <v>0.269</v>
+        <v>0.202</v>
       </c>
       <c r="L11">
-        <v>0.962</v>
+        <v>0.779</v>
       </c>
       <c r="M11">
-        <v>0.124</v>
+        <v>0.086</v>
       </c>
       <c r="N11">
-        <v>1.614</v>
+        <v>1.305</v>
       </c>
       <c r="O11">
-        <v>5.231</v>
+        <v>4.105</v>
       </c>
       <c r="P11">
-        <v>4.4</v>
+        <v>4.207</v>
       </c>
       <c r="Q11">
-        <v>7.84</v>
+        <v>9.665</v>
       </c>
       <c r="R11">
-        <v>0.388</v>
+        <v>0.458</v>
       </c>
       <c r="S11">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="T11">
-        <v>0.185</v>
+        <v>0.14</v>
       </c>
       <c r="U11">
-        <v>0.051</v>
+        <v>0.038</v>
       </c>
       <c r="V11">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="W11">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="X11">
-        <v>0.058</v>
+        <v>0.105</v>
       </c>
       <c r="Y11">
-        <v>0.097</v>
+        <v>0.151</v>
       </c>
       <c r="Z11">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="AA11">
-        <v>0.139</v>
+        <v>0.17</v>
       </c>
       <c r="AB11">
-        <v>0.136</v>
+        <v>0.127</v>
       </c>
       <c r="AC11">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AD11">
-        <v>0.099</v>
+        <v>0.069</v>
       </c>
       <c r="AE11">
-        <v>0.073</v>
+        <v>0.04</v>
       </c>
       <c r="AF11">
-        <v>0.057</v>
+        <v>0.031</v>
       </c>
       <c r="AG11">
-        <v>0.036</v>
+        <v>0.019</v>
       </c>
       <c r="AH11">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="AI11">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="AJ11">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="AK11">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="AL11">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AM11">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AN11">
-        <v>0.533</v>
+        <v>0.378</v>
       </c>
       <c r="AO11">
-        <v>0.466</v>
+        <v>0.345</v>
       </c>
       <c r="AP11">
-        <v>0.538</v>
+        <v>0.326</v>
       </c>
       <c r="AQ11">
-        <v>0.497</v>
+        <v>0.345</v>
       </c>
       <c r="AR11">
-        <v>0.495</v>
+        <v>0.329</v>
       </c>
       <c r="AS11">
-        <v>0.494</v>
+        <v>0.362</v>
       </c>
       <c r="AT11">
-        <v>0.443</v>
+        <v>0.393</v>
       </c>
       <c r="AU11">
-        <v>0.426</v>
+        <v>0.384</v>
       </c>
       <c r="AV11">
-        <v>0.425</v>
+        <v>0.365</v>
       </c>
       <c r="AW11">
-        <v>0.109</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="12" spans="1:49">
       <c r="A12">
-        <v>823390</v>
+        <v>824525</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -2259,141 +2259,141 @@
         <v>72</v>
       </c>
       <c r="F12">
-        <v>3.735</v>
+        <v>4.745</v>
       </c>
       <c r="G12">
-        <v>0.344</v>
+        <v>0.425</v>
       </c>
       <c r="H12">
-        <v>0.075</v>
+        <v>0.087</v>
       </c>
       <c r="I12">
-        <v>0.168</v>
+        <v>0.233</v>
       </c>
       <c r="J12">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="K12">
-        <v>0.339</v>
+        <v>0.297</v>
       </c>
       <c r="L12">
-        <v>0.78</v>
+        <v>1.221</v>
       </c>
       <c r="M12">
-        <v>0.049</v>
+        <v>0.147</v>
       </c>
       <c r="N12">
-        <v>1.638</v>
+        <v>1.713</v>
       </c>
       <c r="O12">
-        <v>4.54</v>
+        <v>5.378</v>
       </c>
       <c r="P12">
-        <v>3.863</v>
+        <v>3.609</v>
       </c>
       <c r="Q12">
-        <v>9.24</v>
+        <v>8.503</v>
       </c>
       <c r="R12">
-        <v>0.465</v>
+        <v>0.305</v>
       </c>
       <c r="S12">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="T12">
-        <v>0.136</v>
+        <v>0.21</v>
       </c>
       <c r="U12">
+        <v>0.094</v>
+      </c>
+      <c r="V12">
+        <v>0.028</v>
+      </c>
+      <c r="W12">
+        <v>0.011</v>
+      </c>
+      <c r="X12">
+        <v>0.045</v>
+      </c>
+      <c r="Y12">
+        <v>0.089</v>
+      </c>
+      <c r="Z12">
+        <v>0.118</v>
+      </c>
+      <c r="AA12">
+        <v>0.145</v>
+      </c>
+      <c r="AB12">
+        <v>0.128</v>
+      </c>
+      <c r="AC12">
+        <v>0.117</v>
+      </c>
+      <c r="AD12">
+        <v>0.096</v>
+      </c>
+      <c r="AE12">
+        <v>0.088</v>
+      </c>
+      <c r="AF12">
+        <v>0.058</v>
+      </c>
+      <c r="AG12">
         <v>0.04</v>
       </c>
-      <c r="V12">
+      <c r="AH12">
+        <v>0.03</v>
+      </c>
+      <c r="AI12">
+        <v>0.02</v>
+      </c>
+      <c r="AJ12">
+        <v>0.012</v>
+      </c>
+      <c r="AK12">
         <v>0.007</v>
       </c>
-      <c r="W12">
-        <v>0.002</v>
-      </c>
-      <c r="X12">
-        <v>0.11</v>
-      </c>
-      <c r="Y12">
-        <v>0.137</v>
-      </c>
-      <c r="Z12">
-        <v>0.143</v>
-      </c>
-      <c r="AA12">
-        <v>0.14</v>
-      </c>
-      <c r="AB12">
-        <v>0.131</v>
-      </c>
-      <c r="AC12">
-        <v>0.106</v>
-      </c>
-      <c r="AD12">
-        <v>0.076</v>
-      </c>
-      <c r="AE12">
-        <v>0.051</v>
-      </c>
-      <c r="AF12">
-        <v>0.041</v>
-      </c>
-      <c r="AG12">
-        <v>0.02</v>
-      </c>
-      <c r="AH12">
-        <v>0.015</v>
-      </c>
-      <c r="AI12">
-        <v>0.01</v>
-      </c>
-      <c r="AJ12">
-        <v>0.01</v>
-      </c>
-      <c r="AK12">
-        <v>0.005</v>
-      </c>
       <c r="AL12">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="AM12">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="AN12">
-        <v>0.392</v>
+        <v>0.51</v>
       </c>
       <c r="AO12">
-        <v>0.297</v>
+        <v>0.56</v>
       </c>
       <c r="AP12">
-        <v>0.339</v>
+        <v>0.554</v>
       </c>
       <c r="AQ12">
-        <v>0.338</v>
+        <v>0.494</v>
       </c>
       <c r="AR12">
-        <v>0.37</v>
+        <v>0.497</v>
       </c>
       <c r="AS12">
-        <v>0.407</v>
+        <v>0.463</v>
       </c>
       <c r="AT12">
-        <v>0.463</v>
+        <v>0.489</v>
       </c>
       <c r="AU12">
-        <v>0.448</v>
+        <v>0.48</v>
       </c>
       <c r="AV12">
-        <v>0.457</v>
+        <v>0.475</v>
       </c>
       <c r="AW12">
-        <v>0.122</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="13" spans="1:49">
       <c r="A13">
-        <v>823636</v>
+        <v>824608</v>
       </c>
       <c r="B13" t="s">
         <v>49</v>
@@ -2408,141 +2408,141 @@
         <v>74</v>
       </c>
       <c r="F13">
-        <v>3.892</v>
+        <v>5.203</v>
       </c>
       <c r="G13">
-        <v>0.393</v>
+        <v>0.551</v>
       </c>
       <c r="H13">
-        <v>0.082</v>
+        <v>0.088</v>
       </c>
       <c r="I13">
-        <v>0.194</v>
+        <v>0.34</v>
       </c>
       <c r="J13">
-        <v>0.132</v>
+        <v>0.091</v>
       </c>
       <c r="K13">
-        <v>0.294</v>
+        <v>0.2</v>
       </c>
       <c r="L13">
-        <v>0.777</v>
+        <v>1.266</v>
       </c>
       <c r="M13">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="N13">
-        <v>1.242</v>
+        <v>1.543</v>
       </c>
       <c r="O13">
-        <v>5.555</v>
+        <v>5.529</v>
       </c>
       <c r="P13">
-        <v>3.686</v>
+        <v>4.745</v>
       </c>
       <c r="Q13">
-        <v>7.297</v>
+        <v>7.746</v>
       </c>
       <c r="R13">
-        <v>0.466</v>
+        <v>0.289</v>
       </c>
       <c r="S13">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="T13">
-        <v>0.138</v>
+        <v>0.22</v>
       </c>
       <c r="U13">
-        <v>0.035</v>
+        <v>0.096</v>
       </c>
       <c r="V13">
+        <v>0.031</v>
+      </c>
+      <c r="W13">
+        <v>0.011</v>
+      </c>
+      <c r="X13">
+        <v>0.036</v>
+      </c>
+      <c r="Y13">
+        <v>0.075</v>
+      </c>
+      <c r="Z13">
+        <v>0.112</v>
+      </c>
+      <c r="AA13">
+        <v>0.122</v>
+      </c>
+      <c r="AB13">
+        <v>0.119</v>
+      </c>
+      <c r="AC13">
+        <v>0.128</v>
+      </c>
+      <c r="AD13">
+        <v>0.102</v>
+      </c>
+      <c r="AE13">
+        <v>0.083</v>
+      </c>
+      <c r="AF13">
+        <v>0.069</v>
+      </c>
+      <c r="AG13">
+        <v>0.047</v>
+      </c>
+      <c r="AH13">
+        <v>0.038</v>
+      </c>
+      <c r="AI13">
+        <v>0.027</v>
+      </c>
+      <c r="AJ13">
         <v>0.01</v>
       </c>
-      <c r="W13">
-        <v>0.001</v>
-      </c>
-      <c r="X13">
-        <v>0.083</v>
-      </c>
-      <c r="Y13">
-        <v>0.12</v>
-      </c>
-      <c r="Z13">
-        <v>0.154</v>
-      </c>
-      <c r="AA13">
-        <v>0.144</v>
-      </c>
-      <c r="AB13">
-        <v>0.134</v>
-      </c>
-      <c r="AC13">
-        <v>0.11</v>
-      </c>
-      <c r="AD13">
-        <v>0.093</v>
-      </c>
-      <c r="AE13">
-        <v>0.059</v>
-      </c>
-      <c r="AF13">
-        <v>0.043</v>
-      </c>
-      <c r="AG13">
-        <v>0.025</v>
-      </c>
-      <c r="AH13">
-        <v>0.013</v>
-      </c>
-      <c r="AI13">
+      <c r="AK13">
+        <v>0.014</v>
+      </c>
+      <c r="AL13">
+        <v>0.009</v>
+      </c>
+      <c r="AM13">
         <v>0.008</v>
       </c>
-      <c r="AJ13">
-        <v>0.007</v>
-      </c>
-      <c r="AK13">
-        <v>0.003</v>
-      </c>
-      <c r="AL13">
-        <v>0.002</v>
-      </c>
-      <c r="AM13">
-        <v>0.002</v>
-      </c>
       <c r="AN13">
-        <v>0.419</v>
+        <v>0.606</v>
       </c>
       <c r="AO13">
-        <v>0.375</v>
+        <v>0.515</v>
       </c>
       <c r="AP13">
-        <v>0.417</v>
+        <v>0.581</v>
       </c>
       <c r="AQ13">
-        <v>0.435</v>
+        <v>0.535</v>
       </c>
       <c r="AR13">
-        <v>0.426</v>
+        <v>0.554</v>
       </c>
       <c r="AS13">
-        <v>0.396</v>
+        <v>0.523</v>
       </c>
       <c r="AT13">
-        <v>0.389</v>
+        <v>0.563</v>
       </c>
       <c r="AU13">
-        <v>0.408</v>
+        <v>0.531</v>
       </c>
       <c r="AV13">
-        <v>0.396</v>
+        <v>0.542</v>
       </c>
       <c r="AW13">
-        <v>0.121</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="14" spans="1:49">
       <c r="A14">
-        <v>823716</v>
+        <v>824850</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
@@ -2557,141 +2557,141 @@
         <v>76</v>
       </c>
       <c r="F14">
-        <v>4.416</v>
+        <v>5.159</v>
       </c>
       <c r="G14">
-        <v>0.484</v>
+        <v>0.47</v>
       </c>
       <c r="H14">
-        <v>0.107</v>
+        <v>0.099</v>
       </c>
       <c r="I14">
-        <v>0.262</v>
+        <v>0.259</v>
       </c>
       <c r="J14">
+        <v>0.101</v>
+      </c>
+      <c r="K14">
+        <v>0.266</v>
+      </c>
+      <c r="L14">
+        <v>1.087</v>
+      </c>
+      <c r="M14">
+        <v>0.079</v>
+      </c>
+      <c r="N14">
+        <v>1.934</v>
+      </c>
+      <c r="O14">
+        <v>6.075</v>
+      </c>
+      <c r="P14">
+        <v>3.826</v>
+      </c>
+      <c r="Q14">
+        <v>7.246</v>
+      </c>
+      <c r="R14">
+        <v>0.342</v>
+      </c>
+      <c r="S14">
+        <v>0.36</v>
+      </c>
+      <c r="T14">
+        <v>0.199</v>
+      </c>
+      <c r="U14">
+        <v>0.073</v>
+      </c>
+      <c r="V14">
+        <v>0.023</v>
+      </c>
+      <c r="W14">
+        <v>0.004</v>
+      </c>
+      <c r="X14">
+        <v>0.041</v>
+      </c>
+      <c r="Y14">
+        <v>0.076</v>
+      </c>
+      <c r="Z14">
         <v>0.098</v>
       </c>
-      <c r="K14">
-        <v>0.237</v>
-      </c>
-      <c r="L14">
-        <v>1.242</v>
-      </c>
-      <c r="M14">
-        <v>0.103</v>
-      </c>
-      <c r="N14">
-        <v>1.93</v>
-      </c>
-      <c r="O14">
-        <v>4.541</v>
-      </c>
-      <c r="P14">
-        <v>3.406</v>
-      </c>
-      <c r="Q14">
-        <v>9.511</v>
-      </c>
-      <c r="R14">
-        <v>0.297</v>
-      </c>
-      <c r="S14">
-        <v>0.353</v>
-      </c>
-      <c r="T14">
-        <v>0.218</v>
-      </c>
-      <c r="U14">
-        <v>0.088</v>
-      </c>
-      <c r="V14">
-        <v>0.033</v>
-      </c>
-      <c r="W14">
+      <c r="AA14">
+        <v>0.118</v>
+      </c>
+      <c r="AB14">
+        <v>0.137</v>
+      </c>
+      <c r="AC14">
+        <v>0.12</v>
+      </c>
+      <c r="AD14">
+        <v>0.105</v>
+      </c>
+      <c r="AE14">
+        <v>0.091</v>
+      </c>
+      <c r="AF14">
+        <v>0.061</v>
+      </c>
+      <c r="AG14">
+        <v>0.051</v>
+      </c>
+      <c r="AH14">
+        <v>0.038</v>
+      </c>
+      <c r="AI14">
+        <v>0.025</v>
+      </c>
+      <c r="AJ14">
         <v>0.011</v>
       </c>
-      <c r="X14">
-        <v>0.054</v>
-      </c>
-      <c r="Y14">
-        <v>0.107</v>
-      </c>
-      <c r="Z14">
-        <v>0.137</v>
-      </c>
-      <c r="AA14">
-        <v>0.143</v>
-      </c>
-      <c r="AB14">
-        <v>0.133</v>
-      </c>
-      <c r="AC14">
-        <v>0.119</v>
-      </c>
-      <c r="AD14">
-        <v>0.084</v>
-      </c>
-      <c r="AE14">
-        <v>0.071</v>
-      </c>
-      <c r="AF14">
-        <v>0.048</v>
-      </c>
-      <c r="AG14">
-        <v>0.039</v>
-      </c>
-      <c r="AH14">
-        <v>0.027</v>
-      </c>
-      <c r="AI14">
-        <v>0.014</v>
-      </c>
-      <c r="AJ14">
-        <v>0.006</v>
-      </c>
       <c r="AK14">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="AL14">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="AM14">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="AN14">
-        <v>0.457</v>
+        <v>0.719</v>
       </c>
       <c r="AO14">
-        <v>0.426</v>
+        <v>0.565</v>
       </c>
       <c r="AP14">
-        <v>0.46</v>
+        <v>0.634</v>
       </c>
       <c r="AQ14">
-        <v>0.426</v>
+        <v>0.607</v>
       </c>
       <c r="AR14">
-        <v>0.445</v>
+        <v>0.534</v>
       </c>
       <c r="AS14">
-        <v>0.476</v>
+        <v>0.454</v>
       </c>
       <c r="AT14">
-        <v>0.471</v>
+        <v>0.481</v>
       </c>
       <c r="AU14">
-        <v>0.513</v>
+        <v>0.437</v>
       </c>
       <c r="AV14">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AW14">
-        <v>0.148</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="15" spans="1:49">
       <c r="A15">
-        <v>824610</v>
+        <v>824930</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
@@ -2706,141 +2706,141 @@
         <v>78</v>
       </c>
       <c r="F15">
-        <v>5.236</v>
+        <v>5.713</v>
       </c>
       <c r="G15">
-        <v>0.616</v>
+        <v>0.607</v>
       </c>
       <c r="H15">
-        <v>0.105</v>
+        <v>0.101</v>
       </c>
       <c r="I15">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="J15">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="K15">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
       <c r="L15">
-        <v>1.318</v>
+        <v>1.376</v>
       </c>
       <c r="M15">
-        <v>0.113</v>
+        <v>0.181</v>
       </c>
       <c r="N15">
-        <v>1.662</v>
+        <v>1.867</v>
       </c>
       <c r="O15">
-        <v>5.837</v>
+        <v>5.898</v>
       </c>
       <c r="P15">
-        <v>4.052</v>
+        <v>4.324</v>
       </c>
       <c r="Q15">
-        <v>9.084</v>
+        <v>8.808</v>
       </c>
       <c r="R15">
-        <v>0.275</v>
+        <v>0.261</v>
       </c>
       <c r="S15">
-        <v>0.341</v>
+        <v>0.35</v>
       </c>
       <c r="T15">
-        <v>0.238</v>
+        <v>0.223</v>
       </c>
       <c r="U15">
-        <v>0.1</v>
+        <v>0.109</v>
       </c>
       <c r="V15">
+        <v>0.042</v>
+      </c>
+      <c r="W15">
+        <v>0.016</v>
+      </c>
+      <c r="X15">
         <v>0.033</v>
       </c>
-      <c r="W15">
-        <v>0.013</v>
-      </c>
-      <c r="X15">
-        <v>0.038</v>
-      </c>
       <c r="Y15">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="Z15">
-        <v>0.104</v>
+        <v>0.089</v>
       </c>
       <c r="AA15">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
       <c r="AB15">
-        <v>0.122</v>
+        <v>0.115</v>
       </c>
       <c r="AC15">
         <v>0.129</v>
       </c>
       <c r="AD15">
-        <v>0.123</v>
+        <v>0.103</v>
       </c>
       <c r="AE15">
-        <v>0.094</v>
+        <v>0.082</v>
       </c>
       <c r="AF15">
-        <v>0.063</v>
+        <v>0.074</v>
       </c>
       <c r="AG15">
+        <v>0.056</v>
+      </c>
+      <c r="AH15">
         <v>0.047</v>
       </c>
-      <c r="AH15">
-        <v>0.034</v>
-      </c>
       <c r="AI15">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="AJ15">
-        <v>0.015</v>
+        <v>0.028</v>
       </c>
       <c r="AK15">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="AL15">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="AM15">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="AN15">
+        <v>0.708</v>
+      </c>
+      <c r="AO15">
+        <v>0.576</v>
+      </c>
+      <c r="AP15">
+        <v>0.616</v>
+      </c>
+      <c r="AQ15">
+        <v>0.615</v>
+      </c>
+      <c r="AR15">
         <v>0.633</v>
       </c>
-      <c r="AO15">
-        <v>0.539</v>
-      </c>
-      <c r="AP15">
-        <v>0.579</v>
-      </c>
-      <c r="AQ15">
-        <v>0.565</v>
-      </c>
-      <c r="AR15">
-        <v>0.544</v>
-      </c>
       <c r="AS15">
-        <v>0.522</v>
+        <v>0.591</v>
       </c>
       <c r="AT15">
-        <v>0.512</v>
+        <v>0.547</v>
       </c>
       <c r="AU15">
-        <v>0.525</v>
+        <v>0.574</v>
       </c>
       <c r="AV15">
-        <v>0.56</v>
+        <v>0.567</v>
       </c>
       <c r="AW15">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="16" spans="1:49">
       <c r="A16">
-        <v>824931</v>
+        <v>825015</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
@@ -2855,141 +2855,141 @@
         <v>80</v>
       </c>
       <c r="F16">
-        <v>5.05</v>
+        <v>5.826</v>
       </c>
       <c r="G16">
-        <v>0.509</v>
+        <v>0.474</v>
       </c>
       <c r="H16">
-        <v>0.097</v>
+        <v>0.085</v>
       </c>
       <c r="I16">
         <v>0.287</v>
       </c>
       <c r="J16">
-        <v>0.084</v>
+        <v>0.098</v>
       </c>
       <c r="K16">
-        <v>0.232</v>
+        <v>0.264</v>
       </c>
       <c r="L16">
-        <v>1.198</v>
+        <v>1.377</v>
       </c>
       <c r="M16">
-        <v>0.12</v>
+        <v>0.214</v>
       </c>
       <c r="N16">
-        <v>1.647</v>
+        <v>2.031</v>
       </c>
       <c r="O16">
-        <v>5.571</v>
+        <v>5.698</v>
       </c>
       <c r="P16">
-        <v>4.147</v>
+        <v>4.359</v>
       </c>
       <c r="Q16">
-        <v>7.405</v>
+        <v>7.188</v>
       </c>
       <c r="R16">
-        <v>0.295</v>
+        <v>0.272</v>
       </c>
       <c r="S16">
-        <v>0.382</v>
+        <v>0.337</v>
       </c>
       <c r="T16">
-        <v>0.207</v>
+        <v>0.221</v>
       </c>
       <c r="U16">
-        <v>0.078</v>
+        <v>0.107</v>
       </c>
       <c r="V16">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="W16">
+        <v>0.018</v>
+      </c>
+      <c r="X16">
+        <v>0.025</v>
+      </c>
+      <c r="Y16">
+        <v>0.062</v>
+      </c>
+      <c r="Z16">
+        <v>0.094</v>
+      </c>
+      <c r="AA16">
+        <v>0.103</v>
+      </c>
+      <c r="AB16">
+        <v>0.117</v>
+      </c>
+      <c r="AC16">
+        <v>0.106</v>
+      </c>
+      <c r="AD16">
+        <v>0.112</v>
+      </c>
+      <c r="AE16">
+        <v>0.094</v>
+      </c>
+      <c r="AF16">
+        <v>0.083</v>
+      </c>
+      <c r="AG16">
+        <v>0.054</v>
+      </c>
+      <c r="AH16">
+        <v>0.048</v>
+      </c>
+      <c r="AI16">
+        <v>0.035</v>
+      </c>
+      <c r="AJ16">
+        <v>0.024</v>
+      </c>
+      <c r="AK16">
+        <v>0.016</v>
+      </c>
+      <c r="AL16">
         <v>0.01</v>
       </c>
-      <c r="X16">
-        <v>0.036</v>
-      </c>
-      <c r="Y16">
-        <v>0.073</v>
-      </c>
-      <c r="Z16">
-        <v>0.111</v>
-      </c>
-      <c r="AA16">
-        <v>0.136</v>
-      </c>
-      <c r="AB16">
-        <v>0.127</v>
-      </c>
-      <c r="AC16">
-        <v>0.126</v>
-      </c>
-      <c r="AD16">
-        <v>0.104</v>
-      </c>
-      <c r="AE16">
-        <v>0.09</v>
-      </c>
-      <c r="AF16">
-        <v>0.066</v>
-      </c>
-      <c r="AG16">
-        <v>0.042</v>
-      </c>
-      <c r="AH16">
-        <v>0.03</v>
-      </c>
-      <c r="AI16">
-        <v>0.021</v>
-      </c>
-      <c r="AJ16">
+      <c r="AM16">
         <v>0.017</v>
       </c>
-      <c r="AK16">
-        <v>0.007</v>
-      </c>
-      <c r="AL16">
-        <v>0.007</v>
-      </c>
-      <c r="AM16">
-        <v>0.008</v>
-      </c>
       <c r="AN16">
-        <v>0.588</v>
+        <v>0.698</v>
       </c>
       <c r="AO16">
-        <v>0.569</v>
+        <v>0.591</v>
       </c>
       <c r="AP16">
-        <v>0.574</v>
+        <v>0.686</v>
       </c>
       <c r="AQ16">
-        <v>0.553</v>
+        <v>0.647</v>
       </c>
       <c r="AR16">
-        <v>0.533</v>
+        <v>0.646</v>
       </c>
       <c r="AS16">
-        <v>0.487</v>
+        <v>0.621</v>
       </c>
       <c r="AT16">
-        <v>0.475</v>
+        <v>0.568</v>
       </c>
       <c r="AU16">
-        <v>0.509</v>
+        <v>0.549</v>
       </c>
       <c r="AV16">
-        <v>0.501</v>
+        <v>0.561</v>
       </c>
       <c r="AW16">
-        <v>0.147</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="17" spans="1:49">
       <c r="A17">
-        <v>823473</v>
+        <v>822821</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
@@ -3004,141 +3004,141 @@
         <v>51</v>
       </c>
       <c r="F17">
-        <v>5.189</v>
+        <v>5.0</v>
       </c>
       <c r="G17">
-        <v>0.638</v>
+        <v>0.562</v>
       </c>
       <c r="H17">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="I17">
-        <v>0.343</v>
+        <v>0.299</v>
       </c>
       <c r="J17">
-        <v>0.082</v>
+        <v>0.09</v>
       </c>
       <c r="K17">
-        <v>0.175</v>
+        <v>0.232</v>
       </c>
       <c r="L17">
-        <v>1.238</v>
+        <v>1.417</v>
       </c>
       <c r="M17">
-        <v>0.12</v>
+        <v>0.103</v>
       </c>
       <c r="N17">
-        <v>1.512</v>
+        <v>1.574</v>
       </c>
       <c r="O17">
-        <v>6.151</v>
+        <v>5.647</v>
       </c>
       <c r="P17">
-        <v>3.718</v>
+        <v>3.217</v>
       </c>
       <c r="Q17">
-        <v>7.627</v>
+        <v>6.09</v>
       </c>
       <c r="R17">
-        <v>0.289</v>
+        <v>0.235</v>
       </c>
       <c r="S17">
-        <v>0.359</v>
+        <v>0.354</v>
       </c>
       <c r="T17">
-        <v>0.224</v>
+        <v>0.248</v>
       </c>
       <c r="U17">
-        <v>0.09</v>
+        <v>0.107</v>
       </c>
       <c r="V17">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="W17">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="X17">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="Y17">
         <v>0.071</v>
       </c>
       <c r="Z17">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="AA17">
-        <v>0.122</v>
+        <v>0.135</v>
       </c>
       <c r="AB17">
+        <v>0.146</v>
+      </c>
+      <c r="AC17">
         <v>0.132</v>
       </c>
-      <c r="AC17">
-        <v>0.13</v>
-      </c>
       <c r="AD17">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="AE17">
-        <v>0.087</v>
+        <v>0.085</v>
       </c>
       <c r="AF17">
-        <v>0.07</v>
+        <v>0.065</v>
       </c>
       <c r="AG17">
-        <v>0.051</v>
+        <v>0.042</v>
       </c>
       <c r="AH17">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AI17">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="AJ17">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="AK17">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AL17">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AM17">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="AN17">
-        <v>0.653</v>
+        <v>0.735</v>
       </c>
       <c r="AO17">
-        <v>0.574</v>
+        <v>0.604</v>
       </c>
       <c r="AP17">
-        <v>0.596</v>
+        <v>0.683</v>
       </c>
       <c r="AQ17">
-        <v>0.601</v>
+        <v>0.586</v>
       </c>
       <c r="AR17">
-        <v>0.593</v>
+        <v>0.627</v>
       </c>
       <c r="AS17">
-        <v>0.585</v>
+        <v>0.493</v>
       </c>
       <c r="AT17">
-        <v>0.548</v>
+        <v>0.442</v>
       </c>
       <c r="AU17">
-        <v>0.575</v>
+        <v>0.443</v>
       </c>
       <c r="AV17">
-        <v>0.221</v>
+        <v>0.19</v>
       </c>
       <c r="AW17">
-        <v>0.126</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="18" spans="1:49">
       <c r="A18">
-        <v>823798</v>
+        <v>822907</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -3153,141 +3153,141 @@
         <v>53</v>
       </c>
       <c r="F18">
-        <v>5.115</v>
+        <v>5.242</v>
       </c>
       <c r="G18">
-        <v>0.597</v>
+        <v>0.572</v>
       </c>
       <c r="H18">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="I18">
-        <v>0.306</v>
+        <v>0.309</v>
       </c>
       <c r="J18">
-        <v>0.076</v>
+        <v>0.085</v>
       </c>
       <c r="K18">
-        <v>0.223</v>
+        <v>0.238</v>
       </c>
       <c r="L18">
-        <v>1.378</v>
+        <v>1.195</v>
       </c>
       <c r="M18">
-        <v>0.126</v>
+        <v>0.116</v>
       </c>
       <c r="N18">
-        <v>1.641</v>
+        <v>2.012</v>
       </c>
       <c r="O18">
-        <v>5.415</v>
+        <v>5.819</v>
       </c>
       <c r="P18">
-        <v>3.598</v>
+        <v>3.409</v>
       </c>
       <c r="Q18">
-        <v>7.79</v>
+        <v>7.61</v>
       </c>
       <c r="R18">
-        <v>0.25</v>
+        <v>0.303</v>
       </c>
       <c r="S18">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="T18">
-        <v>0.235</v>
+        <v>0.203</v>
       </c>
       <c r="U18">
+        <v>0.088</v>
+      </c>
+      <c r="V18">
+        <v>0.027</v>
+      </c>
+      <c r="W18">
+        <v>0.009</v>
+      </c>
+      <c r="X18">
+        <v>0.036</v>
+      </c>
+      <c r="Y18">
+        <v>0.063</v>
+      </c>
+      <c r="Z18">
+        <v>0.104</v>
+      </c>
+      <c r="AA18">
+        <v>0.116</v>
+      </c>
+      <c r="AB18">
+        <v>0.139</v>
+      </c>
+      <c r="AC18">
+        <v>0.125</v>
+      </c>
+      <c r="AD18">
         <v>0.115</v>
       </c>
-      <c r="V18">
-        <v>0.038</v>
-      </c>
-      <c r="W18">
+      <c r="AE18">
+        <v>0.078</v>
+      </c>
+      <c r="AF18">
+        <v>0.075</v>
+      </c>
+      <c r="AG18">
+        <v>0.053</v>
+      </c>
+      <c r="AH18">
+        <v>0.036</v>
+      </c>
+      <c r="AI18">
+        <v>0.02</v>
+      </c>
+      <c r="AJ18">
+        <v>0.015</v>
+      </c>
+      <c r="AK18">
         <v>0.012</v>
       </c>
-      <c r="X18">
-        <v>0.028</v>
-      </c>
-      <c r="Y18">
-        <v>0.067</v>
-      </c>
-      <c r="Z18">
-        <v>0.095</v>
-      </c>
-      <c r="AA18">
-        <v>0.135</v>
-      </c>
-      <c r="AB18">
-        <v>0.149</v>
-      </c>
-      <c r="AC18">
-        <v>0.122</v>
-      </c>
-      <c r="AD18">
-        <v>0.121</v>
-      </c>
-      <c r="AE18">
-        <v>0.084</v>
-      </c>
-      <c r="AF18">
-        <v>0.068</v>
-      </c>
-      <c r="AG18">
-        <v>0.052</v>
-      </c>
-      <c r="AH18">
-        <v>0.031</v>
-      </c>
-      <c r="AI18">
-        <v>0.019</v>
-      </c>
-      <c r="AJ18">
+      <c r="AL18">
+        <v>0.005</v>
+      </c>
+      <c r="AM18">
         <v>0.009</v>
       </c>
-      <c r="AK18">
-        <v>0.008</v>
-      </c>
-      <c r="AL18">
-        <v>0.004</v>
-      </c>
-      <c r="AM18">
-        <v>0.008</v>
-      </c>
       <c r="AN18">
-        <v>0.705</v>
+        <v>0.669</v>
       </c>
       <c r="AO18">
-        <v>0.53</v>
+        <v>0.645</v>
       </c>
       <c r="AP18">
-        <v>0.605</v>
+        <v>0.625</v>
       </c>
       <c r="AQ18">
-        <v>0.561</v>
+        <v>0.619</v>
       </c>
       <c r="AR18">
-        <v>0.613</v>
+        <v>0.584</v>
       </c>
       <c r="AS18">
-        <v>0.584</v>
+        <v>0.548</v>
       </c>
       <c r="AT18">
-        <v>0.541</v>
+        <v>0.532</v>
       </c>
       <c r="AU18">
-        <v>0.509</v>
+        <v>0.534</v>
       </c>
       <c r="AV18">
-        <v>0.245</v>
+        <v>0.263</v>
       </c>
       <c r="AW18">
-        <v>0.111</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="19" spans="1:49">
       <c r="A19">
-        <v>823956</v>
+        <v>823312</v>
       </c>
       <c r="B19" t="s">
         <v>49</v>
@@ -3302,141 +3302,141 @@
         <v>55</v>
       </c>
       <c r="F19">
-        <v>4.846</v>
+        <v>4.796</v>
       </c>
       <c r="G19">
-        <v>0.717</v>
+        <v>0.474</v>
       </c>
       <c r="H19">
-        <v>0.139</v>
+        <v>0.098</v>
       </c>
       <c r="I19">
-        <v>0.389</v>
+        <v>0.217</v>
       </c>
       <c r="J19">
-        <v>0.07</v>
+        <v>0.095</v>
       </c>
       <c r="K19">
-        <v>0.115</v>
+        <v>0.316</v>
       </c>
       <c r="L19">
-        <v>1.459</v>
+        <v>1.294</v>
       </c>
       <c r="M19">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="N19">
-        <v>1.519</v>
+        <v>1.737</v>
       </c>
       <c r="O19">
-        <v>5.185</v>
+        <v>5.02</v>
       </c>
       <c r="P19">
-        <v>3.063</v>
+        <v>3.463</v>
       </c>
       <c r="Q19">
-        <v>7.113</v>
+        <v>7.547</v>
       </c>
       <c r="R19">
-        <v>0.231</v>
+        <v>0.278</v>
       </c>
       <c r="S19">
-        <v>0.333</v>
+        <v>0.354</v>
       </c>
       <c r="T19">
-        <v>0.259</v>
+        <v>0.221</v>
       </c>
       <c r="U19">
-        <v>0.12</v>
+        <v>0.103</v>
       </c>
       <c r="V19">
-        <v>0.041</v>
+        <v>0.033</v>
       </c>
       <c r="W19">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="X19">
-        <v>0.032</v>
+        <v>0.038</v>
       </c>
       <c r="Y19">
-        <v>0.07</v>
+        <v>0.086</v>
       </c>
       <c r="Z19">
+        <v>0.118</v>
+      </c>
+      <c r="AA19">
+        <v>0.135</v>
+      </c>
+      <c r="AB19">
+        <v>0.133</v>
+      </c>
+      <c r="AC19">
+        <v>0.127</v>
+      </c>
+      <c r="AD19">
         <v>0.107</v>
       </c>
-      <c r="AA19">
-        <v>0.146</v>
-      </c>
-      <c r="AB19">
-        <v>0.149</v>
-      </c>
-      <c r="AC19">
-        <v>0.136</v>
-      </c>
-      <c r="AD19">
-        <v>0.105</v>
-      </c>
       <c r="AE19">
-        <v>0.091</v>
+        <v>0.079</v>
       </c>
       <c r="AF19">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="AG19">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AH19">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="AI19">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AJ19">
-        <v>0.011</v>
+        <v>0.009</v>
       </c>
       <c r="AK19">
+        <v>0.008</v>
+      </c>
+      <c r="AL19">
+        <v>0.003</v>
+      </c>
+      <c r="AM19">
         <v>0.005</v>
       </c>
-      <c r="AL19">
-        <v>0.004</v>
-      </c>
-      <c r="AM19">
-        <v>0.004</v>
-      </c>
       <c r="AN19">
-        <v>0.614</v>
+        <v>0.538</v>
       </c>
       <c r="AO19">
-        <v>0.52</v>
+        <v>0.512</v>
       </c>
       <c r="AP19">
-        <v>0.563</v>
+        <v>0.495</v>
       </c>
       <c r="AQ19">
-        <v>0.565</v>
+        <v>0.48</v>
       </c>
       <c r="AR19">
-        <v>0.603</v>
+        <v>0.538</v>
       </c>
       <c r="AS19">
-        <v>0.546</v>
+        <v>0.549</v>
       </c>
       <c r="AT19">
-        <v>0.521</v>
+        <v>0.544</v>
       </c>
       <c r="AU19">
-        <v>0.519</v>
+        <v>0.568</v>
       </c>
       <c r="AV19">
-        <v>0.181</v>
+        <v>0.365</v>
       </c>
       <c r="AW19">
-        <v>0.119</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="20" spans="1:49">
       <c r="A20">
-        <v>824447</v>
+        <v>823392</v>
       </c>
       <c r="B20" t="s">
         <v>49</v>
@@ -3451,141 +3451,141 @@
         <v>57</v>
       </c>
       <c r="F20">
-        <v>4.264</v>
+        <v>4.88</v>
       </c>
       <c r="G20">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="H20">
-        <v>0.104</v>
+        <v>0.115</v>
       </c>
       <c r="I20">
-        <v>0.226</v>
+        <v>0.333</v>
       </c>
       <c r="J20">
-        <v>0.099</v>
+        <v>0.072</v>
       </c>
       <c r="K20">
-        <v>0.268</v>
+        <v>0.196</v>
       </c>
       <c r="L20">
-        <v>1.125</v>
+        <v>0.863</v>
       </c>
       <c r="M20">
+        <v>0.132</v>
+      </c>
+      <c r="N20">
+        <v>2.015</v>
+      </c>
+      <c r="O20">
+        <v>5.519</v>
+      </c>
+      <c r="P20">
+        <v>4.224</v>
+      </c>
+      <c r="Q20">
+        <v>6.844</v>
+      </c>
+      <c r="R20">
+        <v>0.424</v>
+      </c>
+      <c r="S20">
+        <v>0.361</v>
+      </c>
+      <c r="T20">
+        <v>0.154</v>
+      </c>
+      <c r="U20">
+        <v>0.051</v>
+      </c>
+      <c r="V20">
+        <v>0.009</v>
+      </c>
+      <c r="W20">
+        <v>0.001</v>
+      </c>
+      <c r="X20">
+        <v>0.034</v>
+      </c>
+      <c r="Y20">
         <v>0.08</v>
       </c>
-      <c r="N20">
-        <v>1.49</v>
-      </c>
-      <c r="O20">
-        <v>5.166</v>
-      </c>
-      <c r="P20">
-        <v>2.978</v>
-      </c>
-      <c r="Q20">
-        <v>6.046</v>
-      </c>
-      <c r="R20">
-        <v>0.331</v>
-      </c>
-      <c r="S20">
-        <v>0.356</v>
-      </c>
-      <c r="T20">
-        <v>0.208</v>
-      </c>
-      <c r="U20">
-        <v>0.074</v>
-      </c>
-      <c r="V20">
-        <v>0.024</v>
-      </c>
-      <c r="W20">
-        <v>0.007</v>
-      </c>
-      <c r="X20">
-        <v>0.064</v>
-      </c>
-      <c r="Y20">
+      <c r="Z20">
         <v>0.101</v>
-      </c>
-      <c r="Z20">
-        <v>0.127</v>
       </c>
       <c r="AA20">
         <v>0.147</v>
       </c>
       <c r="AB20">
-        <v>0.132</v>
+        <v>0.145</v>
       </c>
       <c r="AC20">
-        <v>0.134</v>
+        <v>0.127</v>
       </c>
       <c r="AD20">
-        <v>0.103</v>
+        <v>0.108</v>
       </c>
       <c r="AE20">
-        <v>0.069</v>
+        <v>0.081</v>
       </c>
       <c r="AF20">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="AG20">
-        <v>0.03</v>
+        <v>0.043</v>
       </c>
       <c r="AH20">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="AI20">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="AJ20">
-        <v>0.008</v>
+        <v>0.013</v>
       </c>
       <c r="AK20">
+        <v>0.007</v>
+      </c>
+      <c r="AL20">
         <v>0.004</v>
       </c>
-      <c r="AL20">
-        <v>0.002</v>
-      </c>
       <c r="AM20">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="AN20">
-        <v>0.499</v>
+        <v>0.629</v>
       </c>
       <c r="AO20">
-        <v>0.407</v>
+        <v>0.518</v>
       </c>
       <c r="AP20">
-        <v>0.484</v>
+        <v>0.594</v>
       </c>
       <c r="AQ20">
-        <v>0.459</v>
+        <v>0.565</v>
       </c>
       <c r="AR20">
-        <v>0.463</v>
+        <v>0.56</v>
       </c>
       <c r="AS20">
-        <v>0.494</v>
+        <v>0.559</v>
       </c>
       <c r="AT20">
-        <v>0.519</v>
+        <v>0.503</v>
       </c>
       <c r="AU20">
-        <v>0.492</v>
+        <v>0.498</v>
       </c>
       <c r="AV20">
-        <v>0.244</v>
+        <v>0.214</v>
       </c>
       <c r="AW20">
-        <v>0.122</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="21" spans="1:49">
       <c r="A21">
-        <v>824526</v>
+        <v>823471</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
@@ -3600,141 +3600,141 @@
         <v>59</v>
       </c>
       <c r="F21">
-        <v>4.854</v>
+        <v>4.72</v>
       </c>
       <c r="G21">
-        <v>0.599</v>
+        <v>0.613</v>
       </c>
       <c r="H21">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="I21">
-        <v>0.299</v>
+        <v>0.308</v>
       </c>
       <c r="J21">
-        <v>0.09</v>
+        <v>0.081</v>
       </c>
       <c r="K21">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="L21">
-        <v>1.445</v>
+        <v>0.962</v>
       </c>
       <c r="M21">
-        <v>0.153</v>
+        <v>0.14</v>
       </c>
       <c r="N21">
-        <v>1.741</v>
+        <v>1.703</v>
       </c>
       <c r="O21">
-        <v>4.885</v>
+        <v>5.886</v>
       </c>
       <c r="P21">
-        <v>3.249</v>
+        <v>3.357</v>
       </c>
       <c r="Q21">
-        <v>8.711</v>
+        <v>7.719</v>
       </c>
       <c r="R21">
-        <v>0.24</v>
+        <v>0.374</v>
       </c>
       <c r="S21">
-        <v>0.34</v>
+        <v>0.383</v>
       </c>
       <c r="T21">
-        <v>0.241</v>
+        <v>0.167</v>
       </c>
       <c r="U21">
-        <v>0.116</v>
+        <v>0.062</v>
       </c>
       <c r="V21">
-        <v>0.045</v>
+        <v>0.012</v>
       </c>
       <c r="W21">
-        <v>0.018</v>
+        <v>0.002</v>
       </c>
       <c r="X21">
-        <v>0.037</v>
+        <v>0.041</v>
       </c>
       <c r="Y21">
-        <v>0.079</v>
+        <v>0.083</v>
       </c>
       <c r="Z21">
-        <v>0.111</v>
+        <v>0.122</v>
       </c>
       <c r="AA21">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AB21">
-        <v>0.138</v>
+        <v>0.135</v>
       </c>
       <c r="AC21">
-        <v>0.13</v>
+        <v>0.124</v>
       </c>
       <c r="AD21">
-        <v>0.099</v>
+        <v>0.109</v>
       </c>
       <c r="AE21">
-        <v>0.085</v>
+        <v>0.082</v>
       </c>
       <c r="AF21">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="AG21">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="AH21">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="AI21">
         <v>0.017</v>
       </c>
       <c r="AJ21">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="AK21">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AL21">
         <v>0.004</v>
       </c>
       <c r="AM21">
-        <v>0.007</v>
+        <v>0.004</v>
       </c>
       <c r="AN21">
-        <v>0.539</v>
+        <v>0.574</v>
       </c>
       <c r="AO21">
-        <v>0.524</v>
+        <v>0.482</v>
       </c>
       <c r="AP21">
-        <v>0.537</v>
+        <v>0.513</v>
       </c>
       <c r="AQ21">
-        <v>0.536</v>
+        <v>0.491</v>
       </c>
       <c r="AR21">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="AS21">
-        <v>0.562</v>
+        <v>0.56</v>
       </c>
       <c r="AT21">
-        <v>0.59</v>
+        <v>0.553</v>
       </c>
       <c r="AU21">
-        <v>0.573</v>
+        <v>0.551</v>
       </c>
       <c r="AV21">
-        <v>0.256</v>
+        <v>0.236</v>
       </c>
       <c r="AW21">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="22" spans="1:49">
       <c r="A22">
-        <v>824849</v>
+        <v>823633</v>
       </c>
       <c r="B22" t="s">
         <v>49</v>
@@ -3749,141 +3749,141 @@
         <v>61</v>
       </c>
       <c r="F22">
-        <v>4.966</v>
+        <v>4.567</v>
       </c>
       <c r="G22">
-        <v>0.524</v>
+        <v>0.544</v>
       </c>
       <c r="H22">
-        <v>0.104</v>
+        <v>0.114</v>
       </c>
       <c r="I22">
-        <v>0.258</v>
+        <v>0.251</v>
       </c>
       <c r="J22">
-        <v>0.094</v>
+        <v>0.09</v>
       </c>
       <c r="K22">
-        <v>0.266</v>
+        <v>0.252</v>
       </c>
       <c r="L22">
-        <v>1.116</v>
+        <v>1.119</v>
       </c>
       <c r="M22">
-        <v>0.095</v>
+        <v>0.054</v>
       </c>
       <c r="N22">
-        <v>1.483</v>
+        <v>1.404</v>
       </c>
       <c r="O22">
-        <v>5.454</v>
+        <v>5.64</v>
       </c>
       <c r="P22">
-        <v>4.772</v>
+        <v>3.911</v>
       </c>
       <c r="Q22">
-        <v>8.978</v>
+        <v>7.573</v>
       </c>
       <c r="R22">
         <v>0.33</v>
       </c>
       <c r="S22">
-        <v>0.362</v>
+        <v>0.369</v>
       </c>
       <c r="T22">
-        <v>0.202</v>
+        <v>0.195</v>
       </c>
       <c r="U22">
-        <v>0.082</v>
+        <v>0.076</v>
       </c>
       <c r="V22">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="W22">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="X22">
-        <v>0.042</v>
+        <v>0.054</v>
       </c>
       <c r="Y22">
-        <v>0.074</v>
+        <v>0.094</v>
       </c>
       <c r="Z22">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="AA22">
-        <v>0.128</v>
+        <v>0.137</v>
       </c>
       <c r="AB22">
-        <v>0.137</v>
+        <v>0.134</v>
       </c>
       <c r="AC22">
-        <v>0.121</v>
+        <v>0.131</v>
       </c>
       <c r="AD22">
-        <v>0.102</v>
+        <v>0.094</v>
       </c>
       <c r="AE22">
-        <v>0.081</v>
+        <v>0.077</v>
       </c>
       <c r="AF22">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="AG22">
-        <v>0.044</v>
+        <v>0.037</v>
       </c>
       <c r="AH22">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="AI22">
-        <v>0.023</v>
+        <v>0.016</v>
       </c>
       <c r="AJ22">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="AK22">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="AL22">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AM22">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="AN22">
-        <v>0.617</v>
+        <v>0.507</v>
       </c>
       <c r="AO22">
-        <v>0.491</v>
+        <v>0.463</v>
       </c>
       <c r="AP22">
-        <v>0.573</v>
+        <v>0.527</v>
       </c>
       <c r="AQ22">
-        <v>0.563</v>
+        <v>0.474</v>
       </c>
       <c r="AR22">
-        <v>0.543</v>
+        <v>0.476</v>
       </c>
       <c r="AS22">
-        <v>0.555</v>
+        <v>0.528</v>
       </c>
       <c r="AT22">
-        <v>0.544</v>
+        <v>0.545</v>
       </c>
       <c r="AU22">
-        <v>0.564</v>
+        <v>0.522</v>
       </c>
       <c r="AV22">
-        <v>0.295</v>
+        <v>0.283</v>
       </c>
       <c r="AW22">
-        <v>0.118</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="23" spans="1:49">
       <c r="A23">
-        <v>825017</v>
+        <v>823717</v>
       </c>
       <c r="B23" t="s">
         <v>49</v>
@@ -3898,141 +3898,141 @@
         <v>63</v>
       </c>
       <c r="F23">
-        <v>4.648</v>
+        <v>4.311</v>
       </c>
       <c r="G23">
-        <v>0.498</v>
+        <v>0.482</v>
       </c>
       <c r="H23">
-        <v>0.103</v>
+        <v>0.093</v>
       </c>
       <c r="I23">
-        <v>0.227</v>
+        <v>0.225</v>
       </c>
       <c r="J23">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="K23">
-        <v>0.282</v>
+        <v>0.28</v>
       </c>
       <c r="L23">
-        <v>1.381</v>
+        <v>0.983</v>
       </c>
       <c r="M23">
         <v>0.085</v>
       </c>
       <c r="N23">
-        <v>1.895</v>
+        <v>1.467</v>
       </c>
       <c r="O23">
-        <v>4.71</v>
+        <v>5.671</v>
       </c>
       <c r="P23">
-        <v>3.276</v>
+        <v>3.255</v>
       </c>
       <c r="Q23">
-        <v>8.697</v>
+        <v>7.542</v>
       </c>
       <c r="R23">
-        <v>0.247</v>
+        <v>0.372</v>
       </c>
       <c r="S23">
-        <v>0.356</v>
+        <v>0.373</v>
       </c>
       <c r="T23">
-        <v>0.243</v>
+        <v>0.177</v>
       </c>
       <c r="U23">
-        <v>0.102</v>
+        <v>0.063</v>
       </c>
       <c r="V23">
-        <v>0.035</v>
+        <v>0.013</v>
       </c>
       <c r="W23">
-        <v>0.018</v>
+        <v>0.003</v>
       </c>
       <c r="X23">
-        <v>0.045</v>
+        <v>0.062</v>
       </c>
       <c r="Y23">
-        <v>0.091</v>
+        <v>0.104</v>
       </c>
       <c r="Z23">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="AA23">
-        <v>0.134</v>
+        <v>0.153</v>
       </c>
       <c r="AB23">
-        <v>0.145</v>
+        <v>0.141</v>
       </c>
       <c r="AC23">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
       <c r="AD23">
-        <v>0.109</v>
+        <v>0.09</v>
       </c>
       <c r="AE23">
-        <v>0.07</v>
+        <v>0.067</v>
       </c>
       <c r="AF23">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="AG23">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="AH23">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="AI23">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="AJ23">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="AK23">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AL23">
+        <v>0.002</v>
+      </c>
+      <c r="AM23">
         <v>0.004</v>
       </c>
-      <c r="AM23">
-        <v>0.006</v>
-      </c>
       <c r="AN23">
-        <v>0.583</v>
+        <v>0.482</v>
       </c>
       <c r="AO23">
-        <v>0.435</v>
+        <v>0.462</v>
       </c>
       <c r="AP23">
-        <v>0.492</v>
+        <v>0.454</v>
       </c>
       <c r="AQ23">
-        <v>0.477</v>
+        <v>0.458</v>
       </c>
       <c r="AR23">
-        <v>0.499</v>
+        <v>0.468</v>
       </c>
       <c r="AS23">
-        <v>0.554</v>
+        <v>0.486</v>
       </c>
       <c r="AT23">
-        <v>0.53</v>
+        <v>0.531</v>
       </c>
       <c r="AU23">
-        <v>0.551</v>
+        <v>0.475</v>
       </c>
       <c r="AV23">
-        <v>0.312</v>
+        <v>0.272</v>
       </c>
       <c r="AW23">
-        <v>0.11</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="24" spans="1:49">
       <c r="A24">
-        <v>822823</v>
+        <v>823796</v>
       </c>
       <c r="B24" t="s">
         <v>49</v>
@@ -4047,141 +4047,141 @@
         <v>65</v>
       </c>
       <c r="F24">
-        <v>4.232</v>
+        <v>4.902</v>
       </c>
       <c r="G24">
-        <v>0.579</v>
+        <v>0.562</v>
       </c>
       <c r="H24">
-        <v>0.117</v>
+        <v>0.107</v>
       </c>
       <c r="I24">
-        <v>0.284</v>
+        <v>0.275</v>
       </c>
       <c r="J24">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="K24">
-        <v>0.199</v>
+        <v>0.235</v>
       </c>
       <c r="L24">
-        <v>1.069</v>
+        <v>1.042</v>
       </c>
       <c r="M24">
-        <v>0.073</v>
+        <v>0.127</v>
       </c>
       <c r="N24">
-        <v>1.509</v>
+        <v>1.729</v>
       </c>
       <c r="O24">
-        <v>5.285</v>
+        <v>5.592</v>
       </c>
       <c r="P24">
-        <v>3.333</v>
+        <v>3.933</v>
       </c>
       <c r="Q24">
-        <v>8.663</v>
+        <v>6.582</v>
       </c>
       <c r="R24">
-        <v>0.349</v>
+        <v>0.361</v>
       </c>
       <c r="S24">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="T24">
-        <v>0.199</v>
+        <v>0.19</v>
       </c>
       <c r="U24">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="V24">
-        <v>0.018</v>
+        <v>0.015</v>
       </c>
       <c r="W24">
         <v>0.005</v>
       </c>
       <c r="X24">
-        <v>0.065</v>
+        <v>0.039</v>
       </c>
       <c r="Y24">
-        <v>0.109</v>
+        <v>0.076</v>
       </c>
       <c r="Z24">
-        <v>0.126</v>
+        <v>0.108</v>
       </c>
       <c r="AA24">
-        <v>0.151</v>
+        <v>0.125</v>
       </c>
       <c r="AB24">
-        <v>0.147</v>
+        <v>0.137</v>
       </c>
       <c r="AC24">
-        <v>0.123</v>
+        <v>0.133</v>
       </c>
       <c r="AD24">
-        <v>0.088</v>
+        <v>0.113</v>
       </c>
       <c r="AE24">
-        <v>0.064</v>
+        <v>0.091</v>
       </c>
       <c r="AF24">
-        <v>0.043</v>
+        <v>0.062</v>
       </c>
       <c r="AG24">
-        <v>0.029</v>
+        <v>0.049</v>
       </c>
       <c r="AH24">
-        <v>0.019</v>
+        <v>0.027</v>
       </c>
       <c r="AI24">
+        <v>0.017</v>
+      </c>
+      <c r="AJ24">
         <v>0.012</v>
       </c>
-      <c r="AJ24">
-        <v>0.011</v>
-      </c>
       <c r="AK24">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AL24">
         <v>0.003</v>
       </c>
       <c r="AM24">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="AN24">
-        <v>0.484</v>
+        <v>0.664</v>
       </c>
       <c r="AO24">
-        <v>0.466</v>
+        <v>0.55</v>
       </c>
       <c r="AP24">
-        <v>0.484</v>
+        <v>0.627</v>
       </c>
       <c r="AQ24">
-        <v>0.47</v>
+        <v>0.553</v>
       </c>
       <c r="AR24">
-        <v>0.487</v>
+        <v>0.575</v>
       </c>
       <c r="AS24">
-        <v>0.474</v>
+        <v>0.494</v>
       </c>
       <c r="AT24">
-        <v>0.507</v>
+        <v>0.482</v>
       </c>
       <c r="AU24">
-        <v>0.457</v>
+        <v>0.489</v>
       </c>
       <c r="AV24">
-        <v>0.195</v>
+        <v>0.239</v>
       </c>
       <c r="AW24">
-        <v>0.115</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="25" spans="1:49">
       <c r="A25">
-        <v>822908</v>
+        <v>823958</v>
       </c>
       <c r="B25" t="s">
         <v>49</v>
@@ -4196,141 +4196,141 @@
         <v>67</v>
       </c>
       <c r="F25">
-        <v>3.599</v>
+        <v>4.663</v>
       </c>
       <c r="G25">
-        <v>0.466</v>
+        <v>0.649</v>
       </c>
       <c r="H25">
-        <v>0.098</v>
+        <v>0.123</v>
       </c>
       <c r="I25">
-        <v>0.185</v>
+        <v>0.346</v>
       </c>
       <c r="J25">
-        <v>0.108</v>
+        <v>0.071</v>
       </c>
       <c r="K25">
-        <v>0.295</v>
+        <v>0.167</v>
       </c>
       <c r="L25">
-        <v>0.862</v>
+        <v>1.306</v>
       </c>
       <c r="M25">
-        <v>0.099</v>
+        <v>0.112</v>
       </c>
       <c r="N25">
-        <v>1.52</v>
+        <v>1.595</v>
       </c>
       <c r="O25">
-        <v>4.805</v>
+        <v>4.967</v>
       </c>
       <c r="P25">
-        <v>2.672</v>
+        <v>3.335</v>
       </c>
       <c r="Q25">
-        <v>9.666</v>
+        <v>6.671</v>
       </c>
       <c r="R25">
-        <v>0.43</v>
+        <v>0.278</v>
       </c>
       <c r="S25">
-        <v>0.354</v>
+        <v>0.347</v>
       </c>
       <c r="T25">
-        <v>0.157</v>
+        <v>0.226</v>
       </c>
       <c r="U25">
-        <v>0.045</v>
+        <v>0.102</v>
       </c>
       <c r="V25">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
       <c r="W25">
+        <v>0.011</v>
+      </c>
+      <c r="X25">
+        <v>0.036</v>
+      </c>
+      <c r="Y25">
+        <v>0.083</v>
+      </c>
+      <c r="Z25">
+        <v>0.126</v>
+      </c>
+      <c r="AA25">
+        <v>0.146</v>
+      </c>
+      <c r="AB25">
+        <v>0.147</v>
+      </c>
+      <c r="AC25">
+        <v>0.124</v>
+      </c>
+      <c r="AD25">
+        <v>0.101</v>
+      </c>
+      <c r="AE25">
+        <v>0.079</v>
+      </c>
+      <c r="AF25">
+        <v>0.057</v>
+      </c>
+      <c r="AG25">
+        <v>0.04</v>
+      </c>
+      <c r="AH25">
+        <v>0.024</v>
+      </c>
+      <c r="AI25">
+        <v>0.015</v>
+      </c>
+      <c r="AJ25">
+        <v>0.008</v>
+      </c>
+      <c r="AK25">
+        <v>0.006</v>
+      </c>
+      <c r="AL25">
         <v>0.003</v>
       </c>
-      <c r="X25">
-        <v>0.095</v>
-      </c>
-      <c r="Y25">
-        <v>0.133</v>
-      </c>
-      <c r="Z25">
-        <v>0.157</v>
-      </c>
-      <c r="AA25">
-        <v>0.164</v>
-      </c>
-      <c r="AB25">
-        <v>0.13</v>
-      </c>
-      <c r="AC25">
-        <v>0.112</v>
-      </c>
-      <c r="AD25">
-        <v>0.078</v>
-      </c>
-      <c r="AE25">
-        <v>0.047</v>
-      </c>
-      <c r="AF25">
-        <v>0.037</v>
-      </c>
-      <c r="AG25">
-        <v>0.018</v>
-      </c>
-      <c r="AH25">
-        <v>0.012</v>
-      </c>
-      <c r="AI25">
-        <v>0.006</v>
-      </c>
-      <c r="AJ25">
+      <c r="AM25">
         <v>0.005</v>
       </c>
-      <c r="AK25">
-        <v>0.002</v>
-      </c>
-      <c r="AL25">
-        <v>0.001</v>
-      </c>
-      <c r="AM25">
-        <v>0.002</v>
-      </c>
       <c r="AN25">
-        <v>0.332</v>
+        <v>0.562</v>
       </c>
       <c r="AO25">
-        <v>0.327</v>
+        <v>0.476</v>
       </c>
       <c r="AP25">
-        <v>0.326</v>
+        <v>0.553</v>
       </c>
       <c r="AQ25">
-        <v>0.323</v>
+        <v>0.475</v>
       </c>
       <c r="AR25">
-        <v>0.331</v>
+        <v>0.531</v>
       </c>
       <c r="AS25">
-        <v>0.431</v>
+        <v>0.485</v>
       </c>
       <c r="AT25">
-        <v>0.481</v>
+        <v>0.547</v>
       </c>
       <c r="AU25">
-        <v>0.528</v>
+        <v>0.594</v>
       </c>
       <c r="AV25">
-        <v>0.299</v>
+        <v>0.22</v>
       </c>
       <c r="AW25">
-        <v>0.145</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="26" spans="1:49">
       <c r="A26">
-        <v>823310</v>
+        <v>824445</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
@@ -4345,141 +4345,141 @@
         <v>69</v>
       </c>
       <c r="F26">
-        <v>4.712</v>
+        <v>3.29</v>
       </c>
       <c r="G26">
-        <v>0.534</v>
+        <v>0.511</v>
       </c>
       <c r="H26">
+        <v>0.101</v>
+      </c>
+      <c r="I26">
+        <v>0.202</v>
+      </c>
+      <c r="J26">
+        <v>0.105</v>
+      </c>
+      <c r="K26">
+        <v>0.243</v>
+      </c>
+      <c r="L26">
+        <v>0.809</v>
+      </c>
+      <c r="M26">
+        <v>0.085</v>
+      </c>
+      <c r="N26">
+        <v>1.418</v>
+      </c>
+      <c r="O26">
+        <v>4.276</v>
+      </c>
+      <c r="P26">
+        <v>2.711</v>
+      </c>
+      <c r="Q26">
+        <v>6.75</v>
+      </c>
+      <c r="R26">
+        <v>0.453</v>
+      </c>
+      <c r="S26">
+        <v>0.351</v>
+      </c>
+      <c r="T26">
+        <v>0.143</v>
+      </c>
+      <c r="U26">
+        <v>0.043</v>
+      </c>
+      <c r="V26">
+        <v>0.006</v>
+      </c>
+      <c r="W26">
+        <v>0.003</v>
+      </c>
+      <c r="X26">
         <v>0.097</v>
       </c>
-      <c r="I26">
-        <v>0.269</v>
-      </c>
-      <c r="J26">
-        <v>0.094</v>
-      </c>
-      <c r="K26">
-        <v>0.25</v>
-      </c>
-      <c r="L26">
-        <v>0.977</v>
-      </c>
-      <c r="M26">
-        <v>0.125</v>
-      </c>
-      <c r="N26">
-        <v>1.776</v>
-      </c>
-      <c r="O26">
-        <v>5.257</v>
-      </c>
-      <c r="P26">
-        <v>4.074</v>
-      </c>
-      <c r="Q26">
-        <v>7.286</v>
-      </c>
-      <c r="R26">
-        <v>0.373</v>
-      </c>
-      <c r="S26">
-        <v>0.372</v>
-      </c>
-      <c r="T26">
-        <v>0.177</v>
-      </c>
-      <c r="U26">
-        <v>0.06</v>
-      </c>
-      <c r="V26">
+      <c r="Y26">
+        <v>0.148</v>
+      </c>
+      <c r="Z26">
+        <v>0.188</v>
+      </c>
+      <c r="AA26">
+        <v>0.163</v>
+      </c>
+      <c r="AB26">
+        <v>0.139</v>
+      </c>
+      <c r="AC26">
+        <v>0.095</v>
+      </c>
+      <c r="AD26">
+        <v>0.068</v>
+      </c>
+      <c r="AE26">
+        <v>0.046</v>
+      </c>
+      <c r="AF26">
+        <v>0.025</v>
+      </c>
+      <c r="AG26">
         <v>0.015</v>
       </c>
-      <c r="W26">
+      <c r="AH26">
+        <v>0.007</v>
+      </c>
+      <c r="AI26">
+        <v>0.004</v>
+      </c>
+      <c r="AJ26">
         <v>0.002</v>
       </c>
-      <c r="X26">
-        <v>0.043</v>
-      </c>
-      <c r="Y26">
-        <v>0.092</v>
-      </c>
-      <c r="Z26">
-        <v>0.108</v>
-      </c>
-      <c r="AA26">
-        <v>0.144</v>
-      </c>
-      <c r="AB26">
-        <v>0.133</v>
-      </c>
-      <c r="AC26">
-        <v>0.14</v>
-      </c>
-      <c r="AD26">
-        <v>0.1</v>
-      </c>
-      <c r="AE26">
-        <v>0.074</v>
-      </c>
-      <c r="AF26">
-        <v>0.056</v>
-      </c>
-      <c r="AG26">
-        <v>0.038</v>
-      </c>
-      <c r="AH26">
-        <v>0.032</v>
-      </c>
-      <c r="AI26">
-        <v>0.013</v>
-      </c>
-      <c r="AJ26">
-        <v>0.01</v>
-      </c>
       <c r="AK26">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="AL26">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="AM26">
-        <v>0.007</v>
+        <v>0.0</v>
       </c>
       <c r="AN26">
-        <v>0.566</v>
+        <v>0.341</v>
       </c>
       <c r="AO26">
-        <v>0.497</v>
+        <v>0.286</v>
       </c>
       <c r="AP26">
-        <v>0.523</v>
+        <v>0.314</v>
       </c>
       <c r="AQ26">
-        <v>0.489</v>
+        <v>0.312</v>
       </c>
       <c r="AR26">
-        <v>0.561</v>
+        <v>0.332</v>
       </c>
       <c r="AS26">
-        <v>0.508</v>
+        <v>0.383</v>
       </c>
       <c r="AT26">
-        <v>0.541</v>
+        <v>0.434</v>
       </c>
       <c r="AU26">
-        <v>0.541</v>
+        <v>0.452</v>
       </c>
       <c r="AV26">
-        <v>0.267</v>
+        <v>0.231</v>
       </c>
       <c r="AW26">
-        <v>0.101</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="27" spans="1:49">
       <c r="A27">
-        <v>823390</v>
+        <v>824525</v>
       </c>
       <c r="B27" t="s">
         <v>49</v>
@@ -4494,94 +4494,94 @@
         <v>71</v>
       </c>
       <c r="F27">
-        <v>4.987</v>
+        <v>5.25</v>
       </c>
       <c r="G27">
-        <v>0.656</v>
+        <v>0.575</v>
       </c>
       <c r="H27">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="I27">
-        <v>0.339</v>
+        <v>0.297</v>
       </c>
       <c r="J27">
-        <v>0.075</v>
+        <v>0.087</v>
       </c>
       <c r="K27">
-        <v>0.168</v>
+        <v>0.233</v>
       </c>
       <c r="L27">
-        <v>0.859</v>
+        <v>1.691</v>
       </c>
       <c r="M27">
-        <v>0.121</v>
+        <v>0.18</v>
       </c>
       <c r="N27">
-        <v>1.985</v>
+        <v>1.61</v>
       </c>
       <c r="O27">
-        <v>5.84</v>
+        <v>4.65</v>
       </c>
       <c r="P27">
-        <v>4.029</v>
+        <v>3.821</v>
       </c>
       <c r="Q27">
-        <v>6.988</v>
+        <v>7.619</v>
       </c>
       <c r="R27">
-        <v>0.427</v>
+        <v>0.188</v>
       </c>
       <c r="S27">
-        <v>0.353</v>
+        <v>0.308</v>
       </c>
       <c r="T27">
-        <v>0.164</v>
+        <v>0.266</v>
       </c>
       <c r="U27">
-        <v>0.046</v>
+        <v>0.147</v>
       </c>
       <c r="V27">
-        <v>0.008</v>
+        <v>0.062</v>
       </c>
       <c r="W27">
-        <v>0.001</v>
+        <v>0.03</v>
       </c>
       <c r="X27">
-        <v>0.039</v>
+        <v>0.031</v>
       </c>
       <c r="Y27">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="Z27">
-        <v>0.109</v>
+        <v>0.097</v>
       </c>
       <c r="AA27">
-        <v>0.138</v>
+        <v>0.118</v>
       </c>
       <c r="AB27">
-        <v>0.138</v>
+        <v>0.149</v>
       </c>
       <c r="AC27">
-        <v>0.126</v>
+        <v>0.135</v>
       </c>
       <c r="AD27">
-        <v>0.103</v>
+        <v>0.114</v>
       </c>
       <c r="AE27">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="AF27">
-        <v>0.058</v>
+        <v>0.074</v>
       </c>
       <c r="AG27">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
       <c r="AH27">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="AI27">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="AJ27">
         <v>0.014</v>
@@ -4590,45 +4590,45 @@
         <v>0.009</v>
       </c>
       <c r="AL27">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AM27">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AN27">
-        <v>0.571</v>
+        <v>0.597</v>
       </c>
       <c r="AO27">
-        <v>0.528</v>
+        <v>0.619</v>
       </c>
       <c r="AP27">
-        <v>0.577</v>
+        <v>0.566</v>
       </c>
       <c r="AQ27">
-        <v>0.568</v>
+        <v>0.601</v>
       </c>
       <c r="AR27">
-        <v>0.552</v>
+        <v>0.586</v>
       </c>
       <c r="AS27">
-        <v>0.584</v>
+        <v>0.612</v>
       </c>
       <c r="AT27">
-        <v>0.585</v>
+        <v>0.581</v>
       </c>
       <c r="AU27">
-        <v>0.55</v>
+        <v>0.603</v>
       </c>
       <c r="AV27">
-        <v>0.225</v>
+        <v>0.287</v>
       </c>
       <c r="AW27">
-        <v>0.113</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="28" spans="1:49">
       <c r="A28">
-        <v>823636</v>
+        <v>824608</v>
       </c>
       <c r="B28" t="s">
         <v>49</v>
@@ -4643,141 +4643,141 @@
         <v>73</v>
       </c>
       <c r="F28">
-        <v>4.627</v>
+        <v>4.323</v>
       </c>
       <c r="G28">
-        <v>0.607</v>
+        <v>0.449</v>
       </c>
       <c r="H28">
-        <v>0.132</v>
+        <v>0.091</v>
       </c>
       <c r="I28">
-        <v>0.294</v>
+        <v>0.2</v>
       </c>
       <c r="J28">
-        <v>0.082</v>
+        <v>0.088</v>
       </c>
       <c r="K28">
-        <v>0.194</v>
+        <v>0.34</v>
       </c>
       <c r="L28">
-        <v>1.328</v>
+        <v>0.936</v>
       </c>
       <c r="M28">
-        <v>0.065</v>
+        <v>0.077</v>
       </c>
       <c r="N28">
-        <v>1.532</v>
+        <v>1.462</v>
       </c>
       <c r="O28">
-        <v>5.473</v>
+        <v>5.455</v>
       </c>
       <c r="P28">
-        <v>3.123</v>
+        <v>3.847</v>
       </c>
       <c r="Q28">
-        <v>6.423</v>
+        <v>8.661</v>
       </c>
       <c r="R28">
-        <v>0.262</v>
+        <v>0.4</v>
       </c>
       <c r="S28">
-        <v>0.349</v>
+        <v>0.353</v>
       </c>
       <c r="T28">
-        <v>0.245</v>
+        <v>0.174</v>
       </c>
       <c r="U28">
-        <v>0.101</v>
+        <v>0.057</v>
       </c>
       <c r="V28">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="W28">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="X28">
-        <v>0.046</v>
+        <v>0.062</v>
       </c>
       <c r="Y28">
-        <v>0.084</v>
+        <v>0.109</v>
       </c>
       <c r="Z28">
-        <v>0.114</v>
+        <v>0.123</v>
       </c>
       <c r="AA28">
-        <v>0.141</v>
+        <v>0.146</v>
       </c>
       <c r="AB28">
-        <v>0.147</v>
+        <v>0.136</v>
       </c>
       <c r="AC28">
         <v>0.123</v>
       </c>
       <c r="AD28">
-        <v>0.113</v>
+        <v>0.093</v>
       </c>
       <c r="AE28">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="AF28">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="AG28">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="AH28">
-        <v>0.025</v>
+        <v>0.017</v>
       </c>
       <c r="AI28">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="AJ28">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="AK28">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="AL28">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="AM28">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AN28">
-        <v>0.54</v>
+        <v>0.494</v>
       </c>
       <c r="AO28">
+        <v>0.444</v>
+      </c>
+      <c r="AP28">
+        <v>0.453</v>
+      </c>
+      <c r="AQ28">
+        <v>0.466</v>
+      </c>
+      <c r="AR28">
+        <v>0.467</v>
+      </c>
+      <c r="AS28">
+        <v>0.445</v>
+      </c>
+      <c r="AT28">
         <v>0.512</v>
       </c>
-      <c r="AP28">
-        <v>0.518</v>
-      </c>
-      <c r="AQ28">
-        <v>0.501</v>
-      </c>
-      <c r="AR28">
-        <v>0.552</v>
-      </c>
-      <c r="AS28">
-        <v>0.496</v>
-      </c>
-      <c r="AT28">
-        <v>0.504</v>
-      </c>
       <c r="AU28">
-        <v>0.53</v>
+        <v>0.499</v>
       </c>
       <c r="AV28">
-        <v>0.246</v>
+        <v>0.324</v>
       </c>
       <c r="AW28">
-        <v>0.124</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="29" spans="1:49">
       <c r="A29">
-        <v>823716</v>
+        <v>824850</v>
       </c>
       <c r="B29" t="s">
         <v>49</v>
@@ -4792,141 +4792,141 @@
         <v>75</v>
       </c>
       <c r="F29">
-        <v>4.306</v>
+        <v>5.283</v>
       </c>
       <c r="G29">
-        <v>0.516</v>
+        <v>0.53</v>
       </c>
       <c r="H29">
+        <v>0.101</v>
+      </c>
+      <c r="I29">
+        <v>0.266</v>
+      </c>
+      <c r="J29">
+        <v>0.099</v>
+      </c>
+      <c r="K29">
+        <v>0.259</v>
+      </c>
+      <c r="L29">
+        <v>1.263</v>
+      </c>
+      <c r="M29">
+        <v>0.11</v>
+      </c>
+      <c r="N29">
+        <v>1.811</v>
+      </c>
+      <c r="O29">
+        <v>5.211</v>
+      </c>
+      <c r="P29">
+        <v>4.616</v>
+      </c>
+      <c r="Q29">
+        <v>8.136</v>
+      </c>
+      <c r="R29">
+        <v>0.282</v>
+      </c>
+      <c r="S29">
+        <v>0.361</v>
+      </c>
+      <c r="T29">
+        <v>0.221</v>
+      </c>
+      <c r="U29">
+        <v>0.096</v>
+      </c>
+      <c r="V29">
+        <v>0.032</v>
+      </c>
+      <c r="W29">
+        <v>0.008</v>
+      </c>
+      <c r="X29">
+        <v>0.03</v>
+      </c>
+      <c r="Y29">
+        <v>0.065</v>
+      </c>
+      <c r="Z29">
         <v>0.098</v>
       </c>
-      <c r="I29">
-        <v>0.237</v>
-      </c>
-      <c r="J29">
-        <v>0.107</v>
-      </c>
-      <c r="K29">
-        <v>0.262</v>
-      </c>
-      <c r="L29">
-        <v>1.022</v>
-      </c>
-      <c r="M29">
-        <v>0.109</v>
-      </c>
-      <c r="N29">
-        <v>1.75</v>
-      </c>
-      <c r="O29">
-        <v>5.376</v>
-      </c>
-      <c r="P29">
-        <v>2.975</v>
-      </c>
-      <c r="Q29">
-        <v>9.105</v>
-      </c>
-      <c r="R29">
-        <v>0.36</v>
-      </c>
-      <c r="S29">
-        <v>0.373</v>
-      </c>
-      <c r="T29">
-        <v>0.18</v>
-      </c>
-      <c r="U29">
-        <v>0.063</v>
-      </c>
-      <c r="V29">
-        <v>0.018</v>
-      </c>
-      <c r="W29">
-        <v>0.006</v>
-      </c>
-      <c r="X29">
-        <v>0.057</v>
-      </c>
-      <c r="Y29">
-        <v>0.105</v>
-      </c>
-      <c r="Z29">
-        <v>0.133</v>
-      </c>
       <c r="AA29">
-        <v>0.145</v>
+        <v>0.129</v>
       </c>
       <c r="AB29">
-        <v>0.143</v>
+        <v>0.135</v>
       </c>
       <c r="AC29">
-        <v>0.113</v>
+        <v>0.116</v>
       </c>
       <c r="AD29">
-        <v>0.101</v>
+        <v>0.12</v>
       </c>
       <c r="AE29">
-        <v>0.072</v>
+        <v>0.091</v>
       </c>
       <c r="AF29">
-        <v>0.053</v>
+        <v>0.067</v>
       </c>
       <c r="AG29">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="AH29">
-        <v>0.021</v>
+        <v>0.036</v>
       </c>
       <c r="AI29">
-        <v>0.012</v>
+        <v>0.022</v>
       </c>
       <c r="AJ29">
-        <v>0.009</v>
+        <v>0.017</v>
       </c>
       <c r="AK29">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="AL29">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AM29">
-        <v>0.003</v>
+        <v>0.011</v>
       </c>
       <c r="AN29">
-        <v>0.488</v>
+        <v>0.628</v>
       </c>
       <c r="AO29">
-        <v>0.465</v>
+        <v>0.574</v>
       </c>
       <c r="AP29">
-        <v>0.48</v>
+        <v>0.632</v>
       </c>
       <c r="AQ29">
-        <v>0.472</v>
+        <v>0.582</v>
       </c>
       <c r="AR29">
-        <v>0.459</v>
+        <v>0.583</v>
       </c>
       <c r="AS29">
-        <v>0.486</v>
+        <v>0.569</v>
       </c>
       <c r="AT29">
-        <v>0.466</v>
+        <v>0.586</v>
       </c>
       <c r="AU29">
-        <v>0.484</v>
+        <v>0.601</v>
       </c>
       <c r="AV29">
-        <v>0.278</v>
+        <v>0.295</v>
       </c>
       <c r="AW29">
-        <v>0.127</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:49">
       <c r="A30">
-        <v>824610</v>
+        <v>824930</v>
       </c>
       <c r="B30" t="s">
         <v>49</v>
@@ -4941,141 +4941,141 @@
         <v>77</v>
       </c>
       <c r="F30">
-        <v>3.845</v>
+        <v>4.204</v>
       </c>
       <c r="G30">
+        <v>0.393</v>
+      </c>
+      <c r="H30">
+        <v>0.074</v>
+      </c>
+      <c r="I30">
+        <v>0.163</v>
+      </c>
+      <c r="J30">
+        <v>0.101</v>
+      </c>
+      <c r="K30">
         <v>0.384</v>
       </c>
-      <c r="H30">
-        <v>0.076</v>
-      </c>
-      <c r="I30">
-        <v>0.157</v>
-      </c>
-      <c r="J30">
-        <v>0.105</v>
-      </c>
-      <c r="K30">
-        <v>0.383</v>
-      </c>
       <c r="L30">
-        <v>0.829</v>
+        <v>1.064</v>
       </c>
       <c r="M30">
-        <v>0.047</v>
+        <v>0.115</v>
       </c>
       <c r="N30">
-        <v>1.157</v>
+        <v>1.482</v>
       </c>
       <c r="O30">
-        <v>4.869</v>
+        <v>5.609</v>
       </c>
       <c r="P30">
-        <v>4.551</v>
+        <v>2.56</v>
       </c>
       <c r="Q30">
-        <v>10.016</v>
+        <v>9.176</v>
       </c>
       <c r="R30">
-        <v>0.444</v>
+        <v>0.347</v>
       </c>
       <c r="S30">
-        <v>0.351</v>
+        <v>0.363</v>
       </c>
       <c r="T30">
-        <v>0.15</v>
+        <v>0.202</v>
       </c>
       <c r="U30">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="V30">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="W30">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="X30">
-        <v>0.088</v>
+        <v>0.061</v>
       </c>
       <c r="Y30">
-        <v>0.128</v>
+        <v>0.109</v>
       </c>
       <c r="Z30">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="AA30">
-        <v>0.161</v>
+        <v>0.136</v>
       </c>
       <c r="AB30">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AC30">
-        <v>0.105</v>
+        <v>0.113</v>
       </c>
       <c r="AD30">
-        <v>0.076</v>
+        <v>0.096</v>
       </c>
       <c r="AE30">
-        <v>0.055</v>
+        <v>0.071</v>
       </c>
       <c r="AF30">
-        <v>0.047</v>
+        <v>0.052</v>
       </c>
       <c r="AG30">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AH30">
         <v>0.018</v>
       </c>
       <c r="AI30">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="AJ30">
+        <v>0.006</v>
+      </c>
+      <c r="AK30">
+        <v>0.003</v>
+      </c>
+      <c r="AL30">
+        <v>0.001</v>
+      </c>
+      <c r="AM30">
         <v>0.005</v>
       </c>
-      <c r="AK30">
-        <v>0.002</v>
-      </c>
-      <c r="AL30">
-        <v>0.002</v>
-      </c>
-      <c r="AM30">
-        <v>0.003</v>
-      </c>
       <c r="AN30">
-        <v>0.385</v>
+        <v>0.43</v>
       </c>
       <c r="AO30">
-        <v>0.354</v>
+        <v>0.4</v>
       </c>
       <c r="AP30">
-        <v>0.33</v>
+        <v>0.443</v>
       </c>
       <c r="AQ30">
-        <v>0.356</v>
+        <v>0.392</v>
       </c>
       <c r="AR30">
         <v>0.412</v>
       </c>
       <c r="AS30">
-        <v>0.467</v>
+        <v>0.477</v>
       </c>
       <c r="AT30">
-        <v>0.494</v>
+        <v>0.528</v>
       </c>
       <c r="AU30">
-        <v>0.528</v>
+        <v>0.536</v>
       </c>
       <c r="AV30">
-        <v>0.297</v>
+        <v>0.376</v>
       </c>
       <c r="AW30">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="31" spans="1:49">
       <c r="A31">
-        <v>824931</v>
+        <v>825015</v>
       </c>
       <c r="B31" t="s">
         <v>49</v>
@@ -5090,136 +5090,136 @@
         <v>79</v>
       </c>
       <c r="F31">
-        <v>4.773</v>
+        <v>5.785</v>
       </c>
       <c r="G31">
-        <v>0.491</v>
+        <v>0.526</v>
       </c>
       <c r="H31">
-        <v>0.084</v>
+        <v>0.098</v>
       </c>
       <c r="I31">
-        <v>0.232</v>
+        <v>0.264</v>
       </c>
       <c r="J31">
-        <v>0.097</v>
+        <v>0.085</v>
       </c>
       <c r="K31">
         <v>0.287</v>
       </c>
       <c r="L31">
-        <v>1.258</v>
+        <v>1.748</v>
       </c>
       <c r="M31">
-        <v>0.128</v>
+        <v>0.146</v>
       </c>
       <c r="N31">
-        <v>1.677</v>
+        <v>2.116</v>
       </c>
       <c r="O31">
-        <v>5.436</v>
+        <v>5.205</v>
       </c>
       <c r="P31">
-        <v>3.133</v>
+        <v>3.513</v>
       </c>
       <c r="Q31">
-        <v>7.673</v>
+        <v>6.718</v>
       </c>
       <c r="R31">
-        <v>0.277</v>
+        <v>0.179</v>
       </c>
       <c r="S31">
-        <v>0.371</v>
+        <v>0.292</v>
       </c>
       <c r="T31">
-        <v>0.226</v>
+        <v>0.274</v>
       </c>
       <c r="U31">
-        <v>0.087</v>
+        <v>0.156</v>
       </c>
       <c r="V31">
-        <v>0.028</v>
+        <v>0.066</v>
       </c>
       <c r="W31">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="X31">
-        <v>0.042</v>
+        <v>0.024</v>
       </c>
       <c r="Y31">
-        <v>0.08</v>
+        <v>0.049</v>
       </c>
       <c r="Z31">
-        <v>0.122</v>
+        <v>0.086</v>
       </c>
       <c r="AA31">
-        <v>0.141</v>
+        <v>0.11</v>
       </c>
       <c r="AB31">
-        <v>0.139</v>
+        <v>0.12</v>
       </c>
       <c r="AC31">
-        <v>0.12</v>
+        <v>0.131</v>
       </c>
       <c r="AD31">
-        <v>0.101</v>
+        <v>0.116</v>
       </c>
       <c r="AE31">
-        <v>0.08</v>
+        <v>0.094</v>
       </c>
       <c r="AF31">
-        <v>0.059</v>
+        <v>0.071</v>
       </c>
       <c r="AG31">
-        <v>0.042</v>
+        <v>0.062</v>
       </c>
       <c r="AH31">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="AI31">
+        <v>0.033</v>
+      </c>
+      <c r="AJ31">
+        <v>0.019</v>
+      </c>
+      <c r="AK31">
+        <v>0.015</v>
+      </c>
+      <c r="AL31">
+        <v>0.009</v>
+      </c>
+      <c r="AM31">
         <v>0.016</v>
       </c>
-      <c r="AJ31">
-        <v>0.013</v>
-      </c>
-      <c r="AK31">
-        <v>0.006</v>
-      </c>
-      <c r="AL31">
-        <v>0.005</v>
-      </c>
-      <c r="AM31">
-        <v>0.005</v>
-      </c>
       <c r="AN31">
-        <v>0.554</v>
+        <v>0.711</v>
       </c>
       <c r="AO31">
-        <v>0.47</v>
+        <v>0.579</v>
       </c>
       <c r="AP31">
-        <v>0.513</v>
+        <v>0.665</v>
       </c>
       <c r="AQ31">
-        <v>0.48</v>
+        <v>0.604</v>
       </c>
       <c r="AR31">
-        <v>0.513</v>
+        <v>0.656</v>
       </c>
       <c r="AS31">
-        <v>0.569</v>
+        <v>0.643</v>
       </c>
       <c r="AT31">
-        <v>0.593</v>
+        <v>0.672</v>
       </c>
       <c r="AU31">
-        <v>0.572</v>
+        <v>0.676</v>
       </c>
       <c r="AV31">
-        <v>0.291</v>
+        <v>0.35</v>
       </c>
       <c r="AW31">
-        <v>0.117</v>
+        <v>0.108</v>
       </c>
     </row>
   </sheetData>

--- a/data/BallparkPal_Teams.xlsx
+++ b/data/BallparkPal_Teams.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
   <si>
     <t>GamePk</t>
   </si>
@@ -164,61 +164,97 @@
     <t>RunsInningExtra</t>
   </si>
   <si>
-    <t>2026-04-30</t>
+    <t>2026-05-01</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
+    <t>MIL</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB </t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
     <t>STL</t>
   </si>
   <si>
+    <t xml:space="preserve">KC </t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD </t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
     <t>PIT</t>
   </si>
   <si>
-    <t xml:space="preserve">SF </t>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>NYY</t>
+  </si>
+  <si>
+    <t>TOR</t>
+  </si>
+  <si>
+    <t>MIN</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
-    <t>WAS</t>
+    <t>MIA</t>
   </si>
   <si>
     <t>NYM</t>
   </si>
   <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>MIN</t>
+    <t>LAA</t>
+  </si>
+  <si>
+    <t>TEX</t>
+  </si>
+  <si>
+    <t>DET</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>COL</t>
   </si>
   <si>
     <t>ARI</t>
   </si>
   <si>
-    <t>MIL</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>CIN</t>
+    <t>CHC</t>
   </si>
   <si>
     <t>HOU</t>
   </si>
   <si>
-    <t>BAL</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KC </t>
+    <t>BOS</t>
+  </si>
+  <si>
+    <t>CLE</t>
   </si>
   <si>
     <t>ATH</t>
@@ -564,7 +600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:49">
@@ -718,7 +754,7 @@
     </row>
     <row r="2" spans="1:49">
       <c r="A2">
-        <v>823391</v>
+        <v>822744</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -733,141 +769,141 @@
         <v>52</v>
       </c>
       <c r="F2">
-        <v>3.155</v>
+        <v>5.722</v>
       </c>
       <c r="G2">
-        <v>0.341</v>
+        <v>0.662</v>
       </c>
       <c r="H2">
-        <v>0.083</v>
+        <v>0.109</v>
       </c>
       <c r="I2">
-        <v>0.144</v>
+        <v>0.428</v>
       </c>
       <c r="J2">
-        <v>0.126</v>
+        <v>0.067</v>
       </c>
       <c r="K2">
-        <v>0.346</v>
+        <v>0.138</v>
       </c>
       <c r="L2">
-        <v>0.782</v>
+        <v>1.329</v>
       </c>
       <c r="M2">
-        <v>0.036</v>
+        <v>0.152</v>
       </c>
       <c r="N2">
-        <v>1.379</v>
+        <v>1.931</v>
       </c>
       <c r="O2">
-        <v>4.21</v>
+        <v>6.294</v>
       </c>
       <c r="P2">
-        <v>3.095</v>
+        <v>4.179</v>
       </c>
       <c r="Q2">
-        <v>9.492</v>
+        <v>8.746</v>
       </c>
       <c r="R2">
-        <v>0.478</v>
+        <v>0.251</v>
       </c>
       <c r="S2">
-        <v>0.325</v>
+        <v>0.369</v>
       </c>
       <c r="T2">
-        <v>0.145</v>
+        <v>0.235</v>
       </c>
       <c r="U2">
-        <v>0.042</v>
+        <v>0.102</v>
       </c>
       <c r="V2">
-        <v>0.007</v>
+        <v>0.035</v>
       </c>
       <c r="W2">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="X2">
-        <v>0.129</v>
+        <v>0.019</v>
       </c>
       <c r="Y2">
-        <v>0.18</v>
+        <v>0.066</v>
       </c>
       <c r="Z2">
-        <v>0.168</v>
+        <v>0.09</v>
       </c>
       <c r="AA2">
-        <v>0.144</v>
+        <v>0.114</v>
       </c>
       <c r="AB2">
-        <v>0.114</v>
+        <v>0.119</v>
       </c>
       <c r="AC2">
-        <v>0.091</v>
+        <v>0.119</v>
       </c>
       <c r="AD2">
-        <v>0.067</v>
+        <v>0.11</v>
       </c>
       <c r="AE2">
-        <v>0.048</v>
+        <v>0.089</v>
       </c>
       <c r="AF2">
-        <v>0.022</v>
+        <v>0.078</v>
       </c>
       <c r="AG2">
-        <v>0.016</v>
+        <v>0.062</v>
       </c>
       <c r="AH2">
-        <v>0.009</v>
+        <v>0.043</v>
       </c>
       <c r="AI2">
-        <v>0.004</v>
+        <v>0.027</v>
       </c>
       <c r="AJ2">
-        <v>0.003</v>
+        <v>0.021</v>
       </c>
       <c r="AK2">
-        <v>0.001</v>
+        <v>0.018</v>
       </c>
       <c r="AL2">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="AM2">
-        <v>0.002</v>
+        <v>0.015</v>
       </c>
       <c r="AN2">
-        <v>0.302</v>
+        <v>0.659</v>
       </c>
       <c r="AO2">
-        <v>0.211</v>
+        <v>0.585</v>
       </c>
       <c r="AP2">
-        <v>0.265</v>
+        <v>0.656</v>
       </c>
       <c r="AQ2">
-        <v>0.258</v>
+        <v>0.632</v>
       </c>
       <c r="AR2">
-        <v>0.287</v>
+        <v>0.621</v>
       </c>
       <c r="AS2">
-        <v>0.344</v>
+        <v>0.597</v>
       </c>
       <c r="AT2">
-        <v>0.38</v>
+        <v>0.569</v>
       </c>
       <c r="AU2">
-        <v>0.432</v>
+        <v>0.563</v>
       </c>
       <c r="AV2">
-        <v>0.451</v>
+        <v>0.541</v>
       </c>
       <c r="AW2">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="3" spans="1:49">
       <c r="A3">
-        <v>823471</v>
+        <v>822990</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
@@ -882,141 +918,141 @@
         <v>54</v>
       </c>
       <c r="F3">
-        <v>4.782</v>
+        <v>4.165</v>
       </c>
       <c r="G3">
-        <v>0.395</v>
+        <v>0.426</v>
       </c>
       <c r="H3">
-        <v>0.071</v>
+        <v>0.085</v>
       </c>
       <c r="I3">
-        <v>0.225</v>
+        <v>0.224</v>
       </c>
       <c r="J3">
-        <v>0.094</v>
+        <v>0.114</v>
       </c>
       <c r="K3">
-        <v>0.344</v>
+        <v>0.292</v>
       </c>
       <c r="L3">
-        <v>1.063</v>
+        <v>1.074</v>
       </c>
       <c r="M3">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="N3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O3">
-        <v>6.491</v>
+        <v>5.631</v>
       </c>
       <c r="P3">
-        <v>3.749</v>
+        <v>3.005</v>
       </c>
       <c r="Q3">
-        <v>7.987</v>
+        <v>9.73</v>
       </c>
       <c r="R3">
-        <v>0.35</v>
+        <v>0.358</v>
       </c>
       <c r="S3">
-        <v>0.364</v>
+        <v>0.346</v>
       </c>
       <c r="T3">
-        <v>0.188</v>
+        <v>0.198</v>
       </c>
       <c r="U3">
-        <v>0.075</v>
+        <v>0.068</v>
       </c>
       <c r="V3">
-        <v>0.016</v>
+        <v>0.023</v>
       </c>
       <c r="W3">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="X3">
-        <v>0.054</v>
+        <v>0.081</v>
       </c>
       <c r="Y3">
-        <v>0.098</v>
+        <v>0.117</v>
       </c>
       <c r="Z3">
-        <v>0.113</v>
+        <v>0.134</v>
       </c>
       <c r="AA3">
-        <v>0.123</v>
+        <v>0.136</v>
       </c>
       <c r="AB3">
-        <v>0.132</v>
+        <v>0.134</v>
       </c>
       <c r="AC3">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="AD3">
-        <v>0.097</v>
+        <v>0.086</v>
       </c>
       <c r="AE3">
-        <v>0.078</v>
+        <v>0.058</v>
       </c>
       <c r="AF3">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="AG3">
-        <v>0.046</v>
+        <v>0.035</v>
       </c>
       <c r="AH3">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="AI3">
-        <v>0.017</v>
+        <v>0.013</v>
       </c>
       <c r="AJ3">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="AK3">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="AL3">
+        <v>0.004</v>
+      </c>
+      <c r="AM3">
         <v>0.003</v>
       </c>
-      <c r="AM3">
-        <v>0.006</v>
-      </c>
       <c r="AN3">
-        <v>0.556</v>
+        <v>0.432</v>
       </c>
       <c r="AO3">
-        <v>0.517</v>
+        <v>0.452</v>
       </c>
       <c r="AP3">
-        <v>0.524</v>
+        <v>0.426</v>
       </c>
       <c r="AQ3">
-        <v>0.515</v>
+        <v>0.461</v>
       </c>
       <c r="AR3">
-        <v>0.544</v>
+        <v>0.413</v>
       </c>
       <c r="AS3">
-        <v>0.517</v>
+        <v>0.442</v>
       </c>
       <c r="AT3">
-        <v>0.49</v>
+        <v>0.457</v>
       </c>
       <c r="AU3">
-        <v>0.444</v>
+        <v>0.405</v>
       </c>
       <c r="AV3">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="AW3">
-        <v>0.098</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="4" spans="1:49">
       <c r="A4">
-        <v>823472</v>
+        <v>823066</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -1025,147 +1061,147 @@
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F4">
-        <v>3.638</v>
+        <v>5.095</v>
       </c>
       <c r="G4">
-        <v>0.399</v>
+        <v>0.633</v>
       </c>
       <c r="H4">
-        <v>0.104</v>
+        <v>0.111</v>
       </c>
       <c r="I4">
-        <v>0.181</v>
+        <v>0.38</v>
       </c>
       <c r="J4">
-        <v>0.124</v>
+        <v>0.077</v>
       </c>
       <c r="K4">
-        <v>0.279</v>
+        <v>0.144</v>
       </c>
       <c r="L4">
-        <v>0.734</v>
+        <v>0.998</v>
       </c>
       <c r="M4">
-        <v>0.097</v>
+        <v>0.119</v>
       </c>
       <c r="N4">
-        <v>1.258</v>
+        <v>1.626</v>
       </c>
       <c r="O4">
-        <v>6.223</v>
+        <v>6.875</v>
       </c>
       <c r="P4">
-        <v>2.546</v>
+        <v>3.391</v>
       </c>
       <c r="Q4">
-        <v>9.458</v>
+        <v>6.167</v>
       </c>
       <c r="R4">
-        <v>0.493</v>
+        <v>0.369</v>
       </c>
       <c r="S4">
-        <v>0.334</v>
+        <v>0.365</v>
       </c>
       <c r="T4">
+        <v>0.191</v>
+      </c>
+      <c r="U4">
+        <v>0.055</v>
+      </c>
+      <c r="V4">
+        <v>0.016</v>
+      </c>
+      <c r="W4">
+        <v>0.004</v>
+      </c>
+      <c r="X4">
+        <v>0.038</v>
+      </c>
+      <c r="Y4">
+        <v>0.074</v>
+      </c>
+      <c r="Z4">
+        <v>0.094</v>
+      </c>
+      <c r="AA4">
         <v>0.126</v>
       </c>
-      <c r="U4">
-        <v>0.039</v>
-      </c>
-      <c r="V4">
+      <c r="AB4">
+        <v>0.136</v>
+      </c>
+      <c r="AC4">
+        <v>0.131</v>
+      </c>
+      <c r="AD4">
+        <v>0.113</v>
+      </c>
+      <c r="AE4">
+        <v>0.096</v>
+      </c>
+      <c r="AF4">
+        <v>0.058</v>
+      </c>
+      <c r="AG4">
+        <v>0.045</v>
+      </c>
+      <c r="AH4">
+        <v>0.032</v>
+      </c>
+      <c r="AI4">
+        <v>0.02</v>
+      </c>
+      <c r="AJ4">
+        <v>0.016</v>
+      </c>
+      <c r="AK4">
         <v>0.007</v>
       </c>
-      <c r="W4">
-        <v>0.001</v>
-      </c>
-      <c r="X4">
-        <v>0.104</v>
-      </c>
-      <c r="Y4">
-        <v>0.143</v>
-      </c>
-      <c r="Z4">
-        <v>0.158</v>
-      </c>
-      <c r="AA4">
-        <v>0.145</v>
-      </c>
-      <c r="AB4">
-        <v>0.124</v>
-      </c>
-      <c r="AC4">
-        <v>0.101</v>
-      </c>
-      <c r="AD4">
-        <v>0.072</v>
-      </c>
-      <c r="AE4">
-        <v>0.053</v>
-      </c>
-      <c r="AF4">
-        <v>0.038</v>
-      </c>
-      <c r="AG4">
-        <v>0.025</v>
-      </c>
-      <c r="AH4">
-        <v>0.018</v>
-      </c>
-      <c r="AI4">
-        <v>0.008</v>
-      </c>
-      <c r="AJ4">
-        <v>0.007</v>
-      </c>
-      <c r="AK4">
-        <v>0.001</v>
-      </c>
       <c r="AL4">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AM4">
-        <v>0.002</v>
+        <v>0.009</v>
       </c>
       <c r="AN4">
-        <v>0.34</v>
+        <v>0.608</v>
       </c>
       <c r="AO4">
-        <v>0.364</v>
+        <v>0.536</v>
       </c>
       <c r="AP4">
-        <v>0.361</v>
+        <v>0.574</v>
       </c>
       <c r="AQ4">
-        <v>0.374</v>
+        <v>0.545</v>
       </c>
       <c r="AR4">
-        <v>0.348</v>
+        <v>0.55</v>
       </c>
       <c r="AS4">
-        <v>0.386</v>
+        <v>0.553</v>
       </c>
       <c r="AT4">
-        <v>0.409</v>
+        <v>0.498</v>
       </c>
       <c r="AU4">
-        <v>0.412</v>
+        <v>0.459</v>
       </c>
       <c r="AV4">
-        <v>0.393</v>
+        <v>0.467</v>
       </c>
       <c r="AW4">
-        <v>0.151</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="5" spans="1:49">
       <c r="A5">
-        <v>823634</v>
+        <v>823146</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
@@ -1174,106 +1210,106 @@
         <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>3.626</v>
+        <v>3.033</v>
       </c>
       <c r="G5">
-        <v>0.395</v>
+        <v>0.364</v>
       </c>
       <c r="H5">
-        <v>0.09</v>
+        <v>0.087</v>
       </c>
       <c r="I5">
-        <v>0.185</v>
+        <v>0.155</v>
       </c>
       <c r="J5">
-        <v>0.112</v>
+        <v>0.12</v>
       </c>
       <c r="K5">
         <v>0.295</v>
       </c>
       <c r="L5">
-        <v>0.918</v>
+        <v>0.929</v>
       </c>
       <c r="M5">
-        <v>0.095</v>
+        <v>0.113</v>
       </c>
       <c r="N5">
-        <v>1.306</v>
+        <v>1.143</v>
       </c>
       <c r="O5">
-        <v>4.724</v>
+        <v>4.435</v>
       </c>
       <c r="P5">
-        <v>3.523</v>
+        <v>2.264</v>
       </c>
       <c r="Q5">
-        <v>9.318</v>
+        <v>9.445</v>
       </c>
       <c r="R5">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="S5">
-        <v>0.371</v>
+        <v>0.355</v>
       </c>
       <c r="T5">
-        <v>0.152</v>
+        <v>0.164</v>
       </c>
       <c r="U5">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="V5">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="W5">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="X5">
-        <v>0.091</v>
+        <v>0.133</v>
       </c>
       <c r="Y5">
-        <v>0.142</v>
+        <v>0.167</v>
       </c>
       <c r="Z5">
+        <v>0.185</v>
+      </c>
+      <c r="AA5">
         <v>0.156</v>
       </c>
-      <c r="AA5">
-        <v>0.154</v>
-      </c>
       <c r="AB5">
-        <v>0.136</v>
+        <v>0.127</v>
       </c>
       <c r="AC5">
-        <v>0.103</v>
+        <v>0.082</v>
       </c>
       <c r="AD5">
-        <v>0.074</v>
+        <v>0.062</v>
       </c>
       <c r="AE5">
-        <v>0.056</v>
+        <v>0.034</v>
       </c>
       <c r="AF5">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="AG5">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="AH5">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="AI5">
         <v>0.005</v>
       </c>
       <c r="AJ5">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AK5">
-        <v>0.003</v>
+        <v>0.0</v>
       </c>
       <c r="AL5">
         <v>0.001</v>
@@ -1282,39 +1318,39 @@
         <v>0.001</v>
       </c>
       <c r="AN5">
-        <v>0.415</v>
+        <v>0.33</v>
       </c>
       <c r="AO5">
-        <v>0.4</v>
+        <v>0.269</v>
       </c>
       <c r="AP5">
-        <v>0.384</v>
+        <v>0.286</v>
       </c>
       <c r="AQ5">
-        <v>0.38</v>
+        <v>0.284</v>
       </c>
       <c r="AR5">
-        <v>0.342</v>
+        <v>0.287</v>
       </c>
       <c r="AS5">
-        <v>0.406</v>
+        <v>0.34</v>
       </c>
       <c r="AT5">
-        <v>0.37</v>
+        <v>0.333</v>
       </c>
       <c r="AU5">
-        <v>0.355</v>
+        <v>0.337</v>
       </c>
       <c r="AV5">
-        <v>0.353</v>
+        <v>0.374</v>
       </c>
       <c r="AW5">
-        <v>0.14</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="6" spans="1:49">
       <c r="A6">
-        <v>823714</v>
+        <v>823309</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
@@ -1323,97 +1359,97 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F6">
-        <v>4.382</v>
+        <v>4.149</v>
       </c>
       <c r="G6">
-        <v>0.518</v>
+        <v>0.416</v>
       </c>
       <c r="H6">
-        <v>0.101</v>
+        <v>0.094</v>
       </c>
       <c r="I6">
-        <v>0.29</v>
+        <v>0.205</v>
       </c>
       <c r="J6">
-        <v>0.113</v>
+        <v>0.109</v>
       </c>
       <c r="K6">
-        <v>0.203</v>
+        <v>0.295</v>
       </c>
       <c r="L6">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="M6">
-        <v>0.122</v>
+        <v>0.07</v>
       </c>
       <c r="N6">
-        <v>1.874</v>
+        <v>1.357</v>
       </c>
       <c r="O6">
-        <v>5.498</v>
+        <v>4.803</v>
       </c>
       <c r="P6">
-        <v>2.737</v>
+        <v>3.743</v>
       </c>
       <c r="Q6">
-        <v>7.147</v>
+        <v>7.389</v>
       </c>
       <c r="R6">
-        <v>0.351</v>
+        <v>0.32</v>
       </c>
       <c r="S6">
-        <v>0.363</v>
+        <v>0.358</v>
       </c>
       <c r="T6">
-        <v>0.192</v>
+        <v>0.21</v>
       </c>
       <c r="U6">
-        <v>0.067</v>
+        <v>0.085</v>
       </c>
       <c r="V6">
         <v>0.021</v>
       </c>
       <c r="W6">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="X6">
-        <v>0.054</v>
+        <v>0.064</v>
       </c>
       <c r="Y6">
-        <v>0.101</v>
+        <v>0.114</v>
       </c>
       <c r="Z6">
-        <v>0.136</v>
+        <v>0.154</v>
       </c>
       <c r="AA6">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AB6">
-        <v>0.139</v>
+        <v>0.124</v>
       </c>
       <c r="AC6">
         <v>0.119</v>
       </c>
       <c r="AD6">
-        <v>0.103</v>
+        <v>0.083</v>
       </c>
       <c r="AE6">
-        <v>0.066</v>
+        <v>0.076</v>
       </c>
       <c r="AF6">
-        <v>0.057</v>
+        <v>0.04</v>
       </c>
       <c r="AG6">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="AH6">
-        <v>0.024</v>
+        <v>0.02</v>
       </c>
       <c r="AI6">
         <v>0.011</v>
@@ -1422,48 +1458,48 @@
         <v>0.008</v>
       </c>
       <c r="AK6">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="AL6">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AM6">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AN6">
-        <v>0.504</v>
+        <v>0.522</v>
       </c>
       <c r="AO6">
-        <v>0.437</v>
+        <v>0.448</v>
       </c>
       <c r="AP6">
-        <v>0.454</v>
+        <v>0.469</v>
       </c>
       <c r="AQ6">
-        <v>0.477</v>
+        <v>0.463</v>
       </c>
       <c r="AR6">
-        <v>0.449</v>
+        <v>0.453</v>
       </c>
       <c r="AS6">
-        <v>0.454</v>
+        <v>0.417</v>
       </c>
       <c r="AT6">
-        <v>0.442</v>
+        <v>0.411</v>
       </c>
       <c r="AU6">
-        <v>0.437</v>
+        <v>0.393</v>
       </c>
       <c r="AV6">
-        <v>0.466</v>
+        <v>0.349</v>
       </c>
       <c r="AW6">
-        <v>0.144</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="7" spans="1:49">
       <c r="A7">
-        <v>823795</v>
+        <v>823389</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -1472,147 +1508,147 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>3.936</v>
+        <v>4.275</v>
       </c>
       <c r="G7">
-        <v>0.388</v>
+        <v>0.454</v>
       </c>
       <c r="H7">
-        <v>0.077</v>
+        <v>0.094</v>
       </c>
       <c r="I7">
-        <v>0.196</v>
+        <v>0.234</v>
       </c>
       <c r="J7">
-        <v>0.12</v>
+        <v>0.103</v>
       </c>
       <c r="K7">
-        <v>0.307</v>
+        <v>0.253</v>
       </c>
       <c r="L7">
-        <v>1.298</v>
+        <v>0.975</v>
       </c>
       <c r="M7">
-        <v>0.158</v>
+        <v>0.159</v>
       </c>
       <c r="N7">
-        <v>1.295</v>
+        <v>1.508</v>
       </c>
       <c r="O7">
-        <v>4.812</v>
+        <v>4.819</v>
       </c>
       <c r="P7">
-        <v>2.391</v>
+        <v>4.193</v>
       </c>
       <c r="Q7">
-        <v>8.227</v>
+        <v>8.68</v>
       </c>
       <c r="R7">
-        <v>0.289</v>
+        <v>0.379</v>
       </c>
       <c r="S7">
-        <v>0.335</v>
+        <v>0.371</v>
       </c>
       <c r="T7">
-        <v>0.225</v>
+        <v>0.171</v>
       </c>
       <c r="U7">
-        <v>0.102</v>
+        <v>0.059</v>
       </c>
       <c r="V7">
-        <v>0.038</v>
+        <v>0.015</v>
       </c>
       <c r="W7">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="X7">
-        <v>0.077</v>
+        <v>0.071</v>
       </c>
       <c r="Y7">
-        <v>0.132</v>
+        <v>0.105</v>
       </c>
       <c r="Z7">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="AA7">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="AB7">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AC7">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="AD7">
-        <v>0.075</v>
+        <v>0.09</v>
       </c>
       <c r="AE7">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="AF7">
-        <v>0.042</v>
+        <v>0.055</v>
       </c>
       <c r="AG7">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
       <c r="AH7">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="AI7">
-        <v>0.009</v>
+        <v>0.017</v>
       </c>
       <c r="AJ7">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="AK7">
+        <v>0.005</v>
+      </c>
+      <c r="AL7">
         <v>0.003</v>
-      </c>
-      <c r="AL7">
-        <v>0.002</v>
       </c>
       <c r="AM7">
         <v>0.004</v>
       </c>
       <c r="AN7">
-        <v>0.42</v>
+        <v>0.439</v>
       </c>
       <c r="AO7">
-        <v>0.336</v>
+        <v>0.441</v>
       </c>
       <c r="AP7">
-        <v>0.413</v>
+        <v>0.44</v>
       </c>
       <c r="AQ7">
-        <v>0.371</v>
+        <v>0.441</v>
       </c>
       <c r="AR7">
-        <v>0.415</v>
+        <v>0.454</v>
       </c>
       <c r="AS7">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="AT7">
-        <v>0.437</v>
+        <v>0.451</v>
       </c>
       <c r="AU7">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="AV7">
-        <v>0.448</v>
+        <v>0.436</v>
       </c>
       <c r="AW7">
-        <v>0.135</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="8" spans="1:49">
       <c r="A8">
-        <v>824524</v>
+        <v>823557</v>
       </c>
       <c r="B8" t="s">
         <v>49</v>
@@ -1621,147 +1657,147 @@
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8">
-        <v>4.817</v>
+        <v>4.487</v>
       </c>
       <c r="G8">
-        <v>0.466</v>
+        <v>0.426</v>
       </c>
       <c r="H8">
-        <v>0.095</v>
+        <v>0.078</v>
       </c>
       <c r="I8">
-        <v>0.256</v>
+        <v>0.232</v>
       </c>
       <c r="J8">
-        <v>0.103</v>
+        <v>0.116</v>
       </c>
       <c r="K8">
-        <v>0.256</v>
+        <v>0.277</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.398</v>
       </c>
       <c r="M8">
-        <v>0.156</v>
+        <v>0.094</v>
       </c>
       <c r="N8">
-        <v>1.656</v>
+        <v>1.362</v>
       </c>
       <c r="O8">
-        <v>5.881</v>
+        <v>5.324</v>
       </c>
       <c r="P8">
-        <v>2.989</v>
+        <v>3.265</v>
       </c>
       <c r="Q8">
-        <v>9.03</v>
+        <v>9.325</v>
       </c>
       <c r="R8">
-        <v>0.283</v>
+        <v>0.261</v>
       </c>
       <c r="S8">
-        <v>0.347</v>
+        <v>0.34</v>
       </c>
       <c r="T8">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="U8">
-        <v>0.099</v>
+        <v>0.111</v>
       </c>
       <c r="V8">
-        <v>0.036</v>
+        <v>0.047</v>
       </c>
       <c r="W8">
+        <v>0.016</v>
+      </c>
+      <c r="X8">
+        <v>0.059</v>
+      </c>
+      <c r="Y8">
+        <v>0.101</v>
+      </c>
+      <c r="Z8">
+        <v>0.131</v>
+      </c>
+      <c r="AA8">
+        <v>0.147</v>
+      </c>
+      <c r="AB8">
+        <v>0.128</v>
+      </c>
+      <c r="AC8">
+        <v>0.11</v>
+      </c>
+      <c r="AD8">
+        <v>0.09</v>
+      </c>
+      <c r="AE8">
+        <v>0.075</v>
+      </c>
+      <c r="AF8">
+        <v>0.053</v>
+      </c>
+      <c r="AG8">
+        <v>0.037</v>
+      </c>
+      <c r="AH8">
+        <v>0.026</v>
+      </c>
+      <c r="AI8">
+        <v>0.017</v>
+      </c>
+      <c r="AJ8">
         <v>0.012</v>
-      </c>
-      <c r="X8">
-        <v>0.044</v>
-      </c>
-      <c r="Y8">
-        <v>0.078</v>
-      </c>
-      <c r="Z8">
-        <v>0.117</v>
-      </c>
-      <c r="AA8">
-        <v>0.143</v>
-      </c>
-      <c r="AB8">
-        <v>0.126</v>
-      </c>
-      <c r="AC8">
-        <v>0.118</v>
-      </c>
-      <c r="AD8">
-        <v>0.109</v>
-      </c>
-      <c r="AE8">
-        <v>0.087</v>
-      </c>
-      <c r="AF8">
-        <v>0.062</v>
-      </c>
-      <c r="AG8">
-        <v>0.047</v>
-      </c>
-      <c r="AH8">
-        <v>0.028</v>
-      </c>
-      <c r="AI8">
-        <v>0.018</v>
-      </c>
-      <c r="AJ8">
-        <v>0.01</v>
       </c>
       <c r="AK8">
         <v>0.005</v>
       </c>
       <c r="AL8">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AM8">
         <v>0.005</v>
       </c>
       <c r="AN8">
-        <v>0.59</v>
+        <v>0.507</v>
       </c>
       <c r="AO8">
-        <v>0.524</v>
+        <v>0.42</v>
       </c>
       <c r="AP8">
-        <v>0.574</v>
+        <v>0.484</v>
       </c>
       <c r="AQ8">
-        <v>0.514</v>
+        <v>0.451</v>
       </c>
       <c r="AR8">
-        <v>0.534</v>
+        <v>0.484</v>
       </c>
       <c r="AS8">
-        <v>0.509</v>
+        <v>0.477</v>
       </c>
       <c r="AT8">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="AU8">
-        <v>0.451</v>
+        <v>0.488</v>
       </c>
       <c r="AV8">
-        <v>0.424</v>
+        <v>0.496</v>
       </c>
       <c r="AW8">
-        <v>0.133</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="9" spans="1:49">
       <c r="A9">
-        <v>824848</v>
+        <v>823713</v>
       </c>
       <c r="B9" t="s">
         <v>49</v>
@@ -1770,147 +1806,147 @@
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F9">
-        <v>5.105</v>
+        <v>4.481</v>
       </c>
       <c r="G9">
-        <v>0.468</v>
+        <v>0.439</v>
       </c>
       <c r="H9">
-        <v>0.09</v>
+        <v>0.092</v>
       </c>
       <c r="I9">
-        <v>0.275</v>
+        <v>0.228</v>
       </c>
       <c r="J9">
-        <v>0.112</v>
+        <v>0.096</v>
       </c>
       <c r="K9">
-        <v>0.262</v>
+        <v>0.301</v>
       </c>
       <c r="L9">
-        <v>1.038</v>
+        <v>0.964</v>
       </c>
       <c r="M9">
-        <v>0.085</v>
+        <v>0.129</v>
       </c>
       <c r="N9">
-        <v>1.787</v>
+        <v>1.919</v>
       </c>
       <c r="O9">
-        <v>6.247</v>
+        <v>5.602</v>
       </c>
       <c r="P9">
-        <v>3.973</v>
+        <v>3.186</v>
       </c>
       <c r="Q9">
-        <v>7.194</v>
+        <v>6.855</v>
       </c>
       <c r="R9">
-        <v>0.366</v>
+        <v>0.376</v>
       </c>
       <c r="S9">
-        <v>0.348</v>
+        <v>0.371</v>
       </c>
       <c r="T9">
-        <v>0.192</v>
+        <v>0.183</v>
       </c>
       <c r="U9">
-        <v>0.072</v>
+        <v>0.055</v>
       </c>
       <c r="V9">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="W9">
+        <v>0.002</v>
+      </c>
+      <c r="X9">
+        <v>0.055</v>
+      </c>
+      <c r="Y9">
+        <v>0.098</v>
+      </c>
+      <c r="Z9">
+        <v>0.125</v>
+      </c>
+      <c r="AA9">
+        <v>0.154</v>
+      </c>
+      <c r="AB9">
+        <v>0.132</v>
+      </c>
+      <c r="AC9">
+        <v>0.113</v>
+      </c>
+      <c r="AD9">
+        <v>0.093</v>
+      </c>
+      <c r="AE9">
+        <v>0.075</v>
+      </c>
+      <c r="AF9">
+        <v>0.051</v>
+      </c>
+      <c r="AG9">
+        <v>0.039</v>
+      </c>
+      <c r="AH9">
+        <v>0.028</v>
+      </c>
+      <c r="AI9">
+        <v>0.015</v>
+      </c>
+      <c r="AJ9">
+        <v>0.009</v>
+      </c>
+      <c r="AK9">
+        <v>0.006</v>
+      </c>
+      <c r="AL9">
+        <v>0.002</v>
+      </c>
+      <c r="AM9">
         <v>0.005</v>
       </c>
-      <c r="X9">
-        <v>0.039</v>
-      </c>
-      <c r="Y9">
-        <v>0.073</v>
-      </c>
-      <c r="Z9">
-        <v>0.106</v>
-      </c>
-      <c r="AA9">
-        <v>0.126</v>
-      </c>
-      <c r="AB9">
-        <v>0.137</v>
-      </c>
-      <c r="AC9">
-        <v>0.112</v>
-      </c>
-      <c r="AD9">
-        <v>0.103</v>
-      </c>
-      <c r="AE9">
-        <v>0.087</v>
-      </c>
-      <c r="AF9">
-        <v>0.075</v>
-      </c>
-      <c r="AG9">
-        <v>0.048</v>
-      </c>
-      <c r="AH9">
-        <v>0.039</v>
-      </c>
-      <c r="AI9">
-        <v>0.02</v>
-      </c>
-      <c r="AJ9">
-        <v>0.015</v>
-      </c>
-      <c r="AK9">
-        <v>0.008</v>
-      </c>
-      <c r="AL9">
-        <v>0.005</v>
-      </c>
-      <c r="AM9">
-        <v>0.007</v>
-      </c>
       <c r="AN9">
-        <v>0.686</v>
+        <v>0.542</v>
       </c>
       <c r="AO9">
-        <v>0.598</v>
+        <v>0.438</v>
       </c>
       <c r="AP9">
-        <v>0.643</v>
+        <v>0.508</v>
       </c>
       <c r="AQ9">
-        <v>0.557</v>
+        <v>0.465</v>
       </c>
       <c r="AR9">
-        <v>0.508</v>
+        <v>0.453</v>
       </c>
       <c r="AS9">
-        <v>0.477</v>
+        <v>0.489</v>
       </c>
       <c r="AT9">
-        <v>0.482</v>
+        <v>0.475</v>
       </c>
       <c r="AU9">
-        <v>0.446</v>
+        <v>0.452</v>
       </c>
       <c r="AV9">
-        <v>0.466</v>
+        <v>0.417</v>
       </c>
       <c r="AW9">
-        <v>0.106</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="10" spans="1:49">
       <c r="A10">
-        <v>824850</v>
+        <v>823877</v>
       </c>
       <c r="B10" t="s">
         <v>49</v>
@@ -1919,103 +1955,103 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F10">
-        <v>4.558</v>
+        <v>4.51</v>
       </c>
       <c r="G10">
-        <v>0.36</v>
+        <v>0.61</v>
       </c>
       <c r="H10">
-        <v>0.077</v>
+        <v>0.114</v>
       </c>
       <c r="I10">
-        <v>0.178</v>
+        <v>0.349</v>
       </c>
       <c r="J10">
-        <v>0.105</v>
+        <v>0.086</v>
       </c>
       <c r="K10">
-        <v>0.359</v>
+        <v>0.137</v>
       </c>
       <c r="L10">
-        <v>1.23</v>
+        <v>1.054</v>
       </c>
       <c r="M10">
-        <v>0.072</v>
+        <v>0.152</v>
       </c>
       <c r="N10">
-        <v>1.706</v>
+        <v>1.826</v>
       </c>
       <c r="O10">
-        <v>5.471</v>
+        <v>4.955</v>
       </c>
       <c r="P10">
-        <v>3.058</v>
+        <v>3.871</v>
       </c>
       <c r="Q10">
-        <v>7.159</v>
+        <v>9.044</v>
       </c>
       <c r="R10">
-        <v>0.302</v>
+        <v>0.35</v>
       </c>
       <c r="S10">
-        <v>0.346</v>
+        <v>0.367</v>
       </c>
       <c r="T10">
-        <v>0.222</v>
+        <v>0.192</v>
       </c>
       <c r="U10">
-        <v>0.093</v>
+        <v>0.066</v>
       </c>
       <c r="V10">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="W10">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="X10">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="Y10">
-        <v>0.092</v>
+        <v>0.1</v>
       </c>
       <c r="Z10">
-        <v>0.128</v>
+        <v>0.12</v>
       </c>
       <c r="AA10">
-        <v>0.141</v>
+        <v>0.147</v>
       </c>
       <c r="AB10">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
       <c r="AC10">
-        <v>0.125</v>
+        <v>0.116</v>
       </c>
       <c r="AD10">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="AE10">
         <v>0.067</v>
       </c>
       <c r="AF10">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AG10">
-        <v>0.037</v>
+        <v>0.042</v>
       </c>
       <c r="AH10">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="AI10">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AJ10">
-        <v>0.013</v>
+        <v>0.008</v>
       </c>
       <c r="AK10">
         <v>0.005</v>
@@ -2027,39 +2063,39 @@
         <v>0.005</v>
       </c>
       <c r="AN10">
-        <v>0.531</v>
+        <v>0.56</v>
       </c>
       <c r="AO10">
-        <v>0.458</v>
+        <v>0.43</v>
       </c>
       <c r="AP10">
-        <v>0.521</v>
+        <v>0.501</v>
       </c>
       <c r="AQ10">
-        <v>0.475</v>
+        <v>0.482</v>
       </c>
       <c r="AR10">
-        <v>0.525</v>
+        <v>0.461</v>
       </c>
       <c r="AS10">
-        <v>0.42</v>
+        <v>0.479</v>
       </c>
       <c r="AT10">
-        <v>0.474</v>
+        <v>0.446</v>
       </c>
       <c r="AU10">
-        <v>0.457</v>
+        <v>0.472</v>
       </c>
       <c r="AV10">
-        <v>0.472</v>
+        <v>0.405</v>
       </c>
       <c r="AW10">
-        <v>0.117</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="11" spans="1:49">
       <c r="A11">
-        <v>824929</v>
+        <v>824041</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -2068,147 +2104,147 @@
         <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F11">
-        <v>5.619</v>
+        <v>5.316</v>
       </c>
       <c r="G11">
-        <v>0.507</v>
+        <v>0.491</v>
       </c>
       <c r="H11">
-        <v>0.083</v>
+        <v>0.097</v>
       </c>
       <c r="I11">
-        <v>0.319</v>
+        <v>0.285</v>
       </c>
       <c r="J11">
-        <v>0.086</v>
+        <v>0.089</v>
       </c>
       <c r="K11">
-        <v>0.259</v>
+        <v>0.254</v>
       </c>
       <c r="L11">
-        <v>1.307</v>
+        <v>1.275</v>
       </c>
       <c r="M11">
-        <v>0.158</v>
+        <v>0.068</v>
       </c>
       <c r="N11">
-        <v>1.728</v>
+        <v>1.571</v>
       </c>
       <c r="O11">
-        <v>6.265</v>
+        <v>5.593</v>
       </c>
       <c r="P11">
-        <v>4.125</v>
+        <v>5.135</v>
       </c>
       <c r="Q11">
-        <v>8.591</v>
+        <v>9.583</v>
       </c>
       <c r="R11">
-        <v>0.28</v>
+        <v>0.292</v>
       </c>
       <c r="S11">
-        <v>0.341</v>
+        <v>0.355</v>
       </c>
       <c r="T11">
-        <v>0.237</v>
+        <v>0.208</v>
       </c>
       <c r="U11">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="V11">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="W11">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="X11">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="Y11">
-        <v>0.067</v>
+        <v>0.076</v>
       </c>
       <c r="Z11">
-        <v>0.099</v>
+        <v>0.094</v>
       </c>
       <c r="AA11">
+        <v>0.116</v>
+      </c>
+      <c r="AB11">
+        <v>0.125</v>
+      </c>
+      <c r="AC11">
         <v>0.119</v>
       </c>
-      <c r="AB11">
+      <c r="AD11">
         <v>0.109</v>
-      </c>
-      <c r="AC11">
-        <v>0.107</v>
-      </c>
-      <c r="AD11">
-        <v>0.107</v>
       </c>
       <c r="AE11">
         <v>0.091</v>
       </c>
       <c r="AF11">
-        <v>0.074</v>
+        <v>0.071</v>
       </c>
       <c r="AG11">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
       <c r="AH11">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="AI11">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
       <c r="AJ11">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="AK11">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="AL11">
+        <v>0.007</v>
+      </c>
+      <c r="AM11">
         <v>0.013</v>
       </c>
-      <c r="AM11">
-        <v>0.015</v>
-      </c>
       <c r="AN11">
-        <v>0.65</v>
+        <v>0.647</v>
       </c>
       <c r="AO11">
-        <v>0.554</v>
+        <v>0.532</v>
       </c>
       <c r="AP11">
-        <v>0.605</v>
+        <v>0.541</v>
       </c>
       <c r="AQ11">
-        <v>0.589</v>
+        <v>0.577</v>
       </c>
       <c r="AR11">
-        <v>0.592</v>
+        <v>0.551</v>
       </c>
       <c r="AS11">
-        <v>0.574</v>
+        <v>0.557</v>
       </c>
       <c r="AT11">
-        <v>0.588</v>
+        <v>0.544</v>
       </c>
       <c r="AU11">
-        <v>0.598</v>
+        <v>0.53</v>
       </c>
       <c r="AV11">
-        <v>0.583</v>
+        <v>0.552</v>
       </c>
       <c r="AW11">
-        <v>0.148</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="12" spans="1:49">
       <c r="A12">
-        <v>825016</v>
+        <v>824287</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -2217,848 +2253,848 @@
         <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F12">
-        <v>4.742</v>
+        <v>5.329</v>
       </c>
       <c r="G12">
-        <v>0.369</v>
+        <v>0.486</v>
       </c>
       <c r="H12">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="I12">
-        <v>0.193</v>
+        <v>0.289</v>
       </c>
       <c r="J12">
-        <v>0.104</v>
+        <v>0.088</v>
       </c>
       <c r="K12">
-        <v>0.365</v>
+        <v>0.254</v>
       </c>
       <c r="L12">
-        <v>1.346</v>
+        <v>0.928</v>
       </c>
       <c r="M12">
-        <v>0.173</v>
+        <v>0.114</v>
       </c>
       <c r="N12">
-        <v>1.846</v>
+        <v>1.845</v>
       </c>
       <c r="O12">
-        <v>4.778</v>
+        <v>5.819</v>
       </c>
       <c r="P12">
-        <v>3.309</v>
+        <v>5.219</v>
       </c>
       <c r="Q12">
-        <v>6.737</v>
+        <v>8.985</v>
       </c>
       <c r="R12">
-        <v>0.268</v>
+        <v>0.401</v>
       </c>
       <c r="S12">
-        <v>0.351</v>
+        <v>0.355</v>
       </c>
       <c r="T12">
-        <v>0.22</v>
+        <v>0.176</v>
       </c>
       <c r="U12">
-        <v>0.108</v>
+        <v>0.052</v>
       </c>
       <c r="V12">
+        <v>0.014</v>
+      </c>
+      <c r="W12">
+        <v>0.002</v>
+      </c>
+      <c r="X12">
+        <v>0.035</v>
+      </c>
+      <c r="Y12">
+        <v>0.074</v>
+      </c>
+      <c r="Z12">
+        <v>0.101</v>
+      </c>
+      <c r="AA12">
+        <v>0.119</v>
+      </c>
+      <c r="AB12">
+        <v>0.121</v>
+      </c>
+      <c r="AC12">
+        <v>0.114</v>
+      </c>
+      <c r="AD12">
+        <v>0.112</v>
+      </c>
+      <c r="AE12">
+        <v>0.088</v>
+      </c>
+      <c r="AF12">
+        <v>0.069</v>
+      </c>
+      <c r="AG12">
+        <v>0.056</v>
+      </c>
+      <c r="AH12">
         <v>0.039</v>
       </c>
-      <c r="W12">
-        <v>0.014</v>
-      </c>
-      <c r="X12">
-        <v>0.048</v>
-      </c>
-      <c r="Y12">
-        <v>0.089</v>
-      </c>
-      <c r="Z12">
-        <v>0.126</v>
-      </c>
-      <c r="AA12">
-        <v>0.133</v>
-      </c>
-      <c r="AB12">
-        <v>0.132</v>
-      </c>
-      <c r="AC12">
-        <v>0.122</v>
-      </c>
-      <c r="AD12">
-        <v>0.096</v>
-      </c>
-      <c r="AE12">
-        <v>0.077</v>
-      </c>
-      <c r="AF12">
-        <v>0.049</v>
-      </c>
-      <c r="AG12">
-        <v>0.046</v>
-      </c>
-      <c r="AH12">
-        <v>0.028</v>
-      </c>
       <c r="AI12">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="AJ12">
         <v>0.015</v>
       </c>
       <c r="AK12">
+        <v>0.012</v>
+      </c>
+      <c r="AL12">
         <v>0.007</v>
       </c>
-      <c r="AL12">
-        <v>0.004</v>
-      </c>
       <c r="AM12">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="AN12">
-        <v>0.5</v>
+        <v>0.652</v>
       </c>
       <c r="AO12">
-        <v>0.438</v>
+        <v>0.647</v>
       </c>
       <c r="AP12">
-        <v>0.491</v>
+        <v>0.605</v>
       </c>
       <c r="AQ12">
-        <v>0.443</v>
+        <v>0.579</v>
       </c>
       <c r="AR12">
-        <v>0.537</v>
+        <v>0.53</v>
       </c>
       <c r="AS12">
-        <v>0.513</v>
+        <v>0.523</v>
       </c>
       <c r="AT12">
-        <v>0.51</v>
+        <v>0.523</v>
       </c>
       <c r="AU12">
-        <v>0.522</v>
+        <v>0.492</v>
       </c>
       <c r="AV12">
-        <v>0.572</v>
+        <v>0.487</v>
       </c>
       <c r="AW12">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="13" spans="1:49">
       <c r="A13">
-        <v>823391</v>
+        <v>824366</v>
       </c>
       <c r="B13" t="s">
         <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="F13">
-        <v>4.49</v>
+        <v>7.148</v>
       </c>
       <c r="G13">
-        <v>0.659</v>
+        <v>0.585</v>
       </c>
       <c r="H13">
-        <v>0.126</v>
+        <v>0.095</v>
       </c>
       <c r="I13">
-        <v>0.346</v>
+        <v>0.393</v>
       </c>
       <c r="J13">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="K13">
-        <v>0.144</v>
+        <v>0.213</v>
       </c>
       <c r="L13">
-        <v>0.861</v>
+        <v>1.626</v>
       </c>
       <c r="M13">
-        <v>0.117</v>
+        <v>0.185</v>
       </c>
       <c r="N13">
-        <v>1.74</v>
+        <v>2.386</v>
       </c>
       <c r="O13">
-        <v>5.593</v>
+        <v>6.993</v>
       </c>
       <c r="P13">
-        <v>3.508</v>
+        <v>4.092</v>
       </c>
       <c r="Q13">
-        <v>6.87</v>
+        <v>5.674</v>
       </c>
       <c r="R13">
-        <v>0.409</v>
+        <v>0.208</v>
       </c>
       <c r="S13">
-        <v>0.387</v>
+        <v>0.306</v>
       </c>
       <c r="T13">
-        <v>0.151</v>
+        <v>0.261</v>
       </c>
       <c r="U13">
-        <v>0.041</v>
+        <v>0.137</v>
       </c>
       <c r="V13">
-        <v>0.008</v>
+        <v>0.064</v>
       </c>
       <c r="W13">
-        <v>0.003</v>
+        <v>0.023</v>
       </c>
       <c r="X13">
-        <v>0.047</v>
+        <v>0.015</v>
       </c>
       <c r="Y13">
-        <v>0.091</v>
+        <v>0.037</v>
       </c>
       <c r="Z13">
-        <v>0.133</v>
+        <v>0.048</v>
       </c>
       <c r="AA13">
-        <v>0.144</v>
+        <v>0.073</v>
       </c>
       <c r="AB13">
-        <v>0.147</v>
+        <v>0.086</v>
       </c>
       <c r="AC13">
-        <v>0.126</v>
+        <v>0.107</v>
       </c>
       <c r="AD13">
-        <v>0.095</v>
+        <v>0.106</v>
       </c>
       <c r="AE13">
-        <v>0.068</v>
+        <v>0.107</v>
       </c>
       <c r="AF13">
-        <v>0.055</v>
+        <v>0.09</v>
       </c>
       <c r="AG13">
-        <v>0.031</v>
+        <v>0.084</v>
       </c>
       <c r="AH13">
-        <v>0.024</v>
+        <v>0.061</v>
       </c>
       <c r="AI13">
-        <v>0.015</v>
+        <v>0.056</v>
       </c>
       <c r="AJ13">
-        <v>0.009</v>
+        <v>0.039</v>
       </c>
       <c r="AK13">
-        <v>0.006</v>
+        <v>0.027</v>
       </c>
       <c r="AL13">
-        <v>0.003</v>
+        <v>0.022</v>
       </c>
       <c r="AM13">
-        <v>0.005</v>
+        <v>0.042</v>
       </c>
       <c r="AN13">
-        <v>0.497</v>
+        <v>0.894</v>
       </c>
       <c r="AO13">
-        <v>0.478</v>
+        <v>0.804</v>
       </c>
       <c r="AP13">
-        <v>0.503</v>
+        <v>0.823</v>
       </c>
       <c r="AQ13">
-        <v>0.498</v>
+        <v>0.777</v>
       </c>
       <c r="AR13">
-        <v>0.516</v>
+        <v>0.742</v>
       </c>
       <c r="AS13">
-        <v>0.506</v>
+        <v>0.737</v>
       </c>
       <c r="AT13">
-        <v>0.518</v>
+        <v>0.667</v>
       </c>
       <c r="AU13">
-        <v>0.535</v>
+        <v>0.682</v>
       </c>
       <c r="AV13">
-        <v>0.198</v>
+        <v>0.692</v>
       </c>
       <c r="AW13">
-        <v>0.121</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="14" spans="1:49">
       <c r="A14">
-        <v>823471</v>
+        <v>824686</v>
       </c>
       <c r="B14" t="s">
         <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="F14">
-        <v>5.568</v>
+        <v>3.946</v>
       </c>
       <c r="G14">
-        <v>0.605</v>
+        <v>0.446</v>
       </c>
       <c r="H14">
         <v>0.094</v>
       </c>
       <c r="I14">
-        <v>0.344</v>
+        <v>0.23</v>
       </c>
       <c r="J14">
-        <v>0.071</v>
+        <v>0.106</v>
       </c>
       <c r="K14">
-        <v>0.225</v>
+        <v>0.252</v>
       </c>
       <c r="L14">
-        <v>1.105</v>
+        <v>0.6</v>
       </c>
       <c r="M14">
-        <v>0.151</v>
+        <v>0.185</v>
       </c>
       <c r="N14">
-        <v>1.885</v>
+        <v>1.376</v>
       </c>
       <c r="O14">
-        <v>6.505</v>
+        <v>6.235</v>
       </c>
       <c r="P14">
-        <v>3.831</v>
+        <v>2.957</v>
       </c>
       <c r="Q14">
-        <v>6.824</v>
+        <v>7.136</v>
       </c>
       <c r="R14">
-        <v>0.329</v>
+        <v>0.558</v>
       </c>
       <c r="S14">
-        <v>0.37</v>
+        <v>0.321</v>
       </c>
       <c r="T14">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="U14">
-        <v>0.076</v>
+        <v>0.025</v>
       </c>
       <c r="V14">
+        <v>0.004</v>
+      </c>
+      <c r="W14">
+        <v>0.001</v>
+      </c>
+      <c r="X14">
+        <v>0.078</v>
+      </c>
+      <c r="Y14">
+        <v>0.138</v>
+      </c>
+      <c r="Z14">
+        <v>0.146</v>
+      </c>
+      <c r="AA14">
+        <v>0.133</v>
+      </c>
+      <c r="AB14">
+        <v>0.131</v>
+      </c>
+      <c r="AC14">
+        <v>0.115</v>
+      </c>
+      <c r="AD14">
+        <v>0.085</v>
+      </c>
+      <c r="AE14">
+        <v>0.062</v>
+      </c>
+      <c r="AF14">
+        <v>0.045</v>
+      </c>
+      <c r="AG14">
+        <v>0.021</v>
+      </c>
+      <c r="AH14">
         <v>0.019</v>
       </c>
-      <c r="W14">
-        <v>0.006</v>
-      </c>
-      <c r="X14">
-        <v>0.023</v>
-      </c>
-      <c r="Y14">
-        <v>0.06</v>
-      </c>
-      <c r="Z14">
-        <v>0.09</v>
-      </c>
-      <c r="AA14">
-        <v>0.113</v>
-      </c>
-      <c r="AB14">
-        <v>0.122</v>
-      </c>
-      <c r="AC14">
-        <v>0.127</v>
-      </c>
-      <c r="AD14">
-        <v>0.114</v>
-      </c>
-      <c r="AE14">
-        <v>0.094</v>
-      </c>
-      <c r="AF14">
-        <v>0.077</v>
-      </c>
-      <c r="AG14">
-        <v>0.07</v>
-      </c>
-      <c r="AH14">
-        <v>0.041</v>
-      </c>
       <c r="AI14">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="AJ14">
-        <v>0.016</v>
+        <v>0.005</v>
       </c>
       <c r="AK14">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AL14">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AM14">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="AN14">
-        <v>0.737</v>
+        <v>0.426</v>
       </c>
       <c r="AO14">
-        <v>0.642</v>
+        <v>0.337</v>
       </c>
       <c r="AP14">
-        <v>0.678</v>
+        <v>0.392</v>
       </c>
       <c r="AQ14">
-        <v>0.656</v>
+        <v>0.383</v>
       </c>
       <c r="AR14">
-        <v>0.637</v>
+        <v>0.406</v>
       </c>
       <c r="AS14">
-        <v>0.607</v>
+        <v>0.401</v>
       </c>
       <c r="AT14">
-        <v>0.577</v>
+        <v>0.442</v>
       </c>
       <c r="AU14">
-        <v>0.556</v>
+        <v>0.458</v>
       </c>
       <c r="AV14">
-        <v>0.247</v>
+        <v>0.422</v>
       </c>
       <c r="AW14">
-        <v>0.088</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="15" spans="1:49">
       <c r="A15">
-        <v>823472</v>
+        <v>824772</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="F15">
-        <v>4.264</v>
+        <v>5.542</v>
       </c>
       <c r="G15">
-        <v>0.601</v>
+        <v>0.516</v>
       </c>
       <c r="H15">
-        <v>0.124</v>
+        <v>0.09</v>
       </c>
       <c r="I15">
-        <v>0.279</v>
+        <v>0.313</v>
       </c>
       <c r="J15">
-        <v>0.104</v>
+        <v>0.099</v>
       </c>
       <c r="K15">
-        <v>0.181</v>
+        <v>0.228</v>
       </c>
       <c r="L15">
-        <v>0.791</v>
+        <v>1.17</v>
       </c>
       <c r="M15">
-        <v>0.12</v>
+        <v>0.094</v>
       </c>
       <c r="N15">
-        <v>1.549</v>
+        <v>2.255</v>
       </c>
       <c r="O15">
-        <v>5.87</v>
+        <v>6.061</v>
       </c>
       <c r="P15">
-        <v>3.289</v>
+        <v>4.087</v>
       </c>
       <c r="Q15">
-        <v>7.619</v>
+        <v>8.028</v>
       </c>
       <c r="R15">
-        <v>0.447</v>
+        <v>0.307</v>
       </c>
       <c r="S15">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="T15">
-        <v>0.146</v>
+        <v>0.219</v>
       </c>
       <c r="U15">
-        <v>0.036</v>
+        <v>0.084</v>
       </c>
       <c r="V15">
+        <v>0.02</v>
+      </c>
+      <c r="W15">
         <v>0.007</v>
       </c>
-      <c r="W15">
-        <v>0.0</v>
-      </c>
       <c r="X15">
-        <v>0.055</v>
+        <v>0.033</v>
       </c>
       <c r="Y15">
-        <v>0.096</v>
+        <v>0.067</v>
       </c>
       <c r="Z15">
-        <v>0.142</v>
+        <v>0.093</v>
       </c>
       <c r="AA15">
-        <v>0.147</v>
+        <v>0.113</v>
       </c>
       <c r="AB15">
-        <v>0.153</v>
+        <v>0.122</v>
       </c>
       <c r="AC15">
-        <v>0.117</v>
+        <v>0.127</v>
       </c>
       <c r="AD15">
         <v>0.101</v>
       </c>
       <c r="AE15">
-        <v>0.067</v>
+        <v>0.08</v>
       </c>
       <c r="AF15">
-        <v>0.04</v>
+        <v>0.078</v>
       </c>
       <c r="AG15">
+        <v>0.059</v>
+      </c>
+      <c r="AH15">
+        <v>0.038</v>
+      </c>
+      <c r="AI15">
         <v>0.031</v>
       </c>
-      <c r="AH15">
-        <v>0.023</v>
-      </c>
-      <c r="AI15">
-        <v>0.012</v>
-      </c>
       <c r="AJ15">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="AK15">
-        <v>0.004</v>
+        <v>0.015</v>
       </c>
       <c r="AL15">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="AM15">
-        <v>0.001</v>
+        <v>0.016</v>
       </c>
       <c r="AN15">
-        <v>0.475</v>
+        <v>0.725</v>
       </c>
       <c r="AO15">
-        <v>0.427</v>
+        <v>0.597</v>
       </c>
       <c r="AP15">
-        <v>0.469</v>
+        <v>0.635</v>
       </c>
       <c r="AQ15">
-        <v>0.461</v>
+        <v>0.581</v>
       </c>
       <c r="AR15">
-        <v>0.479</v>
+        <v>0.579</v>
       </c>
       <c r="AS15">
-        <v>0.468</v>
+        <v>0.538</v>
       </c>
       <c r="AT15">
-        <v>0.499</v>
+        <v>0.526</v>
       </c>
       <c r="AU15">
-        <v>0.507</v>
+        <v>0.557</v>
       </c>
       <c r="AV15">
-        <v>0.221</v>
+        <v>0.525</v>
       </c>
       <c r="AW15">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="16" spans="1:49">
       <c r="A16">
-        <v>823634</v>
+        <v>825012</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F16">
-        <v>4.361</v>
+        <v>4.567</v>
       </c>
       <c r="G16">
-        <v>0.605</v>
+        <v>0.432</v>
       </c>
       <c r="H16">
-        <v>0.112</v>
+        <v>0.087</v>
       </c>
       <c r="I16">
-        <v>0.295</v>
+        <v>0.237</v>
       </c>
       <c r="J16">
-        <v>0.09</v>
+        <v>0.105</v>
       </c>
       <c r="K16">
-        <v>0.185</v>
+        <v>0.306</v>
       </c>
       <c r="L16">
-        <v>1.268</v>
+        <v>1.094</v>
       </c>
       <c r="M16">
-        <v>0.059</v>
+        <v>0.114</v>
       </c>
       <c r="N16">
-        <v>1.54</v>
+        <v>1.803</v>
       </c>
       <c r="O16">
-        <v>5.147</v>
+        <v>5.118</v>
       </c>
       <c r="P16">
-        <v>2.942</v>
+        <v>3.643</v>
       </c>
       <c r="Q16">
-        <v>6.209</v>
+        <v>7.031</v>
       </c>
       <c r="R16">
-        <v>0.287</v>
+        <v>0.348</v>
       </c>
       <c r="S16">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="T16">
-        <v>0.225</v>
+        <v>0.195</v>
       </c>
       <c r="U16">
-        <v>0.098</v>
+        <v>0.07</v>
       </c>
       <c r="V16">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="W16">
         <v>0.009</v>
       </c>
       <c r="X16">
-        <v>0.051</v>
+        <v>0.061</v>
       </c>
       <c r="Y16">
-        <v>0.103</v>
+        <v>0.099</v>
       </c>
       <c r="Z16">
-        <v>0.132</v>
+        <v>0.126</v>
       </c>
       <c r="AA16">
-        <v>0.15</v>
+        <v>0.138</v>
       </c>
       <c r="AB16">
-        <v>0.129</v>
+        <v>0.125</v>
       </c>
       <c r="AC16">
-        <v>0.129</v>
+        <v>0.122</v>
       </c>
       <c r="AD16">
-        <v>0.103</v>
+        <v>0.094</v>
       </c>
       <c r="AE16">
-        <v>0.07</v>
+        <v>0.076</v>
       </c>
       <c r="AF16">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="AG16">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="AH16">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="AI16">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="AJ16">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="AK16">
+        <v>0.009</v>
+      </c>
+      <c r="AL16">
         <v>0.006</v>
       </c>
-      <c r="AL16">
-        <v>0.002</v>
-      </c>
       <c r="AM16">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="AN16">
-        <v>0.522</v>
+        <v>0.452</v>
       </c>
       <c r="AO16">
+        <v>0.372</v>
+      </c>
+      <c r="AP16">
         <v>0.457</v>
       </c>
-      <c r="AP16">
-        <v>0.497</v>
-      </c>
       <c r="AQ16">
+        <v>0.452</v>
+      </c>
+      <c r="AR16">
         <v>0.451</v>
       </c>
-      <c r="AR16">
-        <v>0.452</v>
-      </c>
       <c r="AS16">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="AT16">
-        <v>0.491</v>
+        <v>0.56</v>
       </c>
       <c r="AU16">
-        <v>0.494</v>
+        <v>0.55</v>
       </c>
       <c r="AV16">
-        <v>0.249</v>
+        <v>0.542</v>
       </c>
       <c r="AW16">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="17" spans="1:49">
       <c r="A17">
-        <v>823714</v>
+        <v>822744</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>4.005</v>
+        <v>3.893</v>
       </c>
       <c r="G17">
-        <v>0.482</v>
+        <v>0.338</v>
       </c>
       <c r="H17">
+        <v>0.067</v>
+      </c>
+      <c r="I17">
+        <v>0.138</v>
+      </c>
+      <c r="J17">
+        <v>0.109</v>
+      </c>
+      <c r="K17">
+        <v>0.428</v>
+      </c>
+      <c r="L17">
+        <v>0.872</v>
+      </c>
+      <c r="M17">
+        <v>0.09</v>
+      </c>
+      <c r="N17">
+        <v>1.323</v>
+      </c>
+      <c r="O17">
+        <v>5.324</v>
+      </c>
+      <c r="P17">
+        <v>3.714</v>
+      </c>
+      <c r="Q17">
+        <v>10.733</v>
+      </c>
+      <c r="R17">
+        <v>0.418</v>
+      </c>
+      <c r="S17">
+        <v>0.369</v>
+      </c>
+      <c r="T17">
+        <v>0.153</v>
+      </c>
+      <c r="U17">
+        <v>0.046</v>
+      </c>
+      <c r="V17">
+        <v>0.012</v>
+      </c>
+      <c r="W17">
+        <v>0.002</v>
+      </c>
+      <c r="X17">
+        <v>0.085</v>
+      </c>
+      <c r="Y17">
+        <v>0.125</v>
+      </c>
+      <c r="Z17">
+        <v>0.153</v>
+      </c>
+      <c r="AA17">
+        <v>0.145</v>
+      </c>
+      <c r="AB17">
+        <v>0.128</v>
+      </c>
+      <c r="AC17">
         <v>0.113</v>
       </c>
-      <c r="I17">
-        <v>0.203</v>
-      </c>
-      <c r="J17">
-        <v>0.101</v>
-      </c>
-      <c r="K17">
-        <v>0.29</v>
-      </c>
-      <c r="L17">
-        <v>1.027</v>
-      </c>
-      <c r="M17">
-        <v>0.11</v>
-      </c>
-      <c r="N17">
-        <v>1.765</v>
-      </c>
-      <c r="O17">
-        <v>4.964</v>
-      </c>
-      <c r="P17">
-        <v>2.723</v>
-      </c>
-      <c r="Q17">
-        <v>9.087</v>
-      </c>
-      <c r="R17">
-        <v>0.354</v>
-      </c>
-      <c r="S17">
-        <v>0.377</v>
-      </c>
-      <c r="T17">
-        <v>0.183</v>
-      </c>
-      <c r="U17">
-        <v>0.066</v>
-      </c>
-      <c r="V17">
+      <c r="AD17">
+        <v>0.081</v>
+      </c>
+      <c r="AE17">
+        <v>0.061</v>
+      </c>
+      <c r="AF17">
+        <v>0.038</v>
+      </c>
+      <c r="AG17">
+        <v>0.029</v>
+      </c>
+      <c r="AH17">
         <v>0.018</v>
       </c>
-      <c r="W17">
-        <v>0.003</v>
-      </c>
-      <c r="X17">
-        <v>0.067</v>
-      </c>
-      <c r="Y17">
-        <v>0.116</v>
-      </c>
-      <c r="Z17">
-        <v>0.147</v>
-      </c>
-      <c r="AA17">
-        <v>0.158</v>
-      </c>
-      <c r="AB17">
-        <v>0.133</v>
-      </c>
-      <c r="AC17">
-        <v>0.116</v>
-      </c>
-      <c r="AD17">
-        <v>0.095</v>
-      </c>
-      <c r="AE17">
-        <v>0.064</v>
-      </c>
-      <c r="AF17">
-        <v>0.041</v>
-      </c>
-      <c r="AG17">
-        <v>0.023</v>
-      </c>
-      <c r="AH17">
-        <v>0.019</v>
-      </c>
       <c r="AI17">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="AJ17">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="AK17">
         <v>0.003</v>
@@ -3067,144 +3103,144 @@
         <v>0.003</v>
       </c>
       <c r="AM17">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AN17">
-        <v>0.438</v>
+        <v>0.384</v>
       </c>
       <c r="AO17">
-        <v>0.408</v>
+        <v>0.354</v>
       </c>
       <c r="AP17">
+        <v>0.363</v>
+      </c>
+      <c r="AQ17">
+        <v>0.361</v>
+      </c>
+      <c r="AR17">
         <v>0.431</v>
       </c>
-      <c r="AQ17">
-        <v>0.42</v>
-      </c>
-      <c r="AR17">
-        <v>0.425</v>
-      </c>
       <c r="AS17">
-        <v>0.429</v>
+        <v>0.484</v>
       </c>
       <c r="AT17">
-        <v>0.494</v>
+        <v>0.453</v>
       </c>
       <c r="AU17">
-        <v>0.478</v>
+        <v>0.529</v>
       </c>
       <c r="AV17">
-        <v>0.272</v>
+        <v>0.323</v>
       </c>
       <c r="AW17">
-        <v>0.121</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="18" spans="1:49">
       <c r="A18">
-        <v>823795</v>
+        <v>822990</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F18">
-        <v>4.738</v>
+        <v>4.639</v>
       </c>
       <c r="G18">
-        <v>0.612</v>
+        <v>0.574</v>
       </c>
       <c r="H18">
-        <v>0.12</v>
+        <v>0.114</v>
       </c>
       <c r="I18">
-        <v>0.307</v>
+        <v>0.292</v>
       </c>
       <c r="J18">
-        <v>0.077</v>
+        <v>0.085</v>
       </c>
       <c r="K18">
-        <v>0.196</v>
+        <v>0.224</v>
       </c>
       <c r="L18">
-        <v>1.229</v>
+        <v>0.937</v>
       </c>
       <c r="M18">
-        <v>0.108</v>
+        <v>0.115</v>
       </c>
       <c r="N18">
-        <v>1.427</v>
+        <v>1.722</v>
       </c>
       <c r="O18">
-        <v>5.072</v>
+        <v>5.32</v>
       </c>
       <c r="P18">
-        <v>4.232</v>
+        <v>4.098</v>
       </c>
       <c r="Q18">
-        <v>8.86</v>
+        <v>8.018</v>
       </c>
       <c r="R18">
-        <v>0.291</v>
+        <v>0.395</v>
       </c>
       <c r="S18">
-        <v>0.355</v>
+        <v>0.359</v>
       </c>
       <c r="T18">
-        <v>0.229</v>
+        <v>0.18</v>
       </c>
       <c r="U18">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="V18">
-        <v>0.029</v>
+        <v>0.015</v>
       </c>
       <c r="W18">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="X18">
-        <v>0.048</v>
+        <v>0.051</v>
       </c>
       <c r="Y18">
-        <v>0.069</v>
+        <v>0.086</v>
       </c>
       <c r="Z18">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="AA18">
-        <v>0.146</v>
+        <v>0.136</v>
       </c>
       <c r="AB18">
-        <v>0.138</v>
+        <v>0.133</v>
       </c>
       <c r="AC18">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="AD18">
-        <v>0.106</v>
+        <v>0.097</v>
       </c>
       <c r="AE18">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="AF18">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AG18">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="AH18">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="AI18">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="AJ18">
         <v>0.01</v>
@@ -3216,782 +3252,1974 @@
         <v>0.005</v>
       </c>
       <c r="AM18">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AN18">
-        <v>0.603</v>
+        <v>0.604</v>
       </c>
       <c r="AO18">
-        <v>0.538</v>
+        <v>0.498</v>
       </c>
       <c r="AP18">
-        <v>0.559</v>
+        <v>0.556</v>
       </c>
       <c r="AQ18">
-        <v>0.543</v>
+        <v>0.549</v>
       </c>
       <c r="AR18">
-        <v>0.571</v>
+        <v>0.497</v>
       </c>
       <c r="AS18">
-        <v>0.496</v>
+        <v>0.531</v>
       </c>
       <c r="AT18">
-        <v>0.491</v>
+        <v>0.469</v>
       </c>
       <c r="AU18">
-        <v>0.504</v>
+        <v>0.48</v>
       </c>
       <c r="AV18">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="AW18">
-        <v>0.107</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="19" spans="1:49">
       <c r="A19">
-        <v>824524</v>
+        <v>823066</v>
       </c>
       <c r="B19" t="s">
         <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F19">
-        <v>4.916</v>
+        <v>3.68</v>
       </c>
       <c r="G19">
-        <v>0.534</v>
+        <v>0.367</v>
       </c>
       <c r="H19">
-        <v>0.103</v>
+        <v>0.077</v>
       </c>
       <c r="I19">
-        <v>0.256</v>
+        <v>0.144</v>
       </c>
       <c r="J19">
-        <v>0.095</v>
+        <v>0.111</v>
       </c>
       <c r="K19">
-        <v>0.256</v>
+        <v>0.38</v>
       </c>
       <c r="L19">
-        <v>1.231</v>
+        <v>0.801</v>
       </c>
       <c r="M19">
-        <v>0.176</v>
+        <v>0.046</v>
       </c>
       <c r="N19">
-        <v>1.538</v>
+        <v>1.495</v>
       </c>
       <c r="O19">
-        <v>5.36</v>
+        <v>4.859</v>
       </c>
       <c r="P19">
-        <v>4.023</v>
+        <v>3.543</v>
       </c>
       <c r="Q19">
-        <v>7.626</v>
+        <v>9.136</v>
       </c>
       <c r="R19">
-        <v>0.283</v>
+        <v>0.439</v>
       </c>
       <c r="S19">
+        <v>0.373</v>
+      </c>
+      <c r="T19">
+        <v>0.146</v>
+      </c>
+      <c r="U19">
+        <v>0.033</v>
+      </c>
+      <c r="V19">
+        <v>0.007</v>
+      </c>
+      <c r="W19">
+        <v>0.002</v>
+      </c>
+      <c r="X19">
+        <v>0.079</v>
+      </c>
+      <c r="Y19">
+        <v>0.134</v>
+      </c>
+      <c r="Z19">
+        <v>0.161</v>
+      </c>
+      <c r="AA19">
+        <v>0.151</v>
+      </c>
+      <c r="AB19">
+        <v>0.138</v>
+      </c>
+      <c r="AC19">
+        <v>0.116</v>
+      </c>
+      <c r="AD19">
+        <v>0.092</v>
+      </c>
+      <c r="AE19">
+        <v>0.049</v>
+      </c>
+      <c r="AF19">
+        <v>0.033</v>
+      </c>
+      <c r="AG19">
+        <v>0.018</v>
+      </c>
+      <c r="AH19">
+        <v>0.012</v>
+      </c>
+      <c r="AI19">
+        <v>0.007</v>
+      </c>
+      <c r="AJ19">
+        <v>0.005</v>
+      </c>
+      <c r="AK19">
+        <v>0.002</v>
+      </c>
+      <c r="AL19">
+        <v>0.001</v>
+      </c>
+      <c r="AM19">
+        <v>0.001</v>
+      </c>
+      <c r="AN19">
+        <v>0.406</v>
+      </c>
+      <c r="AO19">
         <v>0.37</v>
       </c>
-      <c r="T19">
-        <v>0.229</v>
-      </c>
-      <c r="U19">
-        <v>0.079</v>
-      </c>
-      <c r="V19">
-        <v>0.031</v>
-      </c>
-      <c r="W19">
-        <v>0.008</v>
-      </c>
-      <c r="X19">
-        <v>0.036</v>
-      </c>
-      <c r="Y19">
-        <v>0.09</v>
-      </c>
-      <c r="Z19">
-        <v>0.104</v>
-      </c>
-      <c r="AA19">
-        <v>0.124</v>
-      </c>
-      <c r="AB19">
-        <v>0.147</v>
-      </c>
-      <c r="AC19">
-        <v>0.12</v>
-      </c>
-      <c r="AD19">
-        <v>0.118</v>
-      </c>
-      <c r="AE19">
-        <v>0.078</v>
-      </c>
-      <c r="AF19">
-        <v>0.059</v>
-      </c>
-      <c r="AG19">
-        <v>0.039</v>
-      </c>
-      <c r="AH19">
-        <v>0.035</v>
-      </c>
-      <c r="AI19">
-        <v>0.016</v>
-      </c>
-      <c r="AJ19">
-        <v>0.013</v>
-      </c>
-      <c r="AK19">
-        <v>0.009</v>
-      </c>
-      <c r="AL19">
-        <v>0.005</v>
-      </c>
-      <c r="AM19">
-        <v>0.007</v>
-      </c>
-      <c r="AN19">
-        <v>0.551</v>
-      </c>
-      <c r="AO19">
-        <v>0.593</v>
-      </c>
       <c r="AP19">
-        <v>0.526</v>
+        <v>0.396</v>
       </c>
       <c r="AQ19">
-        <v>0.54</v>
+        <v>0.367</v>
       </c>
       <c r="AR19">
-        <v>0.54</v>
+        <v>0.41</v>
       </c>
       <c r="AS19">
-        <v>0.546</v>
+        <v>0.399</v>
       </c>
       <c r="AT19">
-        <v>0.536</v>
+        <v>0.396</v>
       </c>
       <c r="AU19">
-        <v>0.591</v>
+        <v>0.417</v>
       </c>
       <c r="AV19">
-        <v>0.268</v>
+        <v>0.302</v>
       </c>
       <c r="AW19">
-        <v>0.124</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="20" spans="1:49">
       <c r="A20">
-        <v>824848</v>
+        <v>823146</v>
       </c>
       <c r="B20" t="s">
         <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F20">
-        <v>5.099</v>
+        <v>3.966</v>
       </c>
       <c r="G20">
-        <v>0.532</v>
+        <v>0.636</v>
       </c>
       <c r="H20">
-        <v>0.112</v>
+        <v>0.12</v>
       </c>
       <c r="I20">
-        <v>0.262</v>
+        <v>0.295</v>
       </c>
       <c r="J20">
-        <v>0.09</v>
+        <v>0.087</v>
       </c>
       <c r="K20">
-        <v>0.275</v>
+        <v>0.155</v>
       </c>
       <c r="L20">
-        <v>1.208</v>
+        <v>1.225</v>
       </c>
       <c r="M20">
-        <v>0.105</v>
+        <v>0.077</v>
       </c>
       <c r="N20">
-        <v>1.629</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
-        <v>5.344</v>
+        <v>3.918</v>
       </c>
       <c r="P20">
-        <v>4.51</v>
+        <v>4.206</v>
       </c>
       <c r="Q20">
-        <v>8.147</v>
+        <v>10.579</v>
       </c>
       <c r="R20">
-        <v>0.305</v>
+        <v>0.293</v>
       </c>
       <c r="S20">
-        <v>0.346</v>
+        <v>0.361</v>
       </c>
       <c r="T20">
-        <v>0.223</v>
+        <v>0.222</v>
       </c>
       <c r="U20">
-        <v>0.096</v>
+        <v>0.089</v>
       </c>
       <c r="V20">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
       <c r="W20">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="X20">
-        <v>0.03</v>
+        <v>0.068</v>
       </c>
       <c r="Y20">
-        <v>0.074</v>
+        <v>0.102</v>
       </c>
       <c r="Z20">
-        <v>0.099</v>
+        <v>0.15</v>
       </c>
       <c r="AA20">
-        <v>0.139</v>
+        <v>0.167</v>
       </c>
       <c r="AB20">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AC20">
-        <v>0.121</v>
+        <v>0.129</v>
       </c>
       <c r="AD20">
-        <v>0.111</v>
+        <v>0.081</v>
       </c>
       <c r="AE20">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="AF20">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="AG20">
-        <v>0.049</v>
+        <v>0.022</v>
       </c>
       <c r="AH20">
-        <v>0.035</v>
+        <v>0.015</v>
       </c>
       <c r="AI20">
-        <v>0.018</v>
+        <v>0.009</v>
       </c>
       <c r="AJ20">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="AK20">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="AL20">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="AM20">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="AN20">
-        <v>0.646</v>
+        <v>0.472</v>
       </c>
       <c r="AO20">
-        <v>0.582</v>
+        <v>0.482</v>
       </c>
       <c r="AP20">
-        <v>0.586</v>
+        <v>0.444</v>
       </c>
       <c r="AQ20">
-        <v>0.595</v>
+        <v>0.411</v>
       </c>
       <c r="AR20">
-        <v>0.58</v>
+        <v>0.445</v>
       </c>
       <c r="AS20">
-        <v>0.569</v>
+        <v>0.457</v>
       </c>
       <c r="AT20">
-        <v>0.53</v>
+        <v>0.444</v>
       </c>
       <c r="AU20">
-        <v>0.524</v>
+        <v>0.425</v>
       </c>
       <c r="AV20">
-        <v>0.288</v>
+        <v>0.201</v>
       </c>
       <c r="AW20">
-        <v>0.09</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="21" spans="1:49">
       <c r="A21">
-        <v>824850</v>
+        <v>823309</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F21">
-        <v>5.796</v>
+        <v>4.767</v>
       </c>
       <c r="G21">
-        <v>0.64</v>
+        <v>0.584</v>
       </c>
       <c r="H21">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="I21">
-        <v>0.359</v>
+        <v>0.295</v>
       </c>
       <c r="J21">
+        <v>0.094</v>
+      </c>
+      <c r="K21">
+        <v>0.205</v>
+      </c>
+      <c r="L21">
+        <v>1.216</v>
+      </c>
+      <c r="M21">
+        <v>0.111</v>
+      </c>
+      <c r="N21">
+        <v>1.498</v>
+      </c>
+      <c r="O21">
+        <v>5.195</v>
+      </c>
+      <c r="P21">
+        <v>3.884</v>
+      </c>
+      <c r="Q21">
+        <v>8.437</v>
+      </c>
+      <c r="R21">
+        <v>0.298</v>
+      </c>
+      <c r="S21">
+        <v>0.364</v>
+      </c>
+      <c r="T21">
+        <v>0.212</v>
+      </c>
+      <c r="U21">
+        <v>0.088</v>
+      </c>
+      <c r="V21">
+        <v>0.029</v>
+      </c>
+      <c r="W21">
+        <v>0.01</v>
+      </c>
+      <c r="X21">
+        <v>0.04</v>
+      </c>
+      <c r="Y21">
+        <v>0.084</v>
+      </c>
+      <c r="Z21">
+        <v>0.116</v>
+      </c>
+      <c r="AA21">
+        <v>0.141</v>
+      </c>
+      <c r="AB21">
+        <v>0.142</v>
+      </c>
+      <c r="AC21">
+        <v>0.129</v>
+      </c>
+      <c r="AD21">
+        <v>0.099</v>
+      </c>
+      <c r="AE21">
         <v>0.077</v>
       </c>
-      <c r="K21">
-        <v>0.178</v>
-      </c>
-      <c r="L21">
-        <v>1.342</v>
-      </c>
-      <c r="M21">
-        <v>0.098</v>
-      </c>
-      <c r="N21">
-        <v>1.597</v>
-      </c>
-      <c r="O21">
-        <v>5.685</v>
-      </c>
-      <c r="P21">
-        <v>5.259</v>
-      </c>
-      <c r="Q21">
-        <v>7.955</v>
-      </c>
-      <c r="R21">
-        <v>0.251</v>
-      </c>
-      <c r="S21">
-        <v>0.365</v>
-      </c>
-      <c r="T21">
-        <v>0.236</v>
-      </c>
-      <c r="U21">
-        <v>0.103</v>
-      </c>
-      <c r="V21">
-        <v>0.032</v>
-      </c>
-      <c r="W21">
-        <v>0.013</v>
-      </c>
-      <c r="X21">
-        <v>0.022</v>
-      </c>
-      <c r="Y21">
-        <v>0.047</v>
-      </c>
-      <c r="Z21">
-        <v>0.085</v>
-      </c>
-      <c r="AA21">
-        <v>0.106</v>
-      </c>
-      <c r="AB21">
-        <v>0.126</v>
-      </c>
-      <c r="AC21">
-        <v>0.123</v>
-      </c>
-      <c r="AD21">
-        <v>0.125</v>
-      </c>
-      <c r="AE21">
-        <v>0.097</v>
-      </c>
       <c r="AF21">
-        <v>0.072</v>
+        <v>0.058</v>
       </c>
       <c r="AG21">
-        <v>0.066</v>
+        <v>0.04</v>
       </c>
       <c r="AH21">
-        <v>0.045</v>
+        <v>0.028</v>
       </c>
       <c r="AI21">
-        <v>0.032</v>
+        <v>0.017</v>
       </c>
       <c r="AJ21">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="AK21">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="AL21">
-        <v>0.009</v>
+        <v>0.005</v>
       </c>
       <c r="AM21">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="AN21">
-        <v>0.87</v>
+        <v>0.501</v>
       </c>
       <c r="AO21">
-        <v>0.694</v>
+        <v>0.467</v>
       </c>
       <c r="AP21">
-        <v>0.815</v>
+        <v>0.524</v>
       </c>
       <c r="AQ21">
-        <v>0.677</v>
+        <v>0.525</v>
       </c>
       <c r="AR21">
-        <v>0.675</v>
+        <v>0.533</v>
       </c>
       <c r="AS21">
-        <v>0.547</v>
+        <v>0.548</v>
       </c>
       <c r="AT21">
-        <v>0.541</v>
+        <v>0.574</v>
       </c>
       <c r="AU21">
-        <v>0.509</v>
+        <v>0.592</v>
       </c>
       <c r="AV21">
-        <v>0.228</v>
+        <v>0.278</v>
       </c>
       <c r="AW21">
-        <v>0.1</v>
+        <v>0.122</v>
       </c>
     </row>
     <row r="22" spans="1:49">
       <c r="A22">
-        <v>824929</v>
+        <v>823389</v>
       </c>
       <c r="B22" t="s">
         <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F22">
-        <v>5.313</v>
+        <v>4.478</v>
       </c>
       <c r="G22">
-        <v>0.493</v>
+        <v>0.546</v>
       </c>
       <c r="H22">
-        <v>0.086</v>
+        <v>0.103</v>
       </c>
       <c r="I22">
-        <v>0.259</v>
+        <v>0.253</v>
       </c>
       <c r="J22">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="K22">
-        <v>0.319</v>
+        <v>0.234</v>
       </c>
       <c r="L22">
-        <v>1.11</v>
+        <v>0.916</v>
       </c>
       <c r="M22">
-        <v>0.12</v>
+        <v>0.108</v>
       </c>
       <c r="N22">
-        <v>1.602</v>
+        <v>1.768</v>
       </c>
       <c r="O22">
-        <v>6.367</v>
+        <v>5.284</v>
       </c>
       <c r="P22">
-        <v>3.752</v>
+        <v>3.866</v>
       </c>
       <c r="Q22">
-        <v>6.481</v>
+        <v>7.559</v>
       </c>
       <c r="R22">
-        <v>0.329</v>
+        <v>0.395</v>
       </c>
       <c r="S22">
-        <v>0.363</v>
+        <v>0.372</v>
       </c>
       <c r="T22">
-        <v>0.207</v>
+        <v>0.169</v>
       </c>
       <c r="U22">
-        <v>0.078</v>
+        <v>0.051</v>
       </c>
       <c r="V22">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="W22">
+        <v>0.001</v>
+      </c>
+      <c r="X22">
+        <v>0.058</v>
+      </c>
+      <c r="Y22">
+        <v>0.093</v>
+      </c>
+      <c r="Z22">
+        <v>0.127</v>
+      </c>
+      <c r="AA22">
+        <v>0.13</v>
+      </c>
+      <c r="AB22">
+        <v>0.148</v>
+      </c>
+      <c r="AC22">
+        <v>0.129</v>
+      </c>
+      <c r="AD22">
+        <v>0.094</v>
+      </c>
+      <c r="AE22">
+        <v>0.071</v>
+      </c>
+      <c r="AF22">
+        <v>0.054</v>
+      </c>
+      <c r="AG22">
+        <v>0.038</v>
+      </c>
+      <c r="AH22">
+        <v>0.024</v>
+      </c>
+      <c r="AI22">
+        <v>0.012</v>
+      </c>
+      <c r="AJ22">
+        <v>0.008</v>
+      </c>
+      <c r="AK22">
+        <v>0.006</v>
+      </c>
+      <c r="AL22">
+        <v>0.005</v>
+      </c>
+      <c r="AM22">
         <v>0.004</v>
       </c>
-      <c r="X22">
-        <v>0.034</v>
-      </c>
-      <c r="Y22">
-        <v>0.07</v>
-      </c>
-      <c r="Z22">
-        <v>0.097</v>
-      </c>
-      <c r="AA22">
-        <v>0.108</v>
-      </c>
-      <c r="AB22">
-        <v>0.134</v>
-      </c>
-      <c r="AC22">
-        <v>0.134</v>
-      </c>
-      <c r="AD22">
-        <v>0.103</v>
-      </c>
-      <c r="AE22">
-        <v>0.092</v>
-      </c>
-      <c r="AF22">
-        <v>0.072</v>
-      </c>
-      <c r="AG22">
-        <v>0.054</v>
-      </c>
-      <c r="AH22">
-        <v>0.036</v>
-      </c>
-      <c r="AI22">
-        <v>0.021</v>
-      </c>
-      <c r="AJ22">
-        <v>0.016</v>
-      </c>
-      <c r="AK22">
-        <v>0.013</v>
-      </c>
-      <c r="AL22">
-        <v>0.007</v>
-      </c>
-      <c r="AM22">
-        <v>0.009</v>
-      </c>
       <c r="AN22">
-        <v>0.671</v>
+        <v>0.537</v>
       </c>
       <c r="AO22">
-        <v>0.534</v>
+        <v>0.52</v>
       </c>
       <c r="AP22">
-        <v>0.589</v>
+        <v>0.515</v>
       </c>
       <c r="AQ22">
-        <v>0.561</v>
+        <v>0.506</v>
       </c>
       <c r="AR22">
-        <v>0.582</v>
+        <v>0.482</v>
       </c>
       <c r="AS22">
-        <v>0.614</v>
+        <v>0.479</v>
       </c>
       <c r="AT22">
-        <v>0.624</v>
+        <v>0.487</v>
       </c>
       <c r="AU22">
-        <v>0.598</v>
+        <v>0.473</v>
       </c>
       <c r="AV22">
-        <v>0.302</v>
+        <v>0.232</v>
       </c>
       <c r="AW22">
-        <v>0.103</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="23" spans="1:49">
       <c r="A23">
-        <v>825016</v>
+        <v>823557</v>
       </c>
       <c r="B23" t="s">
         <v>49</v>
       </c>
       <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23">
+        <v>4.842</v>
+      </c>
+      <c r="G23">
+        <v>0.574</v>
+      </c>
+      <c r="H23">
+        <v>0.116</v>
+      </c>
+      <c r="I23">
+        <v>0.277</v>
+      </c>
+      <c r="J23">
+        <v>0.078</v>
+      </c>
+      <c r="K23">
+        <v>0.232</v>
+      </c>
+      <c r="L23">
+        <v>1.334</v>
+      </c>
+      <c r="M23">
+        <v>0.14</v>
+      </c>
+      <c r="N23">
+        <v>1.383</v>
+      </c>
+      <c r="O23">
+        <v>5.129</v>
+      </c>
+      <c r="P23">
+        <v>4.091</v>
+      </c>
+      <c r="Q23">
+        <v>8.05</v>
+      </c>
+      <c r="R23">
+        <v>0.262</v>
+      </c>
+      <c r="S23">
+        <v>0.351</v>
+      </c>
+      <c r="T23">
+        <v>0.238</v>
+      </c>
+      <c r="U23">
+        <v>0.102</v>
+      </c>
+      <c r="V23">
+        <v>0.033</v>
+      </c>
+      <c r="W23">
+        <v>0.013</v>
+      </c>
+      <c r="X23">
+        <v>0.041</v>
+      </c>
+      <c r="Y23">
+        <v>0.086</v>
+      </c>
+      <c r="Z23">
+        <v>0.102</v>
+      </c>
+      <c r="AA23">
+        <v>0.13</v>
+      </c>
+      <c r="AB23">
+        <v>0.138</v>
+      </c>
+      <c r="AC23">
+        <v>0.132</v>
+      </c>
+      <c r="AD23">
+        <v>0.114</v>
+      </c>
+      <c r="AE23">
+        <v>0.086</v>
+      </c>
+      <c r="AF23">
+        <v>0.053</v>
+      </c>
+      <c r="AG23">
+        <v>0.044</v>
+      </c>
+      <c r="AH23">
+        <v>0.028</v>
+      </c>
+      <c r="AI23">
+        <v>0.021</v>
+      </c>
+      <c r="AJ23">
+        <v>0.01</v>
+      </c>
+      <c r="AK23">
+        <v>0.006</v>
+      </c>
+      <c r="AL23">
+        <v>0.004</v>
+      </c>
+      <c r="AM23">
+        <v>0.006</v>
+      </c>
+      <c r="AN23">
+        <v>0.651</v>
+      </c>
+      <c r="AO23">
+        <v>0.545</v>
+      </c>
+      <c r="AP23">
+        <v>0.605</v>
+      </c>
+      <c r="AQ23">
+        <v>0.537</v>
+      </c>
+      <c r="AR23">
+        <v>0.526</v>
+      </c>
+      <c r="AS23">
+        <v>0.505</v>
+      </c>
+      <c r="AT23">
+        <v>0.518</v>
+      </c>
+      <c r="AU23">
+        <v>0.506</v>
+      </c>
+      <c r="AV23">
+        <v>0.238</v>
+      </c>
+      <c r="AW23">
+        <v>0.122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49">
+      <c r="A24">
+        <v>823713</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24">
+        <v>4.994</v>
+      </c>
+      <c r="G24">
+        <v>0.561</v>
+      </c>
+      <c r="H24">
+        <v>0.096</v>
+      </c>
+      <c r="I24">
+        <v>0.301</v>
+      </c>
+      <c r="J24">
+        <v>0.092</v>
+      </c>
+      <c r="K24">
+        <v>0.228</v>
+      </c>
+      <c r="L24">
+        <v>0.878</v>
+      </c>
+      <c r="M24">
+        <v>0.097</v>
+      </c>
+      <c r="N24">
+        <v>1.809</v>
+      </c>
+      <c r="O24">
+        <v>6.37</v>
+      </c>
+      <c r="P24">
+        <v>3.816</v>
+      </c>
+      <c r="Q24">
+        <v>7.707</v>
+      </c>
+      <c r="R24">
+        <v>0.418</v>
+      </c>
+      <c r="S24">
+        <v>0.367</v>
+      </c>
+      <c r="T24">
+        <v>0.152</v>
+      </c>
+      <c r="U24">
+        <v>0.047</v>
+      </c>
+      <c r="V24">
+        <v>0.013</v>
+      </c>
+      <c r="W24">
+        <v>0.003</v>
+      </c>
+      <c r="X24">
+        <v>0.04</v>
+      </c>
+      <c r="Y24">
+        <v>0.076</v>
+      </c>
+      <c r="Z24">
+        <v>0.114</v>
+      </c>
+      <c r="AA24">
+        <v>0.118</v>
+      </c>
+      <c r="AB24">
+        <v>0.134</v>
+      </c>
+      <c r="AC24">
+        <v>0.13</v>
+      </c>
+      <c r="AD24">
+        <v>0.101</v>
+      </c>
+      <c r="AE24">
+        <v>0.092</v>
+      </c>
+      <c r="AF24">
+        <v>0.068</v>
+      </c>
+      <c r="AG24">
+        <v>0.044</v>
+      </c>
+      <c r="AH24">
+        <v>0.031</v>
+      </c>
+      <c r="AI24">
+        <v>0.021</v>
+      </c>
+      <c r="AJ24">
+        <v>0.01</v>
+      </c>
+      <c r="AK24">
+        <v>0.01</v>
+      </c>
+      <c r="AL24">
+        <v>0.006</v>
+      </c>
+      <c r="AM24">
+        <v>0.005</v>
+      </c>
+      <c r="AN24">
+        <v>0.651</v>
+      </c>
+      <c r="AO24">
+        <v>0.615</v>
+      </c>
+      <c r="AP24">
+        <v>0.637</v>
+      </c>
+      <c r="AQ24">
+        <v>0.59</v>
+      </c>
+      <c r="AR24">
+        <v>0.588</v>
+      </c>
+      <c r="AS24">
+        <v>0.495</v>
+      </c>
+      <c r="AT24">
+        <v>0.477</v>
+      </c>
+      <c r="AU24">
+        <v>0.487</v>
+      </c>
+      <c r="AV24">
+        <v>0.206</v>
+      </c>
+      <c r="AW24">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49">
+      <c r="A25">
+        <v>823877</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25">
+        <v>3.319</v>
+      </c>
+      <c r="G25">
+        <v>0.39</v>
+      </c>
+      <c r="H25">
+        <v>0.086</v>
+      </c>
+      <c r="I25">
+        <v>0.137</v>
+      </c>
+      <c r="J25">
+        <v>0.114</v>
+      </c>
+      <c r="K25">
+        <v>0.349</v>
+      </c>
+      <c r="L25">
+        <v>0.78</v>
+      </c>
+      <c r="M25">
+        <v>0.106</v>
+      </c>
+      <c r="N25">
+        <v>1.316</v>
+      </c>
+      <c r="O25">
+        <v>4.316</v>
+      </c>
+      <c r="P25">
+        <v>3.356</v>
+      </c>
+      <c r="Q25">
+        <v>9.716</v>
+      </c>
+      <c r="R25">
+        <v>0.453</v>
+      </c>
+      <c r="S25">
+        <v>0.368</v>
+      </c>
+      <c r="T25">
+        <v>0.135</v>
+      </c>
+      <c r="U25">
+        <v>0.036</v>
+      </c>
+      <c r="V25">
+        <v>0.005</v>
+      </c>
+      <c r="W25">
+        <v>0.002</v>
+      </c>
+      <c r="X25">
+        <v>0.109</v>
+      </c>
+      <c r="Y25">
+        <v>0.146</v>
+      </c>
+      <c r="Z25">
+        <v>0.179</v>
+      </c>
+      <c r="AA25">
+        <v>0.165</v>
+      </c>
+      <c r="AB25">
+        <v>0.126</v>
+      </c>
+      <c r="AC25">
+        <v>0.094</v>
+      </c>
+      <c r="AD25">
+        <v>0.072</v>
+      </c>
+      <c r="AE25">
+        <v>0.043</v>
+      </c>
+      <c r="AF25">
+        <v>0.028</v>
+      </c>
+      <c r="AG25">
+        <v>0.019</v>
+      </c>
+      <c r="AH25">
+        <v>0.009</v>
+      </c>
+      <c r="AI25">
+        <v>0.003</v>
+      </c>
+      <c r="AJ25">
+        <v>0.003</v>
+      </c>
+      <c r="AK25">
+        <v>0.002</v>
+      </c>
+      <c r="AL25">
+        <v>0.001</v>
+      </c>
+      <c r="AM25">
+        <v>0.002</v>
+      </c>
+      <c r="AN25">
+        <v>0.371</v>
+      </c>
+      <c r="AO25">
+        <v>0.285</v>
+      </c>
+      <c r="AP25">
+        <v>0.356</v>
+      </c>
+      <c r="AQ25">
+        <v>0.332</v>
+      </c>
+      <c r="AR25">
+        <v>0.306</v>
+      </c>
+      <c r="AS25">
+        <v>0.37</v>
+      </c>
+      <c r="AT25">
+        <v>0.394</v>
+      </c>
+      <c r="AU25">
+        <v>0.424</v>
+      </c>
+      <c r="AV25">
+        <v>0.273</v>
+      </c>
+      <c r="AW25">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49">
+      <c r="A26">
+        <v>824041</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
         <v>69</v>
       </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23">
-        <v>5.941</v>
-      </c>
-      <c r="G23">
-        <v>0.631</v>
-      </c>
-      <c r="H23">
+      <c r="F26">
+        <v>5.129</v>
+      </c>
+      <c r="G26">
+        <v>0.509</v>
+      </c>
+      <c r="H26">
+        <v>0.089</v>
+      </c>
+      <c r="I26">
+        <v>0.254</v>
+      </c>
+      <c r="J26">
+        <v>0.097</v>
+      </c>
+      <c r="K26">
+        <v>0.285</v>
+      </c>
+      <c r="L26">
+        <v>1.282</v>
+      </c>
+      <c r="M26">
+        <v>0.121</v>
+      </c>
+      <c r="N26">
+        <v>1.62</v>
+      </c>
+      <c r="O26">
+        <v>4.686</v>
+      </c>
+      <c r="P26">
+        <v>5.253</v>
+      </c>
+      <c r="Q26">
+        <v>9.774</v>
+      </c>
+      <c r="R26">
+        <v>0.286</v>
+      </c>
+      <c r="S26">
+        <v>0.347</v>
+      </c>
+      <c r="T26">
+        <v>0.222</v>
+      </c>
+      <c r="U26">
+        <v>0.103</v>
+      </c>
+      <c r="V26">
+        <v>0.034</v>
+      </c>
+      <c r="W26">
+        <v>0.008</v>
+      </c>
+      <c r="X26">
+        <v>0.036</v>
+      </c>
+      <c r="Y26">
+        <v>0.071</v>
+      </c>
+      <c r="Z26">
+        <v>0.098</v>
+      </c>
+      <c r="AA26">
+        <v>0.127</v>
+      </c>
+      <c r="AB26">
+        <v>0.122</v>
+      </c>
+      <c r="AC26">
+        <v>0.133</v>
+      </c>
+      <c r="AD26">
+        <v>0.117</v>
+      </c>
+      <c r="AE26">
+        <v>0.089</v>
+      </c>
+      <c r="AF26">
+        <v>0.068</v>
+      </c>
+      <c r="AG26">
+        <v>0.054</v>
+      </c>
+      <c r="AH26">
+        <v>0.033</v>
+      </c>
+      <c r="AI26">
+        <v>0.02</v>
+      </c>
+      <c r="AJ26">
+        <v>0.014</v>
+      </c>
+      <c r="AK26">
+        <v>0.006</v>
+      </c>
+      <c r="AL26">
+        <v>0.004</v>
+      </c>
+      <c r="AM26">
+        <v>0.007</v>
+      </c>
+      <c r="AN26">
+        <v>0.674</v>
+      </c>
+      <c r="AO26">
+        <v>0.577</v>
+      </c>
+      <c r="AP26">
+        <v>0.629</v>
+      </c>
+      <c r="AQ26">
+        <v>0.58</v>
+      </c>
+      <c r="AR26">
+        <v>0.544</v>
+      </c>
+      <c r="AS26">
+        <v>0.552</v>
+      </c>
+      <c r="AT26">
+        <v>0.522</v>
+      </c>
+      <c r="AU26">
+        <v>0.518</v>
+      </c>
+      <c r="AV26">
+        <v>0.295</v>
+      </c>
+      <c r="AW26">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49">
+      <c r="A27">
+        <v>824287</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27">
+        <v>5.18</v>
+      </c>
+      <c r="G27">
+        <v>0.514</v>
+      </c>
+      <c r="H27">
+        <v>0.088</v>
+      </c>
+      <c r="I27">
+        <v>0.254</v>
+      </c>
+      <c r="J27">
+        <v>0.09</v>
+      </c>
+      <c r="K27">
+        <v>0.289</v>
+      </c>
+      <c r="L27">
+        <v>0.97</v>
+      </c>
+      <c r="M27">
+        <v>0.12</v>
+      </c>
+      <c r="N27">
+        <v>1.734</v>
+      </c>
+      <c r="O27">
+        <v>5.527</v>
+      </c>
+      <c r="P27">
+        <v>5.098</v>
+      </c>
+      <c r="Q27">
+        <v>8.274</v>
+      </c>
+      <c r="R27">
+        <v>0.381</v>
+      </c>
+      <c r="S27">
+        <v>0.363</v>
+      </c>
+      <c r="T27">
+        <v>0.181</v>
+      </c>
+      <c r="U27">
+        <v>0.057</v>
+      </c>
+      <c r="V27">
+        <v>0.015</v>
+      </c>
+      <c r="W27">
+        <v>0.003</v>
+      </c>
+      <c r="X27">
+        <v>0.038</v>
+      </c>
+      <c r="Y27">
+        <v>0.07</v>
+      </c>
+      <c r="Z27">
+        <v>0.095</v>
+      </c>
+      <c r="AA27">
+        <v>0.121</v>
+      </c>
+      <c r="AB27">
+        <v>0.129</v>
+      </c>
+      <c r="AC27">
+        <v>0.127</v>
+      </c>
+      <c r="AD27">
+        <v>0.11</v>
+      </c>
+      <c r="AE27">
+        <v>0.091</v>
+      </c>
+      <c r="AF27">
+        <v>0.072</v>
+      </c>
+      <c r="AG27">
+        <v>0.061</v>
+      </c>
+      <c r="AH27">
+        <v>0.035</v>
+      </c>
+      <c r="AI27">
+        <v>0.019</v>
+      </c>
+      <c r="AJ27">
+        <v>0.011</v>
+      </c>
+      <c r="AK27">
+        <v>0.01</v>
+      </c>
+      <c r="AL27">
+        <v>0.004</v>
+      </c>
+      <c r="AM27">
+        <v>0.006</v>
+      </c>
+      <c r="AN27">
+        <v>0.685</v>
+      </c>
+      <c r="AO27">
+        <v>0.605</v>
+      </c>
+      <c r="AP27">
+        <v>0.632</v>
+      </c>
+      <c r="AQ27">
+        <v>0.571</v>
+      </c>
+      <c r="AR27">
+        <v>0.602</v>
+      </c>
+      <c r="AS27">
+        <v>0.527</v>
+      </c>
+      <c r="AT27">
+        <v>0.509</v>
+      </c>
+      <c r="AU27">
+        <v>0.528</v>
+      </c>
+      <c r="AV27">
+        <v>0.265</v>
+      </c>
+      <c r="AW27">
+        <v>0.119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49">
+      <c r="A28">
+        <v>824366</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28">
+        <v>5.947</v>
+      </c>
+      <c r="G28">
+        <v>0.415</v>
+      </c>
+      <c r="H28">
+        <v>0.075</v>
+      </c>
+      <c r="I28">
+        <v>0.213</v>
+      </c>
+      <c r="J28">
+        <v>0.095</v>
+      </c>
+      <c r="K28">
+        <v>0.393</v>
+      </c>
+      <c r="L28">
+        <v>1.299</v>
+      </c>
+      <c r="M28">
+        <v>0.23</v>
+      </c>
+      <c r="N28">
+        <v>2.046</v>
+      </c>
+      <c r="O28">
+        <v>6.413</v>
+      </c>
+      <c r="P28">
+        <v>3.598</v>
+      </c>
+      <c r="Q28">
+        <v>7.043</v>
+      </c>
+      <c r="R28">
+        <v>0.275</v>
+      </c>
+      <c r="S28">
+        <v>0.351</v>
+      </c>
+      <c r="T28">
+        <v>0.234</v>
+      </c>
+      <c r="U28">
+        <v>0.096</v>
+      </c>
+      <c r="V28">
+        <v>0.03</v>
+      </c>
+      <c r="W28">
+        <v>0.014</v>
+      </c>
+      <c r="X28">
+        <v>0.02</v>
+      </c>
+      <c r="Y28">
+        <v>0.05</v>
+      </c>
+      <c r="Z28">
+        <v>0.084</v>
+      </c>
+      <c r="AA28">
+        <v>0.108</v>
+      </c>
+      <c r="AB28">
+        <v>0.109</v>
+      </c>
+      <c r="AC28">
+        <v>0.118</v>
+      </c>
+      <c r="AD28">
+        <v>0.121</v>
+      </c>
+      <c r="AE28">
+        <v>0.103</v>
+      </c>
+      <c r="AF28">
+        <v>0.087</v>
+      </c>
+      <c r="AG28">
+        <v>0.06</v>
+      </c>
+      <c r="AH28">
+        <v>0.045</v>
+      </c>
+      <c r="AI28">
+        <v>0.026</v>
+      </c>
+      <c r="AJ28">
+        <v>0.024</v>
+      </c>
+      <c r="AK28">
+        <v>0.013</v>
+      </c>
+      <c r="AL28">
+        <v>0.012</v>
+      </c>
+      <c r="AM28">
+        <v>0.02</v>
+      </c>
+      <c r="AN28">
+        <v>0.73</v>
+      </c>
+      <c r="AO28">
+        <v>0.62</v>
+      </c>
+      <c r="AP28">
+        <v>0.691</v>
+      </c>
+      <c r="AQ28">
+        <v>0.655</v>
+      </c>
+      <c r="AR28">
+        <v>0.653</v>
+      </c>
+      <c r="AS28">
+        <v>0.647</v>
+      </c>
+      <c r="AT28">
+        <v>0.656</v>
+      </c>
+      <c r="AU28">
+        <v>0.639</v>
+      </c>
+      <c r="AV28">
+        <v>0.385</v>
+      </c>
+      <c r="AW28">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49">
+      <c r="A29">
+        <v>824686</v>
+      </c>
+      <c r="B29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29">
+        <v>4.209</v>
+      </c>
+      <c r="G29">
+        <v>0.554</v>
+      </c>
+      <c r="H29">
+        <v>0.106</v>
+      </c>
+      <c r="I29">
+        <v>0.252</v>
+      </c>
+      <c r="J29">
+        <v>0.094</v>
+      </c>
+      <c r="K29">
+        <v>0.23</v>
+      </c>
+      <c r="L29">
+        <v>0.8</v>
+      </c>
+      <c r="M29">
+        <v>0.114</v>
+      </c>
+      <c r="N29">
+        <v>1.433</v>
+      </c>
+      <c r="O29">
+        <v>5.6</v>
+      </c>
+      <c r="P29">
+        <v>3.607</v>
+      </c>
+      <c r="Q29">
+        <v>6.913</v>
+      </c>
+      <c r="R29">
+        <v>0.448</v>
+      </c>
+      <c r="S29">
+        <v>0.363</v>
+      </c>
+      <c r="T29">
+        <v>0.14</v>
+      </c>
+      <c r="U29">
+        <v>0.039</v>
+      </c>
+      <c r="V29">
+        <v>0.008</v>
+      </c>
+      <c r="W29">
+        <v>0.001</v>
+      </c>
+      <c r="X29">
+        <v>0.06</v>
+      </c>
+      <c r="Y29">
+        <v>0.102</v>
+      </c>
+      <c r="Z29">
+        <v>0.137</v>
+      </c>
+      <c r="AA29">
+        <v>0.153</v>
+      </c>
+      <c r="AB29">
+        <v>0.143</v>
+      </c>
+      <c r="AC29">
+        <v>0.121</v>
+      </c>
+      <c r="AD29">
+        <v>0.099</v>
+      </c>
+      <c r="AE29">
+        <v>0.065</v>
+      </c>
+      <c r="AF29">
+        <v>0.044</v>
+      </c>
+      <c r="AG29">
+        <v>0.029</v>
+      </c>
+      <c r="AH29">
+        <v>0.017</v>
+      </c>
+      <c r="AI29">
+        <v>0.011</v>
+      </c>
+      <c r="AJ29">
+        <v>0.007</v>
+      </c>
+      <c r="AK29">
+        <v>0.008</v>
+      </c>
+      <c r="AL29">
+        <v>0.001</v>
+      </c>
+      <c r="AM29">
+        <v>0.002</v>
+      </c>
+      <c r="AN29">
+        <v>0.466</v>
+      </c>
+      <c r="AO29">
+        <v>0.462</v>
+      </c>
+      <c r="AP29">
+        <v>0.443</v>
+      </c>
+      <c r="AQ29">
+        <v>0.455</v>
+      </c>
+      <c r="AR29">
+        <v>0.439</v>
+      </c>
+      <c r="AS29">
+        <v>0.462</v>
+      </c>
+      <c r="AT29">
+        <v>0.463</v>
+      </c>
+      <c r="AU29">
+        <v>0.52</v>
+      </c>
+      <c r="AV29">
+        <v>0.242</v>
+      </c>
+      <c r="AW29">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49">
+      <c r="A30">
+        <v>824772</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30">
+        <v>5.007</v>
+      </c>
+      <c r="G30">
+        <v>0.484</v>
+      </c>
+      <c r="H30">
+        <v>0.099</v>
+      </c>
+      <c r="I30">
+        <v>0.228</v>
+      </c>
+      <c r="J30">
+        <v>0.09</v>
+      </c>
+      <c r="K30">
+        <v>0.313</v>
+      </c>
+      <c r="L30">
+        <v>1.043</v>
+      </c>
+      <c r="M30">
+        <v>0.161</v>
+      </c>
+      <c r="N30">
+        <v>2.105</v>
+      </c>
+      <c r="O30">
+        <v>5.865</v>
+      </c>
+      <c r="P30">
+        <v>3.357</v>
+      </c>
+      <c r="Q30">
+        <v>7.772</v>
+      </c>
+      <c r="R30">
+        <v>0.353</v>
+      </c>
+      <c r="S30">
+        <v>0.362</v>
+      </c>
+      <c r="T30">
+        <v>0.199</v>
+      </c>
+      <c r="U30">
+        <v>0.067</v>
+      </c>
+      <c r="V30">
+        <v>0.016</v>
+      </c>
+      <c r="W30">
+        <v>0.004</v>
+      </c>
+      <c r="X30">
+        <v>0.039</v>
+      </c>
+      <c r="Y30">
+        <v>0.075</v>
+      </c>
+      <c r="Z30">
         <v>0.104</v>
       </c>
-      <c r="I23">
-        <v>0.365</v>
-      </c>
-      <c r="J23">
-        <v>0.08</v>
-      </c>
-      <c r="K23">
-        <v>0.193</v>
-      </c>
-      <c r="L23">
-        <v>1.624</v>
-      </c>
-      <c r="M23">
+      <c r="AA30">
+        <v>0.126</v>
+      </c>
+      <c r="AB30">
+        <v>0.138</v>
+      </c>
+      <c r="AC30">
+        <v>0.128</v>
+      </c>
+      <c r="AD30">
+        <v>0.101</v>
+      </c>
+      <c r="AE30">
+        <v>0.088</v>
+      </c>
+      <c r="AF30">
+        <v>0.069</v>
+      </c>
+      <c r="AG30">
+        <v>0.052</v>
+      </c>
+      <c r="AH30">
+        <v>0.032</v>
+      </c>
+      <c r="AI30">
+        <v>0.025</v>
+      </c>
+      <c r="AJ30">
+        <v>0.012</v>
+      </c>
+      <c r="AK30">
+        <v>0.004</v>
+      </c>
+      <c r="AL30">
+        <v>0.004</v>
+      </c>
+      <c r="AM30">
+        <v>0.004</v>
+      </c>
+      <c r="AN30">
+        <v>0.634</v>
+      </c>
+      <c r="AO30">
+        <v>0.494</v>
+      </c>
+      <c r="AP30">
+        <v>0.595</v>
+      </c>
+      <c r="AQ30">
+        <v>0.535</v>
+      </c>
+      <c r="AR30">
+        <v>0.572</v>
+      </c>
+      <c r="AS30">
+        <v>0.552</v>
+      </c>
+      <c r="AT30">
+        <v>0.535</v>
+      </c>
+      <c r="AU30">
+        <v>0.547</v>
+      </c>
+      <c r="AV30">
+        <v>0.303</v>
+      </c>
+      <c r="AW30">
+        <v>0.102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49">
+      <c r="A31">
+        <v>825012</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+      <c r="E31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31">
+        <v>5.023</v>
+      </c>
+      <c r="G31">
+        <v>0.568</v>
+      </c>
+      <c r="H31">
+        <v>0.105</v>
+      </c>
+      <c r="I31">
+        <v>0.306</v>
+      </c>
+      <c r="J31">
+        <v>0.087</v>
+      </c>
+      <c r="K31">
+        <v>0.237</v>
+      </c>
+      <c r="L31">
+        <v>1.444</v>
+      </c>
+      <c r="M31">
+        <v>0.094</v>
+      </c>
+      <c r="N31">
+        <v>1.904</v>
+      </c>
+      <c r="O31">
+        <v>4.864</v>
+      </c>
+      <c r="P31">
+        <v>3.733</v>
+      </c>
+      <c r="Q31">
+        <v>9.401</v>
+      </c>
+      <c r="R31">
+        <v>0.233</v>
+      </c>
+      <c r="S31">
+        <v>0.342</v>
+      </c>
+      <c r="T31">
+        <v>0.256</v>
+      </c>
+      <c r="U31">
+        <v>0.114</v>
+      </c>
+      <c r="V31">
+        <v>0.033</v>
+      </c>
+      <c r="W31">
+        <v>0.022</v>
+      </c>
+      <c r="X31">
+        <v>0.036</v>
+      </c>
+      <c r="Y31">
+        <v>0.082</v>
+      </c>
+      <c r="Z31">
+        <v>0.106</v>
+      </c>
+      <c r="AA31">
+        <v>0.12</v>
+      </c>
+      <c r="AB31">
+        <v>0.137</v>
+      </c>
+      <c r="AC31">
+        <v>0.132</v>
+      </c>
+      <c r="AD31">
+        <v>0.111</v>
+      </c>
+      <c r="AE31">
+        <v>0.087</v>
+      </c>
+      <c r="AF31">
+        <v>0.055</v>
+      </c>
+      <c r="AG31">
+        <v>0.044</v>
+      </c>
+      <c r="AH31">
+        <v>0.03</v>
+      </c>
+      <c r="AI31">
+        <v>0.025</v>
+      </c>
+      <c r="AJ31">
+        <v>0.013</v>
+      </c>
+      <c r="AK31">
+        <v>0.007</v>
+      </c>
+      <c r="AL31">
+        <v>0.005</v>
+      </c>
+      <c r="AM31">
+        <v>0.01</v>
+      </c>
+      <c r="AN31">
+        <v>0.576</v>
+      </c>
+      <c r="AO31">
+        <v>0.538</v>
+      </c>
+      <c r="AP31">
+        <v>0.589</v>
+      </c>
+      <c r="AQ31">
+        <v>0.573</v>
+      </c>
+      <c r="AR31">
+        <v>0.525</v>
+      </c>
+      <c r="AS31">
+        <v>0.569</v>
+      </c>
+      <c r="AT31">
+        <v>0.601</v>
+      </c>
+      <c r="AU31">
+        <v>0.568</v>
+      </c>
+      <c r="AV31">
+        <v>0.268</v>
+      </c>
+      <c r="AW31">
         <v>0.11</v>
-      </c>
-      <c r="N23">
-        <v>2.172</v>
-      </c>
-      <c r="O23">
-        <v>5.846</v>
-      </c>
-      <c r="P23">
-        <v>3.49</v>
-      </c>
-      <c r="Q23">
-        <v>7.806</v>
-      </c>
-      <c r="R23">
-        <v>0.195</v>
-      </c>
-      <c r="S23">
-        <v>0.322</v>
-      </c>
-      <c r="T23">
-        <v>0.266</v>
-      </c>
-      <c r="U23">
-        <v>0.133</v>
-      </c>
-      <c r="V23">
-        <v>0.057</v>
-      </c>
-      <c r="W23">
-        <v>0.027</v>
-      </c>
-      <c r="X23">
-        <v>0.019</v>
-      </c>
-      <c r="Y23">
-        <v>0.047</v>
-      </c>
-      <c r="Z23">
-        <v>0.081</v>
-      </c>
-      <c r="AA23">
-        <v>0.101</v>
-      </c>
-      <c r="AB23">
-        <v>0.114</v>
-      </c>
-      <c r="AC23">
-        <v>0.124</v>
-      </c>
-      <c r="AD23">
-        <v>0.119</v>
-      </c>
-      <c r="AE23">
-        <v>0.114</v>
-      </c>
-      <c r="AF23">
-        <v>0.082</v>
-      </c>
-      <c r="AG23">
-        <v>0.064</v>
-      </c>
-      <c r="AH23">
-        <v>0.043</v>
-      </c>
-      <c r="AI23">
-        <v>0.032</v>
-      </c>
-      <c r="AJ23">
-        <v>0.019</v>
-      </c>
-      <c r="AK23">
-        <v>0.013</v>
-      </c>
-      <c r="AL23">
-        <v>0.012</v>
-      </c>
-      <c r="AM23">
-        <v>0.016</v>
-      </c>
-      <c r="AN23">
-        <v>0.789</v>
-      </c>
-      <c r="AO23">
-        <v>0.673</v>
-      </c>
-      <c r="AP23">
-        <v>0.763</v>
-      </c>
-      <c r="AQ23">
-        <v>0.719</v>
-      </c>
-      <c r="AR23">
-        <v>0.676</v>
-      </c>
-      <c r="AS23">
-        <v>0.624</v>
-      </c>
-      <c r="AT23">
-        <v>0.619</v>
-      </c>
-      <c r="AU23">
-        <v>0.588</v>
-      </c>
-      <c r="AV23">
-        <v>0.252</v>
-      </c>
-      <c r="AW23">
-        <v>0.112</v>
       </c>
     </row>
   </sheetData>
